--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,17 +450,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,20 +487,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Falsifier / Kill-Cond</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Derived</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Inherited/Open</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>SpotChecked</t>
         </is>
@@ -513,33 +519,38 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>BH_Thermal2Pi</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bekenstein-Hawking 1/4 coefficient</t>
+          <t>Bekenstein-Hawking coefficient 1/4 (T=kappa/2pi, S=A/4), GEOMETRIC route</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>I — via log-g matching (log g = pi); 'matching, not derivation' (§4, conclusion)</t>
+          <t>Both factors ED-structural: 1/2 from kappa=1/(2r_s) (b-profile slope, GR-III); 2pi from near-horizon Rindler shape via smoothness (numerically confirmed)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>current — in-folder EDG status of the 1/4 is INHERITED (Staleness #1)</t>
+          <t>tool = Euclidean continuation, the SAME route GR uses (on par with GR, not beyond); b-profile + kappa inherited from GR-III; arrow-native continuation-free 2pi OPEN (§4b)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
+          <t>current — the in-folder DERIVED route for the 1/4 (imported 2026-07-29)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29 (read in full before import)</t>
         </is>
       </c>
     </row>
@@ -551,31 +562,40 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>044_5</t>
+          <t>039</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Greybody factors Gamma_ls</t>
+          <t>Horizon = b-&gt;0 decoupling surface (Gamma_cross collapse)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>I — 'NOT a new derivation... INHERITED from Regge-Wheeler 1957/Zerilli/Page'</t>
+          <t>D mechanism (decoupling-surface)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>r_H location + kappa INHERITED from GR (§3.2 honest-ack: r_H a CG reference, not derived)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -585,31 +605,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>047_5</t>
+          <t>040</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Universal T = kappa/2pi for all 4 horizon types</t>
+          <t>Trans-Planckian resolution (modes terminate at wc)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>I — 'INHERITED from standard semi-classical GR'; genuine ED content = V5-saturation identification only</t>
+          <t>D-via-I</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>conditional on P-V5-UV-Cutoff + P-Cutoff-Saturation</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -619,31 +644,36 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>041</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>t_Page ~ 0.54·tau_BH; c1, wc, c* values</t>
+          <t>Planck-mass remnant M* = c*·l_P (Scenario C)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D-via-I</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>conditional on P-Cutoff-Saturation-Endpoint + P-Remnant-Stability + 048; c* inherited</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -653,31 +683,40 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>042</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>'Remnants NOT a dark-matter candidate'</t>
+          <t>No-singularity (C_cum bounded, r &gt;= l_P)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position</t>
+          <t>D-via-I</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>conditional on P-Bandwidth-Boundedness + P-Substrate-Interior-Cutoff; interior OPEN</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>current — abstract's 'P04-derived' is really postulated (Staleness #3)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -687,31 +726,36 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>043</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>'Classical singularity is a coarse-graining artifact'</t>
+          <t>Area-law FORM S ∝ A</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position</t>
+          <t>D-via-I (form forced)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>conditional on P-Horizon-Participation + P-Multiplicity-g; coefficient inherited by this route</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>current (the FORM; coefficient has a separate geometric route — next row)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -721,31 +765,36 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>044_5</t>
+          <t>044</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>'Leading-order match is identification, not derivation'</t>
+          <t>BHPT scattering / Regge-Wheeler form</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position; greybody factors inherited</t>
+          <t>form-forced</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>conditional on P-Horizon-Ingoing-Only + P-Asymptotic-Outgoing; cross-sections inherited</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -755,31 +804,36 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>047_5</t>
+          <t>045</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>'Four-horizon structural identification'</t>
+          <t>Helicity preserved (Schwarzschild) / amplified (Kerr)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position; temperature fully inherited</t>
+          <t>form-forced</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>conditional on P-Helicity-Channel + P-Kerr-Helicity-Coupling; superradiance OPEN</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -789,35 +843,36 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>046</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>'Paradox not generated' + 'information not lost'</t>
+          <t>Kerr twist g_tphi</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position (audit rows 9-10); rests on P-Substrate-Unitarity; 'structural ledger, not constructive proof'</t>
+          <t>form-forced</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>current — the arc's load-bearing soft spot</t>
+          <t>conditional on P-Substrate-Vorticity + P-Twist-Coarse-Graining; a inherited; interior OPEN</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -827,31 +882,36 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>047_5</t>
+          <t>047</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Cross-class horizon identification (M3)</t>
+          <t>Hawking temperature T_H = kappa/2pi via V5 KMS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>genuine ED content = the V5-saturation mechanism only</t>
+          <t>KMS =&gt; thermal = D</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>kappa I; Euclidean/conical 2pi = I-via-DCGT (audit rows 5-8, not substrate-derived)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>current — see Staleness #2 on the '2pi derived' claim</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -861,31 +921,36 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>052</t>
+          <t>047</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Paradox synthesis (integrates 039+047+050+041)</t>
+          <t>Non-thermal Hawking correction [1 - c1(w/wc)^2]</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>arc consolidation</t>
+          <t>D form</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>conditional on P-V5-Even; wc chosen-to-match, c1 inherited</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -895,31 +960,36 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>042/046</t>
+          <t>048</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Substrate BH interior for r &lt; l_P</t>
+          <t>Scenario C forced (A, B excluded)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>D-via-I</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>conditional on P-Resummation-Convergence + P-Endpoint-Truncation; coeffs inherited</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -929,31 +999,36 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>049</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Substrate derivation of log g</t>
+          <t>PBH relic abundance Omega* ∝ n_PBH·M*</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>D-via-I</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>conditional on P-One-Remnant-Per-PBH</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -963,31 +1038,36 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>050</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Superradiance</t>
+          <t>Page-curve rise + turnover + decline</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>conditional on P-V5-EntBudget + P-Re-routing; t_Page ~ 0.54·tau_BH inherited; unitarity OPEN</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -997,31 +1077,40 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>047/BH_Thermal2Pi</t>
+          <t>HorizonTiling</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Arrow-native (continuation-free) 2pi</t>
+          <t>Horizon tiles ~1 bit/Planck cell (3 counts: holo=1, frozen 0.78, edge 0.88)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>OPEN — the derived-2pi route is Euclidean (reversible-time); arrow-native 2pi not yet supplied</t>
+          <t>measured convergence</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>open (memo relocated OUT of EDG)</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>2 of 3 counts assume the emergent geometry (curvature emergence OPEN); scale l_V5~l_P inherited</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>current — explicit consilience, 'not a novel prediction, not tiered as one'</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1031,31 +1120,36 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>050/051</t>
+          <t>043</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Full unitarity (constructive, not postulated)</t>
+          <t>Bekenstein-Hawking 1/4 coefficient, COMBINATORIAL route</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>OPEN — target #4; 051 assumes it (P-Substrate-Unitarity)</t>
-        </is>
-      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>I — via log-g matching (log g = pi); 'matching, not derivation' (§4). NOTE: folder also has the geometric DERIVED route (BH_Thermal2Pi); net folder status of the 1/4 = DERIVED</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>current — this route inherits; net 1/4 now derived (Staleness #1 RESOLVED)</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1065,31 +1159,32 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>052_5</t>
+          <t>044_5</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Substrate-anchored tau_V5 floor (merger-lag)</t>
+          <t>Greybody factors Gamma_ls</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>I — 'NOT a new derivation... INHERITED from Regge-Wheeler 1957/Zerilli/Page'</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1099,31 +1194,32 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>HorizonTiling/046</t>
+          <t>047_5</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Curvature emergence underneath the geometric counts</t>
+          <t>Universal T = kappa/2pi for all 4 horizon types</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>OPEN — the bridge under 2-of-3 tiling counts + the Kerr geometry</t>
-        </is>
-      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>I — 'INHERITED from standard semi-classical GR'; genuine ED content = V5-saturation identification only</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1133,39 +1229,32 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>039</t>
+          <t>050</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Horizon = b-&gt;0 decoupling surface (Gamma_cross collapse)</t>
+          <t>t_Page ~ 0.54·tau_BH; c1, wc, c* values</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>D mechanism (decoupling-surface)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>r_H location + kappa INHERITED from GR (§3.2 honest-ack: r_H a CG reference, not derived)</t>
-        </is>
-      </c>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>I</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1175,35 +1264,32 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>041</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Trans-Planckian resolution (modes terminate at wc)</t>
+          <t>'Remnants NOT a dark-matter candidate'</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-V5-UV-Cutoff + P-Cutoff-Saturation</t>
-        </is>
-      </c>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1213,35 +1299,32 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>042</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Planck-mass remnant M* = c*·l_P (Scenario C)</t>
+          <t>'Classical singularity is a coarse-graining artifact'</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Cutoff-Saturation-Endpoint + P-Remnant-Stability + 048; c* inherited</t>
-        </is>
-      </c>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1251,39 +1334,32 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>044_5</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>No-singularity (C_cum bounded, r &gt;= l_P)</t>
+          <t>'Leading-order match is identification, not derivation'</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Bandwidth-Boundedness + P-Substrate-Interior-Cutoff; interior OPEN</t>
-        </is>
-      </c>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>current — abstract's 'P04-derived' is really postulated (Staleness #3)</t>
+          <t>A-&gt;position; greybody factors inherited</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1293,35 +1369,32 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>047_5</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Area-law FORM S ∝ A</t>
+          <t>'Four-horizon structural identification'</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I (form forced)</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Horizon-Participation + P-Multiplicity-g; coefficient inherited</t>
-        </is>
-      </c>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>current (the FORM; coefficient separate — Staleness #1)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>A-&gt;position; temperature fully inherited</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1331,35 +1404,36 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>044</t>
+          <t>051</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>BHPT scattering / Regge-Wheeler form</t>
+          <t>'Paradox not generated' + 'information not lost'</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>form-forced</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Horizon-Ingoing-Only + P-Asymptotic-Outgoing; cross-sections inherited</t>
-        </is>
-      </c>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t>A-&gt;position (audit rows 9-10); rests on P-Substrate-Unitarity; 'structural ledger, not constructive proof'</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>current — the arc's load-bearing soft spot</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1369,35 +1443,40 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>045</t>
+          <t>052_5</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Helicity preserved (Schwarzschild) / amplified (Kerr)</t>
+          <t>Merger-lag (existence of a delay)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
+          <t>Prediction</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>form-forced</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Helicity-Channel + P-Kerr-Helicity-Coupling; superradiance OPEN</t>
-        </is>
-      </c>
+          <t>22-Ways P2 (merger-lag): PROVISIONAL, existence-only; NOT refutation-grade (needs substrate tau_V5 floor, OPEN)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>PROVISIONAL / M2, existence-only; tau_V5 floor OPEN; numerics inherited; zero D rows (row 14 A-&gt;position); NOT refutation-grade in BTFR sense; confirms 22-Ways P2</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>current — do not upgrade until a substrate tau_V5 floor is supplied</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1407,35 +1486,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>046</t>
+          <t>047_5</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Kerr twist g_tphi</t>
+          <t>Cross-class horizon identification (M3)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>form-forced</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Substrate-Vorticity + P-Twist-Coarse-Graining; a inherited; interior OPEN</t>
-        </is>
-      </c>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>genuine ED content = the V5-saturation mechanism only</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1445,35 +1521,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>052</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Hawking temperature T_H = kappa/2pi via V5 KMS</t>
+          <t>Paradox synthesis (integrates 039+047+050+041)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>KMS =&gt; thermal = D</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>kappa I; Euclidean/conical 2pi = I-via-DCGT (audit rows 5-8, not substrate-derived)</t>
-        </is>
-      </c>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>current — see Staleness #2 on the '2pi derived' claim</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>arc consolidation</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1483,35 +1556,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>047</t>
+          <t>042/046</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Non-thermal Hawking correction [1 - c1(w/wc)^2]</t>
+          <t>Substrate BH interior for r &lt; l_P</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>D form</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-V5-Even; wc chosen-to-match, c1 inherited</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1521,35 +1591,32 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>043</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Scenario C forced (A, B excluded)</t>
+          <t>Substrate derivation of log g</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-Resummation-Convergence + P-Endpoint-Truncation; coeffs inherited</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1559,35 +1626,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>045</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>PBH relic abundance Omega* ∝ n_PBH·M*</t>
+          <t>Superradiance</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-One-Remnant-Per-PBH</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1597,35 +1661,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>050/051</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Page-curve rise + turnover + decline</t>
+          <t>Full unitarity (constructive, not postulated)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-via-I / Form-forced</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-V5-EntBudget + P-Re-routing; t_Page ~ 0.54·tau_BH inherited; unitarity OPEN</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>OPEN — target #4; 051 assumes it (P-Substrate-Unitarity)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1640,30 +1701,31 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Merger-lag (existence of a delay)</t>
+          <t>Substrate-anchored tau_V5 floor (merger-lag)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>PROVISIONAL / M2, existence-only; tau_V5 floor OPEN; numerics inherited; zero D rows (row 14 A-&gt;position); NOT refutation-grade in BTFR sense; confirms 22-Ways P2</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>22-Ways P2 (merger-lag): PROVISIONAL, existence-only; NOT refutation-grade (needs substrate tau_V5 floor, OPEN)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>current — do not upgrade until a substrate tau_V5 floor is supplied</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1673,75 +1735,67 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>HorizonTiling</t>
+          <t>BH_Thermal2Pi</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Horizon tiles ~1 bit/Planck cell (3 counts: holo=1, frozen 0.78, edge 0.88)</t>
+          <t>Arrow-native (continuation-free) 2pi</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>measured convergence</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2 of 3 counts assume the emergent geometry (curvature emergence OPEN); scale l_V5~l_P inherited</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>current — explicit consilience, 'not a novel prediction, not tiered as one'</t>
+          <t>OPEN — derived-2pi route is Euclidean (reversible-time), on par with GR; arrow-native 2pi from raw commitment statistics not yet supplied (§4b honest negative; possibly a category error — 2pi may be an intrinsically continuum feature)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>open (§4b, now in-folder)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>64</v>
+          <t>Black-hole</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HorizonTiling/046</t>
+        </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Schmidt rank&gt;1 =&gt; non-factorizable</t>
+          <t>Curvature emergence underneath the geometric counts</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>D (standard SVD applied)</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>conditional on P-V5-Schmidt-Generic</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>current — strengthens 063 only under that postulate</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>OPEN — the bridge under 2-of-3 tiling counts + the Kerr geometry</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1749,12 +1803,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>65</v>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Monogamy (CKW-form inequality)</t>
+          <t>Schmidt rank&gt;1 =&gt; non-factorizable</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1762,22 +1818,23 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>form D (form-forced) from V5 finite budget + P04 additivity</t>
-        </is>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
+          <t>D (standard SVD applied)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t>conditional on P-V5-Schmidt-Generic</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>current — strengthens 063 only under that postulate</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1785,12 +1842,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>66</v>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>No-signaling p(a|x,y)=p(a|x), over-determined by 3 locks</t>
+          <t>Monogamy (CKW-form inequality)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1798,26 +1857,23 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Lock L1 (marginal independence) = D-via-I from tensor-product + POVM completeness</t>
-        </is>
-      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>L2 rests on P-Substrate-Causality; L3 = Paper_073; '3-locks =&gt; over-determination' is A-&gt;position</t>
+          <t>form D (form-forced) from V5 finite budget + P04 additivity</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>current — cleanest paper in arc; Bell-Tsirelson explicitly OPEN here (row 11)</t>
+          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1825,12 +1881,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>68</v>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>von Neumann entropy form S = -Tr rho log rho</t>
+          <t>No-signaling p(a|x,y)=p(a|x), over-determined by 3 locks</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1838,22 +1896,27 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I (Shannon-Khinchin + Khinchin uniqueness)</t>
-        </is>
-      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-Continuity + P-Additivity + P-Maximality; normalization inherited</t>
+          <t>Lock L1 (marginal independence) = D-via-I from tensor-product + POVM completeness</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>current — two substrate-derivations open</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
+          <t>L2 rests on P-Substrate-Causality; L3 = Paper_073; '3-locks =&gt; over-determination' is A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>current — cleanest paper in arc; Bell-Tsirelson explicitly OPEN here (row 11)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1861,35 +1924,38 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>63</v>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>E-2 bilocal cross-chain term Delta_KL exists</t>
+          <t>von Neumann entropy form S = -Tr rho log rho</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>D conditional on V5 (Paper_090)</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (Shannon-Khinchin + Khinchin uniqueness)</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>conditional on P-Continuity + P-Additivity + P-Maximality; normalization inherited</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current — two substrate-derivations open</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1897,31 +1963,38 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>64</v>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>The Schmidt decomposition form itself</t>
+          <t>E-2 bilocal cross-chain term Delta_KL exists</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>I — SVD is standard math (round-7 relabel: was D-cond-SVD, now I)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>D conditional on V5 (Paper_090)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1929,12 +2002,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>68</v>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>k_B / log-base normalization; concrete entropy values</t>
+          <t>The Schmidt decomposition form itself</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1943,17 +2018,18 @@
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
+          <t>I — SVD is standard math (round-7 relabel: was D-cond-SVD, now I)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1961,12 +2037,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
-        <v>69</v>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Tsirelson bound 2*sqrt(2)</t>
+          <t>k_B / log-base normalization; concrete entropy values</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1975,17 +2053,18 @@
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>I — 'not derived from first principles... INHERITED' (preamble 1)</t>
-        </is>
-      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1993,12 +2072,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>69</v>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Bell &lt; Tsirelson &lt; NS nesting; PR-box exclusion</t>
+          <t>Tsirelson bound 2*sqrt(2)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2006,26 +2087,19 @@
           <t>Selected/Inherited</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I (form composition)</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>entirely conditional on P-V5-Hilbert-Constraint</t>
-        </is>
-      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>current — inherits a Soler residual (see Status/staleness)</t>
+          <t>I — 'not derived from first principles... INHERITED' (preamble 1)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2033,31 +2107,38 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>63</v>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>E-1 factorizable Psi^AB = Psi^A x Psi^B &amp; the tensor-product structure</t>
+          <t>Bell &lt; Tsirelson &lt; NS nesting; PR-box exclusion</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>P-Bipartite-Mapping — 'definitional commitment, not a separate derivation'</t>
+          <t>D-via-I (form composition)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>entirely conditional on P-V5-Hilbert-Constraint</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>current — inherits a Soler residual (see Status/staleness)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>yes 2026-07-28</t>
         </is>
@@ -2069,12 +2150,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>64</v>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>V5-bilocal has Schmidt rank&gt;1 generically</t>
+          <t>E-1 factorizable Psi^AB = Psi^A x Psi^B &amp; the tensor-product structure</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2083,17 +2166,22 @@
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>P-V5-Schmidt-Generic — derivability from V5 envelope alone is OPEN</t>
-        </is>
-      </c>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t>P-Bipartite-Mapping — 'definitional commitment, not a separate derivation'</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2101,12 +2189,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>65</v>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Monogamy budget cap; measure saturates the budget</t>
+          <t>V5-bilocal has Schmidt rank&gt;1 generically</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2115,17 +2205,18 @@
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>P-V5-Budget, P-Measure-Saturation</t>
-        </is>
-      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t>P-V5-Schmidt-Generic — derivability from V5 envelope alone is OPEN</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2133,12 +2224,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>69</v>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>ED sits at Tsirelson; PR-boxes excluded</t>
+          <t>Monogamy budget cap; measure saturates the budget</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2147,17 +2240,18 @@
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>P-V5-Hilbert-Constraint</t>
-        </is>
-      </c>
+      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>P-V5-Budget, P-Measure-Saturation</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2165,35 +2259,34 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>63</v>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>E-2 non-factorizability is IRREDUCIBLE</t>
+          <t>ED sits at Tsirelson; PR-boxes excluded</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>A-&gt;assertion — 'does not supply an explicit irreducibility proof' (round-5: was D, now A)</t>
-        </is>
-      </c>
+      <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>current — the arc's load-bearing soft spot</t>
+          <t>P-V5-Hilbert-Constraint</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2201,12 +2294,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>71</v>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ER=EPR-class echo</t>
+          <t>E-2 non-factorizability is IRREDUCIBLE</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2215,17 +2310,22 @@
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>A-&gt;position — 'does NOT derive ER=EPR constructively'; rests on P-V5-Shared-EntanglementGravity</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
+          <t>A-&gt;assertion — 'does not supply an explicit irreducibility proof' (round-5: was D, now A)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>current — the arc's load-bearing soft spot</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2233,12 +2333,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>72</v>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>071</t>
+        </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Entanglement = unresolved individuation regime (not action-at-a-distance)</t>
+          <t>ER=EPR-class echo</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2247,17 +2349,18 @@
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>A-&gt;position — interpretive framing; does not modify QM predictions</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
+          <t>A-&gt;position — 'does NOT derive ER=EPR constructively'; rests on P-V5-Shared-EntanglementGravity</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2265,31 +2368,34 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>70</v>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Bipartite architecture as one phenomenon</t>
+          <t>Entanglement = unresolved individuation regime (not action-at-a-distance)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Asserted</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>A-&gt;position — 'does not override or strengthen constituent verdicts'</t>
-        </is>
-      </c>
+      <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>current (consolidation)</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
+          <t>A-&gt;position — interpretive framing; does not modify QM predictions</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2297,27 +2403,34 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>67</v>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>von Neumann E-6 (duplicate)</t>
+          <t>Bipartite architecture as one phenomenon</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Superseded</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>SUPERSEDED by 068 (merged 2026-07-05); kept for provenance</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
+          <t>A-&gt;position — 'does not override or strengthen constituent verdicts'</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>current (consolidation)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2325,31 +2438,30 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>64</v>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>067</t>
+        </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>derivability of P-V5-Schmidt-Generic</t>
+          <t>von Neumann E-6 (duplicate)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by 068 (merged 2026-07-05); kept for provenance</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2357,12 +2469,14 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>68</v>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>O-vN-1: derive P-Additivity from P04 (quantitative)</t>
+          <t>derivability of P-V5-Schmidt-Generic</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2371,17 +2485,18 @@
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2389,34 +2504,72 @@
           <t>Entanglement</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>68</v>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>O-vN-1: derive P-Additivity from P04 (quantitative)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
           <t>O-vN-2: derive P-Maximality from P11</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>OPEN — structurally blocked; ED has no substrate-level temperature</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H55"/>
+  <autoFilter ref="A1:I56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1800,17 +1800,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>Baryogenesis</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Schmidt rank&gt;1 =&gt; non-factorizable</t>
+          <t>Matter-antimatter asymmetry = structural consequence of R4 single-template admissibility + first-arrival IC</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1821,35 +1821,39 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D (standard SVD applied)</t>
+          <t>single-template admission (coherence functional + V5 phase-coherence + no-slack, D-via-I); global lock-in</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-V5-Schmidt-Generic</t>
+          <t>eta_B~6e-10 I (Planck/BBN); WHICH chirality wins = IC-INHERITED</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>current — strengthens 063 only under that postulate</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>current — form-IDENTIFIED (M3); P-BinaryAdmission WITHDRAWN; native Z2 relocated to IC not derived (#2b open core persists)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>Cos-06</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Monogamy (CKW-form inequality)</t>
+          <t>Primordial tensor modes = substrate SADDLE-HESSIAN fluctuations, SAME mechanism as post-recombination GW (GW_00)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1860,17 +1864,17 @@
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>form D (form-forced) from V5 finite budget + P04 additivity</t>
+          <t>the cross-arc identification (D-via-I); 'cleanest cross-arc unification in the arc'</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
+          <t>consistency relation n_T=-r/8 inherited</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — genuine ED-distinctive content</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -1878,99 +1882,99 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>Cos-01</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>No-signaling p(a|x,y)=p(a|x), over-determined by 3 locks</t>
+          <t>Inflation = post-SCBU substrate SATURATION regime; a(t)=a0 e^{Ht}</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Lock L1 (marginal independence) = D-via-I from tensor-product + POVM completeness</t>
+          <t>exp growth via Q1A+Q2A+C3 chain (row 13 CLOSED)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>L2 rests on P-Substrate-Causality; L3 = Paper_073; '3-locks =&gt; over-determination' is A-&gt;position</t>
+          <t>Friedmann/de Sitter step I; uniform-Psi IC-inherited; Route A open</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>current — cleanest paper in arc; Bell-Tsirelson explicitly OPEN here (row 11)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current — form-IDENTIFIED (M3), value+IC inherited</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>Cos-05</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>von Neumann entropy form S = -Tr rho log rho</t>
+          <t>Dark energy = late-universe SATURATION regime; w=-1 (leading order)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>D-via-I (Shannon-Khinchin + Khinchin uniqueness)</t>
+          <t>w=-1 via the SAME inherited Q1A+Q2A+C3 chain as Cos-01</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-Continuity + P-Additivity + P-Maximality; normalization inherited</t>
+          <t>Lambda value + Omega_L~0.685 I; H0 pending Route A</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>current — two substrate-derivations open</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>current — form-IDENTIFIED (M3), conditional on Route A</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>Cos-05</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>E-2 bilocal cross-chain term Delta_KL exists</t>
+          <t>Lambda-smallness (120-OOM) reduces to Route A + Friedmann; naive rho_vac~M_P^4 STRUCTURALLY ABSENT substrate-side (no infinite mode-tower)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1981,52 +1985,60 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>D conditional on V5 (Paper_090)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>catastrophe-dissolution D-via-I via Paper_038_5 §3.7; rho_L=(3/8pi)H0^2 M_P^2</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>smallness = quantitative-magnitude conditional on Route A (single load-bearing OPEN)</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — value inherited via H0, smallness open; do NOT say 'ED inherits the overshoot'</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
+          <t>yes 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>DF2/DF4</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>The Schmidt decomposition form itself</t>
+          <t>Low-accel galaxies CONSISTENT WITH (not counterexamples to) derived a0, via commitment-density saturation suppression</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>O(1) hierarchy g_int&lt;g_ext&lt;&lt;a0; EFE-class suppression from finite outer-scale capacity</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>I — SVD is standard math (round-7 relabel: was D-cond-SVD, now I)</t>
+          <t>a0=cH0/(2pi) I (Paper_029); the suppression FUNCTION not yet derived from primitives (§5)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — Grounded (observational, order-of-magnitude); MOND cross-link</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2034,52 +2046,60 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>SCBU</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>k_B / log-base normalization; concrete entropy values</t>
+          <t>a0 &amp; xi_canonical = two projection MECHANISMS of one boundary R_H=c/H0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>the two mechanisms (D-via-I rows 7-8); joint H0-scaling (D rows 9-10)</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>numerical a0/xi values I (row 11); xi_canonical-from-H0 OPEN (the paper's single open item)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>current — verdict A-&gt;position/M3 under P-Substrate-Cosmology-Unified; ONLY TWO projections (Staleness #2)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>Baryogenesis</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Tsirelson bound 2*sqrt(2)</t>
+          <t>First-arrival chirality chi* (which template = matter)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2091,7 +2111,7 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>I — 'not derived from first principles... INHERITED' (preamble 1)</t>
+          <t>IC-INHERITED, framework-neutral; native Z2 relocated from postulate to IC, not derived</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2104,17 +2124,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>Cos-01/05/06</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Bell &lt; Tsirelson &lt; NS nesting; PR-box exclusion</t>
+          <t>Uniform-Psi realizability (the saturation IC)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2123,92 +2143,80 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I (form composition)</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>entirely conditional on P-V5-Hilbert-Constraint</t>
+          <t>IC-INHERITED, framework-neutral: cyclic-CCC OR R3 single-aeon (choice 'outside scope')</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>current — inherits a Soler residual (see Status/staleness)</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>Cos-03/04</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>E-1 factorizable Psi^AB = Psi^A x Psi^B &amp; the tensor-product structure</t>
+          <t>Omega_c h^2~0.12 (CMB cold-dark-matter component, ~5x baryons)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>P-Bipartite-Mapping — 'definitional commitment, not a separate derivation'</t>
+          <t>INHERITED as a LCDM-CDM proxy inside CAMB/CLASS — the standing clusters/CMB debt (see ../dark-sector/)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current — the #5b debt (distinct from #5c Gaussianity)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>all Cos</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>V5-bilocal has Schmidt rank&gt;1 generically</t>
+          <t>H0 value</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>P-V5-Schmidt-Generic — derivability from V5 envelope alone is OPEN</t>
+          <t>INHERITED (a single substrate parameter; substrate derivation open)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2221,17 +2229,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>SCBU</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Monogamy budget cap; measure saturates the budget</t>
+          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2243,42 +2251,50 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>P-V5-Budget, P-Measure-Saturation</t>
+          <t>P-Substrate-Cosmology-Unified (the single new postulate; audit row 6)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>current — the folder's one substantive paper-specific postulate</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>Baryogenesis</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ED sits at Tsirelson; PR-boxes excluded</t>
+          <t>Matter &amp; antimatter follow identical V1 geodesics; no large antimatter domains</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>F2/F4: antihydrogen falls at a different rate (ALPHA-g 2023 consistent); antimatter domains / annihilation signatures</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>P-V5-Hilbert-Constraint</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2291,73 +2307,77 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>Cos-05</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>E-2 non-factorizability is IRREDUCIBLE</t>
+          <t>Dark energy strictly w=-1, no time-variation (vs quintessence/phantom)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>F1/F4: clean phantom w&lt;-1 over wide z, or w-dot != 0, or Lambda-dot != 0. Distinctive w=-1 null; ties 22-Ways w=-1</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;assertion — 'does not supply an explicit irreducibility proof' (round-5: was D, now A)</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>current — the arc's load-bearing soft spot</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-28</t>
-        </is>
-      </c>
+          <t>current — a real distinctive null; ties to 22-Ways w=-1</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>071</t>
+          <t>Cos-06</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ER=EPR-class echo</t>
+          <t>Route-A4 normalization: A_s and r jointly consistent with H_infl ~ Theta^{1/2}</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>F1/F2: A_s/r inconsistent with Route-A4 H_infl. CHANNEL-SPECIFIC, NOT a test of slow-roll/inflation</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position — 'does NOT derive ER=EPR constructively'; rests on P-V5-Shared-EntanglementGravity</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — CHANNEL-SPECIFIC, NOT a test of inflation itself</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2365,34 +2385,38 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>072</t>
+          <t>DF2/DF4</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Entanglement = unresolved individuation regime (not action-at-a-distance)</t>
+          <t>Group-embedded low-accel galaxies show a KNEE-like suppression sharper than MOND-EFE; void UDGs full enhancement</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Preds 1-4: environmental independence (LCDM) or smooth MOND-EFE roll-off; knee sharper than MOND (Pred-4 uniquely ED, below current precision)</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position — interpretive framing; does not modify QM predictions</t>
+          <t>(see Falsifier); suppression function uncalculated (Open)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — a real ED-vs-MOND discriminator</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2400,65 +2424,73 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>Baryogenesis</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Bipartite architecture as one phenomenon</t>
+          <t>P-BinaryAdmission</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position — 'does not override or strengthen constituent verdicts'</t>
+          <t>WITHDRAWN 2026-05-17 — 'binary chirality' declared a projection artifact; replaced by R4 single-template + first-arrival IC. Earlier M2 archived in event-density; Memo_ED_BinaryChirality (R1/R2/R3) rendered moot</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>current (consolidation)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>von Neumann E-6 (duplicate)</t>
+          <t>Twistor-analog substrate integral; Big-Ring/Grand-Arc scale; cyclic vs single-aeon termination</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Superseded</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>OPEN (three named; rows 14,15,17)</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SUPERSEDED by 068 (merged 2026-07-05); kept for provenance</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2466,17 +2498,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>Cos-01/05</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>derivability of P-V5-Schmidt-Generic</t>
+          <t>Route A (substrate-derived l_V5(H0) -&gt; quantitative Lambda, N~60, H)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2488,7 +2520,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN — the single load-bearing OPEN in each; 'highest-leverage open derivation in the program'</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2501,17 +2533,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>Cos-02/03/04/06</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>O-vN-1: derive P-Additivity from P04 (quantitative)</t>
+          <t>Non-load-bearing inherited puzzles: 7Li, Hubble tension, S8, ~60 e-folds / termination</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2523,7 +2555,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN, non-load-bearing — inherited standard-cosmology puzzles</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2536,17 +2568,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Cosmology</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>Cos-03/04</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>O-vN-2: derive P-Maximality from P11</t>
+          <t>CMB/clusters decoupled dark component has NO native ED mechanism</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2558,18 +2590,1159 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>OPEN -&gt; #5b. Mimetic-DM ruled out 3 ways; UDM-at-recombination ruled out (crowding c/c_max~1e-114); horizon-boost baryon-coupled (wrong type); only working option = added AeST-class field. 'Native and open, not a bolt-on'</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>DF2/DF4</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Suppression function (ED analogue of MOND's nu) from primitives</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — order-of-magnitude only; exact knee shape uncalculated</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Gaussianity / CMB observed-layer debt</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>OPEN (#5c) — substrate deposit field measured non-Gaussian below ~32 cells; reproducing known CMB objects does not pay it. DISTINCT from the #5b dark-matter debt</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SCBU</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>xi_canonical substrate-derivation from H0 (analogous to a0)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — the paper's single open item; would upgrade M3-&gt;M2</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>CCC's six structural elements &lt;-&gt; ED substrate content (X&lt;-&gt;SCBU; twistor&lt;-&gt;V5 memory; next-aeon&lt;-&gt;P12 re-entry; etc.)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>M3 form-IDENTIFIED + value-INHERITED; delta T/T, eta^G, 4piG all I; mix of A-&gt;position + D-via-I rows. 'Does not commit ED to cyclic cosmology'</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Contrast-zero state unique ==&gt; CCC crossover GLUING is an identity, not a postulated match</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position, conditional on the contrast ontology (Facts paper) — grounds CCC's assumption, not a substrate derivation</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Planck-mass remnants dissolve at X (Scenario-C cutoff = two-chain V5 handshake; boundary emptying removes the partner)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>faithful substrate-graph confirmation 'precluded on existing tooling' (in-queue)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Cos-02</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>BBN = freeze-out competition Gamma_nuc vs substrate-H(t); Y_p~0.247</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Inherited / Consilience</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>H(t) via continuum-Friedmann (D-via-I); freeze-out sequence D-via-I</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Y_p,D/H,3He,7Li, nuclear physics, eta_b I from standard BBN codes</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>current — Consilience (M3)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Cos-03</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>CMB acoustic peaks = angular projection of baryon-photon oscillator; l_n~n·pi·D_A/r_s</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Inherited / Consilience</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>r_s,D_A,peaks,baryon-loading,Silk D-via-I via continuum-Friedmann</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>peak positions/heights/TE/EE I from CAMB/CLASS; n_s, Omega_b h^2 IC-inherited</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>current — Consilience (M3)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Cos-04</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Linear structure = growth of primordial perturbations P(k,a)=D^2 T^2 P_init</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Inherited / Consilience</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>D(a),T(k),k_eq,BAO r_s D-via-I</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>sigma_8,P(k),Omega_m h^2 I; §3.5: 'ED supplies no late-LDE suppression BEYOND LCDM'</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>current — Consilience (M3)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Cos-06</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Inflationary fluctuation spectrum = sub-leading O(eps) perturbations on Cos-01 saturation</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Inherited / Consilience</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>P_zeta,P_T,n_s-1=-6eps+2eta,r=16eps D-via-I via standard slow-roll</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>A_s~2.1e-9,n_s~0.965,r&lt;0.06 I from Planck+BICEP</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>current — Consilience (M3); F1 falsifier is Route-A4-specific, not a test of slow-roll</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Schmidt rank&gt;1 =&gt; non-factorizable</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>D (standard SVD applied)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-V5-Schmidt-Generic</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>current — strengthens 063 only under that postulate</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Monogamy (CKW-form inequality)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>form D (form-forced) from V5 finite budget + P04 additivity</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>No-signaling p(a|x,y)=p(a|x), over-determined by 3 locks</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Lock L1 (marginal independence) = D-via-I from tensor-product + POVM completeness</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>L2 rests on P-Substrate-Causality; L3 = Paper_073; '3-locks =&gt; over-determination' is A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>current — cleanest paper in arc; Bell-Tsirelson explicitly OPEN here (row 11)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>von Neumann entropy form S = -Tr rho log rho</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (Shannon-Khinchin + Khinchin uniqueness)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-Continuity + P-Additivity + P-Maximality; normalization inherited</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>current — two substrate-derivations open</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>E-2 bilocal cross-chain term Delta_KL exists</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>D conditional on V5 (Paper_090)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>The Schmidt decomposition form itself</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>I — SVD is standard math (round-7 relabel: was D-cond-SVD, now I)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>k_B / log-base normalization; concrete entropy values</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Tsirelson bound 2*sqrt(2)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>I — 'not derived from first principles... INHERITED' (preamble 1)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Bell &lt; Tsirelson &lt; NS nesting; PR-box exclusion</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (form composition)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>entirely conditional on P-V5-Hilbert-Constraint</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>current — inherits a Soler residual (see Status/staleness)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>E-1 factorizable Psi^AB = Psi^A x Psi^B &amp; the tensor-product structure</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>P-Bipartite-Mapping — 'definitional commitment, not a separate derivation'</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>V5-bilocal has Schmidt rank&gt;1 generically</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>P-V5-Schmidt-Generic — derivability from V5 envelope alone is OPEN</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Monogamy budget cap; measure saturates the budget</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>P-V5-Budget, P-Measure-Saturation</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>ED sits at Tsirelson; PR-boxes excluded</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>P-V5-Hilbert-Constraint</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>E-2 non-factorizability is IRREDUCIBLE</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;assertion — 'does not supply an explicit irreducibility proof' (round-5: was D, now A)</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>current — the arc's load-bearing soft spot</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>071</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>ER=EPR-class echo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position — 'does NOT derive ER=EPR constructively'; rests on P-V5-Shared-EntanglementGravity</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement = unresolved individuation regime (not action-at-a-distance)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position — interpretive framing; does not modify QM predictions</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Bipartite architecture as one phenomenon</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position — 'does not override or strengthen constituent verdicts'</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>current (consolidation)</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>067</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>von Neumann E-6 (duplicate)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by 068 (merged 2026-07-05); kept for provenance</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>derivability of P-V5-Schmidt-Generic</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>O-vN-1: derive P-Additivity from P04 (quantitative)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>O-vN-2: derive P-Maximality from P11</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
           <t>OPEN — structurally blocked; ED has no substrate-level temperature</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I56"/>
+  <autoFilter ref="A1:I87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2094,29 +2094,33 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Baryogenesis</t>
+          <t>Cos-02</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>First-arrival chirality chi* (which template = matter)</t>
+          <t>BBN = freeze-out competition Gamma_nuc vs substrate-H(t); Y_p~0.247</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Inherited / Consilience</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>H(t) via continuum-Friedmann (D-via-I); freeze-out sequence D-via-I</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>IC-INHERITED, framework-neutral; native Z2 relocated from postulate to IC, not derived</t>
+          <t>Y_p,D/H,3He,7Li, nuclear physics, eta_b I from standard BBN codes</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — Consilience (M3)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2129,29 +2133,33 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Cos-01/05/06</t>
+          <t>Cos-03</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Uniform-Psi realizability (the saturation IC)</t>
+          <t>CMB acoustic peaks = angular projection of baryon-photon oscillator; l_n~n·pi·D_A/r_s</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Inherited / Consilience</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>r_s,D_A,peaks,baryon-loading,Silk D-via-I via continuum-Friedmann</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>IC-INHERITED, framework-neutral: cyclic-CCC OR R3 single-aeon (choice 'outside scope')</t>
+          <t>peak positions/heights/TE/EE I from CAMB/CLASS; n_s, Omega_b h^2 IC-inherited</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — Consilience (M3)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2164,29 +2172,33 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cos-03/04</t>
+          <t>Cos-04</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Omega_c h^2~0.12 (CMB cold-dark-matter component, ~5x baryons)</t>
+          <t>Linear structure = growth of primordial perturbations P(k,a)=D^2 T^2 P_init</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Inherited / Consilience</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>D(a),T(k),k_eq,BAO r_s D-via-I</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>INHERITED as a LCDM-CDM proxy inside CAMB/CLASS — the standing clusters/CMB debt (see ../dark-sector/)</t>
+          <t>sigma_8,P(k),Omega_m h^2 I; §3.5: 'ED supplies no late-LDE suppression BEYOND LCDM'</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>current — the #5b debt (distinct from #5c Gaussianity)</t>
+          <t>current — Consilience (M3)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2199,29 +2211,33 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>all Cos</t>
+          <t>Cos-06</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>H0 value</t>
+          <t>Inflationary fluctuation spectrum = sub-leading O(eps) perturbations on Cos-01 saturation</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Inherited / Consilience</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>P_zeta,P_T,n_s-1=-6eps+2eta,r=16eps D-via-I via standard slow-roll</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>INHERITED (a single substrate parameter; substrate derivation open)</t>
+          <t>A_s~2.1e-9,n_s~0.965,r&lt;0.06 I from Planck+BICEP</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — Consilience (M3); F1 falsifier is Route-A4-specific, not a test of slow-roll</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2234,36 +2250,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SCBU</t>
+          <t>Baryogenesis</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin</t>
+          <t>First-arrival chirality chi* (which template = matter)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>P-Substrate-Cosmology-Unified (the single new postulate; audit row 6)</t>
+          <t>IC-INHERITED, framework-neutral; native Z2 relocated from postulate to IC, not derived</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>current — the folder's one substantive paper-specific postulate</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2273,28 +2285,24 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Baryogenesis</t>
+          <t>Cos-01/05/06</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Matter &amp; antimatter follow identical V1 geodesics; no large antimatter domains</t>
+          <t>Uniform-Psi realizability (the saturation IC)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>F2/F4: antihydrogen falls at a different rate (ALPHA-g 2023 consistent); antimatter domains / annihilation signatures</t>
-        </is>
-      </c>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier)</t>
+          <t>IC-INHERITED, framework-neutral: cyclic-CCC OR R3 single-aeon (choice 'outside scope')</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2312,33 +2320,29 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Cos-05</t>
+          <t>Cos-03/04</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Dark energy strictly w=-1, no time-variation (vs quintessence/phantom)</t>
+          <t>Omega_c h^2~0.12 (CMB cold-dark-matter component, ~5x baryons)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>F1/F4: clean phantom w&lt;-1 over wide z, or w-dot != 0, or Lambda-dot != 0. Distinctive w=-1 null; ties 22-Ways w=-1</t>
-        </is>
-      </c>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier)</t>
+          <t>INHERITED as a LCDM-CDM proxy inside CAMB/CLASS — the standing clusters/CMB debt (see ../dark-sector/)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>current — a real distinctive null; ties to 22-Ways w=-1</t>
+          <t>current — the #5b debt (distinct from #5c Gaussianity)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2351,33 +2355,29 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cos-06</t>
+          <t>all Cos</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Route-A4 normalization: A_s and r jointly consistent with H_infl ~ Theta^{1/2}</t>
+          <t>H0 value</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>F1/F2: A_s/r inconsistent with Route-A4 H_infl. CHANNEL-SPECIFIC, NOT a test of slow-roll/inflation</t>
-        </is>
-      </c>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier)</t>
+          <t>INHERITED (a single substrate parameter; substrate derivation open)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>current — CHANNEL-SPECIFIC, NOT a test of inflation itself</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2390,36 +2390,36 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>DF2/DF4</t>
+          <t>SCBU</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Group-embedded low-accel galaxies show a KNEE-like suppression sharper than MOND-EFE; void UDGs full enhancement</t>
+          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Preds 1-4: environmental independence (LCDM) or smooth MOND-EFE roll-off; knee sharper than MOND (Pred-4 uniquely ED, below current precision)</t>
-        </is>
-      </c>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier); suppression function uncalculated (Open)</t>
+          <t>P-Substrate-Cosmology-Unified (the single new postulate; audit row 6)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>current — a real ED-vs-MOND discriminator</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>current — the folder's one substantive paper-specific postulate</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2434,31 +2434,31 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>P-BinaryAdmission</t>
+          <t>Matter &amp; antimatter follow identical V1 geodesics; no large antimatter domains</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>F2/F4: antihydrogen falls at a different rate (ALPHA-g 2023 consistent); antimatter domains / annihilation signatures</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>WITHDRAWN 2026-05-17 — 'binary chirality' declared a projection artifact; replaced by R4 single-template + first-arrival IC. Earlier M2 archived in event-density; Memo_ED_BinaryChirality (R1/R2/R3) rendered moot</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>superseded</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2468,29 +2468,33 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>Cos-05</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Twistor-analog substrate integral; Big-Ring/Grand-Arc scale; cyclic vs single-aeon termination</t>
+          <t>Dark energy strictly w=-1, no time-variation (vs quintessence/phantom)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>F1/F4: clean phantom w&lt;-1 over wide z, or w-dot != 0, or Lambda-dot != 0. Distinctive w=-1 null; ties 22-Ways w=-1</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>OPEN (three named; rows 14,15,17)</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current — a real distinctive null; ties to 22-Ways w=-1</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2503,29 +2507,33 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cos-01/05</t>
+          <t>Cos-06</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Route A (substrate-derived l_V5(H0) -&gt; quantitative Lambda, N~60, H)</t>
+          <t>Route-A4 normalization: A_s and r jointly consistent with H_infl ~ Theta^{1/2}</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>F1/F2: A_s/r inconsistent with Route-A4 H_infl. CHANNEL-SPECIFIC, NOT a test of slow-roll/inflation</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>OPEN — the single load-bearing OPEN in each; 'highest-leverage open derivation in the program'</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current — CHANNEL-SPECIFIC, NOT a test of inflation itself</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2538,29 +2546,33 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Cos-02/03/04/06</t>
+          <t>DF2/DF4</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Non-load-bearing inherited puzzles: 7Li, Hubble tension, S8, ~60 e-folds / termination</t>
+          <t>Group-embedded low-accel galaxies show a KNEE-like suppression sharper than MOND-EFE; void UDGs full enhancement</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Preds 1-4: environmental independence (LCDM) or smooth MOND-EFE roll-off; knee sharper than MOND (Pred-4 uniquely ED, below current precision)</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>OPEN, non-load-bearing — inherited standard-cosmology puzzles</t>
+          <t>(see Falsifier); suppression function uncalculated (Open)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current — a real ED-vs-MOND discriminator</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2573,29 +2585,29 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Cos-03/04</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>CMB/clusters decoupled dark component has NO native ED mechanism</t>
+          <t>CCC's six structural elements &lt;-&gt; ED substrate content (X&lt;-&gt;SCBU; twistor&lt;-&gt;V5 memory; next-aeon&lt;-&gt;P12 re-entry; etc.)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>OPEN -&gt; #5b. Mimetic-DM ruled out 3 ways; UDM-at-recombination ruled out (crowding c/c_max~1e-114); horizon-boost baryon-coupled (wrong type); only working option = added AeST-class field. 'Native and open, not a bolt-on'</t>
+          <t>M3 form-IDENTIFIED + value-INHERITED; delta T/T, eta^G, 4piG all I; mix of A-&gt;position + D-via-I rows. 'Does not commit ED to cyclic cosmology'</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2608,29 +2620,29 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>DF2/DF4</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Suppression function (ED analogue of MOND's nu) from primitives</t>
+          <t>Contrast-zero state unique ==&gt; CCC crossover GLUING is an identity, not a postulated match</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>OPEN — order-of-magnitude only; exact knee shape uncalculated</t>
+          <t>A-&gt;position, conditional on the contrast ontology (Facts paper) — grounds CCC's assumption, not a substrate derivation</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -2643,29 +2655,33 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>README</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Gaussianity / CMB observed-layer debt</t>
+          <t>Planck-mass remnants dissolve at X (Scenario-C cutoff = two-chain V5 handshake; boundary emptying removes the partner)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Identification</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>OPEN (#5c) — substrate deposit field measured non-Gaussian below ~32 cells; reproducing known CMB objects does not pay it. DISTINCT from the #5b dark-matter debt</t>
+          <t>faithful substrate-graph confirmation 'precluded on existing tooling' (in-queue)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -2678,32 +2694,36 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SCBU</t>
+          <t>Baryogenesis</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>xi_canonical substrate-derivation from H0 (analogous to a0)</t>
+          <t>P-BinaryAdmission</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>OPEN — the paper's single open item; would upgrade M3-&gt;M2</t>
+          <t>WITHDRAWN 2026-05-17 — 'binary chirality' declared a projection artifact; replaced by R4 single-template + first-arrival IC. Earlier M2 archived in event-density; Memo_ED_BinaryChirality (R1/R2/R3) rendered moot</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2718,24 +2738,24 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CCC's six structural elements &lt;-&gt; ED substrate content (X&lt;-&gt;SCBU; twistor&lt;-&gt;V5 memory; next-aeon&lt;-&gt;P12 re-entry; etc.)</t>
+          <t>Twistor-analog substrate integral; Big-Ring/Grand-Arc scale; cyclic vs single-aeon termination</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>M3 form-IDENTIFIED + value-INHERITED; delta T/T, eta^G, 4piG all I; mix of A-&gt;position + D-via-I rows. 'Does not commit ED to cyclic cosmology'</t>
+          <t>OPEN (three named; rows 14,15,17)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -2748,29 +2768,29 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>Cos-01/05</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Contrast-zero state unique ==&gt; CCC crossover GLUING is an identity, not a postulated match</t>
+          <t>Route A (substrate-derived l_V5(H0) -&gt; quantitative Lambda, N~60, H)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position, conditional on the contrast ontology (Facts paper) — grounds CCC's assumption, not a substrate derivation</t>
+          <t>OPEN — the single load-bearing OPEN in each; 'highest-leverage open derivation in the program'</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -2783,33 +2803,29 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>Cos-02/03/04/06</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Planck-mass remnants dissolve at X (Scenario-C cutoff = two-chain V5 handshake; boundary emptying removes the partner)</t>
+          <t>Non-load-bearing inherited puzzles: 7Li, Hubble tension, S8, ~60 e-folds / termination</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Identification</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>D-via-I</t>
-        </is>
-      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>faithful substrate-graph confirmation 'precluded on existing tooling' (in-queue)</t>
+          <t>OPEN, non-load-bearing — inherited standard-cosmology puzzles</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -2822,33 +2838,29 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Cos-02</t>
+          <t>Cos-03/04</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>BBN = freeze-out competition Gamma_nuc vs substrate-H(t); Y_p~0.247</t>
+          <t>CMB/clusters decoupled dark component has NO native ED mechanism</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Inherited / Consilience</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>H(t) via continuum-Friedmann (D-via-I); freeze-out sequence D-via-I</t>
-        </is>
-      </c>
+      <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Y_p,D/H,3He,7Li, nuclear physics, eta_b I from standard BBN codes</t>
+          <t>OPEN -&gt; #5b. Mimetic-DM ruled out 3 ways; UDM-at-recombination ruled out (crowding c/c_max~1e-114); horizon-boost baryon-coupled (wrong type); only working option = added AeST-class field. 'Native and open, not a bolt-on'</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>current — Consilience (M3)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -2861,33 +2873,29 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Cos-03</t>
+          <t>DF2/DF4</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CMB acoustic peaks = angular projection of baryon-photon oscillator; l_n~n·pi·D_A/r_s</t>
+          <t>Suppression function (ED analogue of MOND's nu) from primitives</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Inherited / Consilience</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>r_s,D_A,peaks,baryon-loading,Silk D-via-I via continuum-Friedmann</t>
-        </is>
-      </c>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>peak positions/heights/TE/EE I from CAMB/CLASS; n_s, Omega_b h^2 IC-inherited</t>
+          <t>OPEN — order-of-magnitude only; exact knee shape uncalculated</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>current — Consilience (M3)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -2900,33 +2908,29 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Cos-04</t>
+          <t>README</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Linear structure = growth of primordial perturbations P(k,a)=D^2 T^2 P_init</t>
+          <t>Gaussianity / CMB observed-layer debt</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Inherited / Consilience</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>D(a),T(k),k_eq,BAO r_s D-via-I</t>
-        </is>
-      </c>
+      <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>sigma_8,P(k),Omega_m h^2 I; §3.5: 'ED supplies no late-LDE suppression BEYOND LCDM'</t>
+          <t>OPEN (#5c) — substrate deposit field measured non-Gaussian below ~32 cells; reproducing known CMB objects does not pay it. DISTINCT from the #5b dark-matter debt</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>current — Consilience (M3)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -2939,33 +2943,29 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Cos-06</t>
+          <t>SCBU</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Inflationary fluctuation spectrum = sub-leading O(eps) perturbations on Cos-01 saturation</t>
+          <t>xi_canonical substrate-derivation from H0 (analogous to a0)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Inherited / Consilience</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>P_zeta,P_T,n_s-1=-6eps+2eta,r=16eps D-via-I via standard slow-roll</t>
-        </is>
-      </c>
+      <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>A_s~2.1e-9,n_s~0.965,r&lt;0.06 I from Planck+BICEP</t>
+          <t>OPEN — the paper's single open item; would upgrade M3-&gt;M2</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>current — Consilience (M3); F1 falsifier is Route-A4-specific, not a test of slow-roll</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -2973,191 +2973,203 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>(KM-I/027-034)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Schmidt rank&gt;1 =&gt; non-factorizable</t>
+          <t>Galactic dynamics from MOND/horizon, no dark-matter particle</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>D (standard SVD applied)</t>
-        </is>
-      </c>
+      <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-V5-Schmidt-Generic</t>
+          <t>standing prior result; the sector's strongest, SEPARATE piece (cited not re-derived)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>current — strengthens 063 only under that postulate</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29 (read in full)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>031</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Monogamy (CKW-form inequality)</t>
+          <t>Baryonic Tully-Fisher slope-4 + near-zero scatter</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>form D (form-forced) from V5 finite budget + P04 additivity</t>
+          <t>exact consequence of the combination rule</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
+          <t>MOND-SHARED: discriminates ED+MOND from LCDM, NOT ED from MOND; the ED-distinctive part is only the a0 normalization</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>current — honest distinction (§3.2)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>No-signaling p(a|x,y)=p(a|x), over-determined by 3 locks</t>
+          <t>Cluster missing-mass shortfall filled by the relic</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Lock L1 (marginal independence) = D-via-I from tensor-product + POVM completeness</t>
+          <t>real collisionless matter clustering at cluster scale</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>L2 rests on P-Substrate-Causality; L3 = Paper_073; '3-locks =&gt; over-determination' is A-&gt;position</t>
+          <t>the warm-keV window keeps it diffuse in galaxies, clumped at clusters — narrow, the live risk</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>current — cleanest paper in arc; Bell-Tsirelson explicitly OPEN here (row 11)</t>
+          <t>current — structural</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
+          <t>yes 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>QuadraticStrain/030</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>von Neumann entropy form S = -Tr rho log rho</t>
+          <t>MOND = the off-diagonal HORIZON-INTERFERENCE cross-term; sqrt(a_N a0) forced</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>D-via-I (Shannon-Khinchin + Khinchin uniqueness)</t>
+          <t>P=sqrt(b)e^{ipi}, Str=|sum P|^2 splits diagonal (Newton) + off-diagonal (MOND)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-Continuity + P-Additivity + P-Maximality; normalization inherited</t>
+          <t>standing / structural</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>current — two substrate-derivations open</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>029</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>E-2 bilocal cross-chain term Delta_KL exists</t>
+          <t>a0 = cH0/(2pi), parameter-free ~10% match</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>D conditional on V5 (Paper_090)</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>2pi from azimuthal-Fourier normalization of the dipole projection</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>~10% POSTDICTION; a0 value inherited via H0</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>current</t>
@@ -3165,184 +3177,212 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
+          <t>yes 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>The Schmidt decomposition form itself</t>
+          <t>a0(z) = cH(z)/(2pi) EVOLUTION (flagship bet)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>F3: MOND scale shown CONSTANT with z refutes it. First data (MUSE-DARK III, A&amp;A 2026) instead EXCLUDE constant a0 at ~30sigma (evolution confirmed); a robustly-confirmed rate incompatible with ~H(z) refutes the EXACT bet (data run faster), not the evolution</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>unfudgeable SHAPE (horizon projection introduces no l_P; no free dimensionless number to bend the power)</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>I — SVD is standard math (round-7 relabel: was D-cond-SVD, now I)</t>
+          <t>evolution CONFIRMED ~30sigma (MUSE-DARK III, A&amp;A 2026), excludes constant a0 / kills constant-scale MOND; EXACT rate ~H(z) in MILD TENSION (data run faster, ~1-few sigma, one survey)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>current — FLAGSHIP: direction won, exact rate under tension; do NOT over-bank (Rubin/Euclid decide)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>k_B / log-base normalization; concrete entropy values</t>
+          <t>Relic rho ∝ a^-3 from the P11 commitment number</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>F5/F2: the relic's conserved commitment number shown NOT ED-native -&gt; the a^-3 headline collapses, relic loses its edge over a modified-gravity dial</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Noether current of the global U(1); div J = 0 IS P11 (commitment-irreversibility) =&gt; n·a^3=const</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>derived GIVEN the field content of §2; the volume memory a modified-gravity dial structurally lacks</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>current — the sector's one genuinely-new derived headline</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Tsirelson bound 2*sqrt(2)</t>
+          <t>Sector is TWO-COMPONENT, not one substance (L_self coarse-grains CANONICAL)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>cos kernel analytic =&gt; gradient expansion gives only analytic powers =&gt; canonical p~1.99 on the real V5 functional; no (grad theta)^3/2, no a0</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>I — 'not derived from first principles... INHERITED' (preamble 1)</t>
+          <t>derived + numerically confirmed; one open edge = non-perturbative/vortex sector (minor)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>current — RESOLVED 2026-07-19 (supersedes the open self-term + the retracted khronon-mode probe)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Bell &lt; Tsirelson &lt; NS nesting; PR-box exclusion</t>
+          <t>Pressureless-dust limit w~0 (fast-oscillating massive scalar)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D-via-I (form composition)</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>entirely conditional on P-V5-Hilbert-Constraint</t>
-        </is>
-      </c>
+          <t>&lt;p&gt; -&gt; 0 for a massive scalar with theta-dot ~ m_R</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>current — inherits a Soler residual (see Status/staleness)</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
+          <t>yes 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>E-1 factorizable Psi^AB = Psi^A x Psi^B &amp; the tensor-product structure</t>
+          <t>Committed NEUTRAL RELIC candidate for clusters/CMB</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>P-Bipartite-Mapping — 'definitional commitment, not a separate derivation'</t>
+          <t>form-complete / native — neutral-channel sibling of the baryons (Baryogenesis) + binding mass (Mass-Without-Mass) + channel/polarity (MS-II)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3352,36 +3392,36 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
+          <t>yes 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>V5-bilocal has Schmidt rank&gt;1 generically</t>
+          <t>Field content Phi=sqrt(rho/m_R)e^{i theta} = coarse-grained neutral-channel participation measure</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>P-V5-Schmidt-Generic — derivability from V5 envelope alone is OPEN</t>
+          <t>structural (standard condensate/Madelung form + corpus field content)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3389,34 +3429,38 @@
           <t>current</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Monogamy budget cap; measure saturates the budget</t>
+          <t>Khronometric kinetic form L_kin (time-along-u + spatial c_perp)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>P-V5-Budget, P-Measure-Saturation</t>
+          <t>structural — the two-speed split is the arrow's preferred frame, not chosen by hand</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3424,34 +3468,42 @@
           <t>current</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ED sits at Tsirelson; PR-boxes excluded</t>
+          <t>Relic is MASSIVE by V5 binding, cold-capable</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Native / V5-conditional</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>V5 finite-reach retarded attraction confines fronts into a sub-luminal bound composite</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>P-V5-Hilbert-Constraint</t>
+          <t>mechanism native but V5-CONDITIONAL (V5 = faithful structural addition, not shown primitive-forced); mass VALUE inherited</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3459,73 +3511,77 @@
           <t>current</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>E-2 non-factorizability is IRREDUCIBLE</t>
+          <t>Bullet Cluster offset (relic sails through, collisionless)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;assertion — 'does not supply an explicit irreducibility proof' (round-5: was D, now A)</t>
+          <t>INHERITED mechanism — the LCDM-class collisionless account is inherited, not re-derived; relic = native reason a collisionless component is present</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>current — the arc's load-bearing soft spot</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-28</t>
+          <t>yes 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>071</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ER=EPR-class echo</t>
+          <t>Relic mass m_R</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position — 'does NOT derive ER=EPR constructively'; rests on P-V5-Shared-EntanglementGravity</t>
+          <t>INHERITED (eta_B tier). Mechanism-preferred value is cold GeV-Planck — 6-26 OOM heavier than the needed warm window (the live risk)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3533,34 +3589,38 @@
           <t>current</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>072</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Entanglement = unresolved individuation regime (not action-at-a-distance)</t>
+          <t>Relic abundance Omega_c ~ 0.12</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position — interpretive framing; does not modify QM predictions</t>
+          <t>INHERITED (eta_B tier); the relic gives the value a native field-theoretic HOME, amount still inherited</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3568,181 +3628,1191 @@
           <t>current</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Bipartite architecture as one phenomenon</t>
+          <t>Dark matter is WARM (~0.2-0.7 keV), not a cold WIMP</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>F1: a cold heavy WIMP detection, or perfectly-cold DM, refutes the warm relic. LIVE RISK: mechanism prefers cold GeV-Planck (6-26 OOM too heavy)</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position — 'does not override or strengthen constituent verdicts'</t>
+          <t>(see Falsifier); consistency BOUND on free-streaming (~0.1-1 Mpc); keV = thermal-equivalent</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>current (consolidation)</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>current — directional prediction AND the sector's quantified live risk (mechanism prefers cold)</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>von Neumann E-6 (duplicate)</t>
+          <t>Galaxies contain NO dark-matter halo at all</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>F2: DM substance found INSIDE galaxies (halo, CDM cusps, scattered mass) refutes the horizon-only galactic account</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier)</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SUPERSEDED by 068 (merged 2026-07-05); kept for provenance</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>current — clean ED-vs-superfluid-DM discriminator</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>derivability of P-V5-Schmidt-Generic</t>
+          <t>DF2/DF4 show a SHARPER external-field knee than MOND's smooth roll-off</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>environmental independence (LCDM) or smooth MOND-EFE roll-off refutes; suppression function not derived (Open)</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>(see Falsifier); suppression function not derived (Open)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>current — ED-distinctive vs MOND</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>DarkSector</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>O-vN-1: derive P-Additivity from P04 (quantitative)</t>
+          <t>No gravitational slip beyond O(Phi); activity-dependent weak-lensing enhancement in disturbed systems</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prediction</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>metric-only coupling has no vector field to make a slip; Paper_038_6 PROVISIONAL</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>current — ED-distinctive lensing</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Entanglement</t>
+          <t>Dark-sector</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>068</t>
+          <t>RelicLagrangian</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>O-vN-2: derive P-Maximality from P11</t>
+          <t>L_self 'open superfluid self-term' + the khronon-mode one-substance probe</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
+          <t>RESOLVED / RETRACTED 2026-07-19 -&gt; L_self canonical (two-component). Supersedes the first-draft OPEN flag AND the retracted khronon-mode probe (wrong variable, missed the density response)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Dark-sector</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>DarkSector</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>CMB spectrum computed from ED</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>F6: a computed CMB spectrum from the relic action that misses the Planck peaks for EVERY mass in the warm window</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier F6) NOT DONE — the largest owed piece; well-specified AeST-style Boltzmann run, now gated only on the mass/abundance</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Dark-sector</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>DarkSector</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Galactic small-scale puzzles (missing-satellite, satellite-plane)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>OPEN / unaddressed — ED has engaged neither (horizon jurisdiction, no mechanism worked out)</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Dark-sector</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>DarkSector</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>DF2/DF4 suppression function</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — not derived, only order-of-magnitude estimated</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Dark-sector</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>RelicLagrangian</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Relic mass / free-streaming value</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — the live risk; mechanism gives cold GeV-Planck, needed warm ~keV (6-26 OOM gap). If forced cold, relic clumps in galaxies and the sector fails</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Dark-sector</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>RelicLagrangian</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Non-perturbative / vortex edge of L_self</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>OPEN (minor) — the gradient expansion covers only the perturbative kinetic sector; a defect contribution is the sole residue of the one-substance route</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Schmidt rank&gt;1 =&gt; non-factorizable</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>D (standard SVD applied)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-V5-Schmidt-Generic</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>current — strengthens 063 only under that postulate</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Monogamy (CKW-form inequality)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>form D (form-forced) from V5 finite budget + P04 additivity</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>No-signaling p(a|x,y)=p(a|x), over-determined by 3 locks</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Lock L1 (marginal independence) = D-via-I from tensor-product + POVM completeness</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>L2 rests on P-Substrate-Causality; L3 = Paper_073; '3-locks =&gt; over-determination' is A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>current — cleanest paper in arc; Bell-Tsirelson explicitly OPEN here (row 11)</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>von Neumann entropy form S = -Tr rho log rho</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (Shannon-Khinchin + Khinchin uniqueness)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-Continuity + P-Additivity + P-Maximality; normalization inherited</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>current — two substrate-derivations open</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>E-2 bilocal cross-chain term Delta_KL exists</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>D conditional on V5 (Paper_090)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>The Schmidt decomposition form itself</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>I — SVD is standard math (round-7 relabel: was D-cond-SVD, now I)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>k_B / log-base normalization; concrete entropy values</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Tsirelson bound 2*sqrt(2)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>I — 'not derived from first principles... INHERITED' (preamble 1)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Bell &lt; Tsirelson &lt; NS nesting; PR-box exclusion</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (form composition)</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>entirely conditional on P-V5-Hilbert-Constraint</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>current — inherits a Soler residual (see Status/staleness)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>E-1 factorizable Psi^AB = Psi^A x Psi^B &amp; the tensor-product structure</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>P-Bipartite-Mapping — 'definitional commitment, not a separate derivation'</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>V5-bilocal has Schmidt rank&gt;1 generically</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>P-V5-Schmidt-Generic — derivability from V5 envelope alone is OPEN</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Monogamy budget cap; measure saturates the budget</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>P-V5-Budget, P-Measure-Saturation</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>ED sits at Tsirelson; PR-boxes excluded</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>P-V5-Hilbert-Constraint</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>E-2 non-factorizability is IRREDUCIBLE</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;assertion — 'does not supply an explicit irreducibility proof' (round-5: was D, now A)</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>current — the arc's load-bearing soft spot</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>071</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>ER=EPR-class echo</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position — 'does NOT derive ER=EPR constructively'; rests on P-V5-Shared-EntanglementGravity</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement = unresolved individuation regime (not action-at-a-distance)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position — interpretive framing; does not modify QM predictions</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Bipartite architecture as one phenomenon</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position — 'does not override or strengthen constituent verdicts'</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>current (consolidation)</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>067</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>von Neumann E-6 (duplicate)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by 068 (merged 2026-07-05); kept for provenance</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>derivability of P-V5-Schmidt-Generic</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>O-vN-1: derive P-Additivity from P04 (quantitative)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>O-vN-2: derive P-Maximality from P11</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
           <t>OPEN — structurally blocked; ED has no substrate-level temperature</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I87"/>
+  <autoFilter ref="A1:I113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4811,8 +4811,1763 @@
       </c>
       <c r="I113" s="2" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Holographic bound N(R) &lt;= 4piR^2/l_ED^2 (area law as edge-count)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>channel-count on a closed 2-surface</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>P-Codim-1 + P-Sat postulates; l_ED value inherited</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Newton a_N = GM/R^2 from the cumulative-strain reading</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>holographic source-resolution; N(R) factors cancel =&gt; Phi=-GM/R</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>P-Potential-Reading (Model A); V1 1/R envelope inherited (DCGT)</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>032.5</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Free chains follow acoustic-metric geodesics</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>eikonal/stationary-phase =&gt; S=-mc·integral dtau =&gt; geodesic eq</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>FORCED-conditional on P-FreeChain + guardrails (035); eikonal-&gt;action step OPEN; M3</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>current — superseded-in-part by GR-III geodesic treatment (Staleness #6)</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>034/036</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Deep-MOND a=sqrt(a_N a0); flat-background AQUAL field eq</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>mu(x)-&gt;x + field eq + spherical geometry; AQUAL Lagrangian variational</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>FORM-FORCED given P-MOND-Interpolation / P-MOND-Field-Form; mu form inherited empirically</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>a0 continuum-limit invariant (does not RG-run)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>c invariant x H0 invariant</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>P-H0-Cosmological-Invariant postulate</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>GR-I</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Temporal lapse N^2~b -&gt; weak-field Einstein metric (Schwarzschild branch, not Nordstrom)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>front-null + commitment-rate law =&gt; N^2~b</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>D-cond on P-Commitment-Linear (alpha=1) — later FORCED in GR-III §4</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>GR-I</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Emergent g~1/b + factor-of-two light bending</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>n_opt~b^-1 = square of spatial index (sim 2.09 vs 2.00)</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>conditional on 13 primitives; sim uses imposed Newtonian-limit b-profile</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>GR-II</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Field-equation form G+Lambda·g = kappa·T</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Lovelock, given metric + conserved source + 2nd-order</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>forced IFF purely metric — the open condition, which §5 FAILS (ED is khronometric, not pure GR)</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>GR-II</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Matter conservation div T = 0 &lt;=&gt; geodesic motion</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>forced by P05 transport typing + P04 extensivity; exact for dust</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>pressure/anisotropic-stress need full rule</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>GR-II</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>ED gravity is KHRONOMETRIC (2 tensor + 1 khronon); gauge = foliation-preserving diffeos</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>arrow (P11/P13) in the law =&gt; preferred foliation =&gt; mode count 2+1</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>D-structural (not a completed linearized propagator)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>GR-II</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>c_T = c structurally (GW170817 as identity); universal (not differential) Lorentz violation</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>one substrate, one transport (P05), one cone; shared by all species</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>F-independent</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>GR-III</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>alpha=1 (P-Commitment-Linear) FORCED; Nordstrom excluded</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>P04 reserve monotone-draining (P11) =&gt; beta=0 =&gt; alpha=1</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>D-cond on a named band-accounting premise</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>GR-III</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Khronon scalar speed c_s = c</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>reserve sector dissipative (P11), not kinetic =&gt; no second cone</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>leading order; sub-leading reserve renormalization benign</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>GR-IV</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>alpha_2 = 0 EXACTLY</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>khronometric PPN numerator vanishes on the scalar-luminal surface once c_T=c, c_s=c — the SAME causal cone as GW170817's c_T=c (one fact, two faces)</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>literature-verified (Blas-Lim, Ramos-Barausse, Foster-Jacobson) + numerically checked</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>current — the keystone kill-switch, passed</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>GR-IV</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>alpha_1 = -4·lambda_local; commitment FORCED sparse =&gt; lambda_local&lt;&lt;1 (&gt;=70 orders safe)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>metric stiffness always-on (P02); khronon stiffness only where commitments fire (P11); dense commit = Zeno =&gt; no QM, and ED has a QM sector</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>prefactor O(1) tied to kappa/D=8piG</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>MetricFromGraph</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Reach law p=1/(d-1) =&gt; g~1/b in EXACTLY 3D</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>ball-cut exponent = d-1 (holographic surface count); 3D uniquely reproduces GR-I</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>derived conditional on the surface-count; metric is KINEMATIC/static-linear, nonlinear OPEN; exactly-3 is internal coherence, NOT a proof ED forces 3D</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Six ED-10 weak-field prerequisites fulfilled at form level</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>enumerates WF-1..6 with falsifiers</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>WF-3 conditional on the P14 placeholder; sufficiency for curvature = A-&gt;assertion</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>033</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Scalar-tensor acoustic-metric field eq (covariantization)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>opens Arc ED-10</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>three P-postulates; 'conditional-positive'; deep-MOND superluminality A-&gt;cost (re-tiered to 'feature' by KM line, Staleness #4)</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>038.5</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Lambda = V1 cosmological-scale integral over R_H; Lambda CONSTANT, w=-1 forced, = frozen saturation-floor</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>form-IDENTIFIED (V1 finite 2nd moment + curvature coupling + R_H domain); live-horizon Lambda =&gt; w=0/dead, so only the frozen floor accelerates</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>value inherited; M3 conditional on Route-A; RESIDUAL OPEN: force vs stipulate the frozen value (§3.5, updated 2026-07-16)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>KM-I</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>The khronon's deep field IS the MOND sector (unifies the two gravity programs)</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>promoting the acceleration term to W(A^2) =&gt; AQUAL in the metric potential; deep-IR embeds 030</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>single hinge = 'forced-given-030' (matches the derived Combination Rule, does not re-derive); interpolation a Cassini-constrained family</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>current — THE STANDING MOND RESULT; do not reinvent</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29 (corroborated via 030/QuadraticStrain checks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>KM-I</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Lensing tracks the MOND potential, no added vector; no new ghost; PPN-safe</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>metric-borne modification; unitary-gauge no time-derivatives</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>slip O(Phi)-suppressed</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>KM-II</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Orthogonality theorem: theta=0 in statics =&gt; the regulator family is invisible to every tested result</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>kinematics of static congruences</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>the cleanest result; sequesters the cosmology sector</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>KM-II</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Clustering dial = the soft spot (one dial sets degeneracy-cure + Cerenkov + clusters/CMB)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>class mechanisms are DIRECTIONS, not verifications; abundance = value-inherited IC</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>KM-II</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>One-Lambda thesis: W0 = -24·pi^2·Omega_Lambda ~ -162</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>shared SCBU boundary; scaling exact; sign passes (V1 density positive =&gt; Lambda&gt;0)</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (tier transported from 038.5, not upgraded); ab-initio integral OPEN with a numeric target</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>GR-III</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Dynamical rule b-dot=D·grad^2 b - kappa·rho: steady state grad^2 b~rho (0.999); r_s~M; emergent frozen b-&gt;0 horizon; area law S~A</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>fixed point of the two forced terms; horizon forms with nothing about a horizon in the rule</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1/4 coefficient inherited</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>GR-III</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Hawking scaling kappa=1/(2 r_s) ~ 1/r_h</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>vacuum solution + GR-I g00·grr=-1; corrects an earlier 'flat' measurement error</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>direct sim resolution-limited</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>QuadraticStrain</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Phase-coherence constructive sign supplied (P12-Coh rewards alignment)</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>build-verified 2D/3D; finite-reach not crystalline</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P12-Coh operationalization</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>G = c^3·l_P^2 / hbar</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>form-DERIVED, value-INHERITED (M3); l_ED=l_P is the empirical-matching choice, not a substrate derivation</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>a0 = cH0/(2pi)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>form-derived, ~10% parameter-free match; H0 INHERITED; 029's reading is STATIC ('tracks whichever H0') — no a0(z) (Staleness #1)</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>038.5</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Lambda magnitude rho_Lambda ~ 1.1e-52 m^-2</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>value-INHERITED; smallness = (H0/M_P)^2 via Friedmann, gated on Route-A</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>P14 Bilocal Strain Coupling (geometric-mean)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>postulated, non-unique (§8.4/8.9); later DISCHARGED by QuadraticStrain as the forced interference modulus</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>current — see QuadraticStrain (Staleness #8)</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Six acoustic-metric guardrails (C1-C6)</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>all six are P (postulates) with substrate-consistency justifications</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>QuadraticStrain</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>P-Quadratic-Strain (Model C)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>one postulate replacing P14 + 030's regime assumption</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>BTFR v^4 = GM_b a0, slope exactly 4, zero intrinsic scatter</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>slope != 4 or irreducible intrinsic scatter (data 3.95+-0.08, ~0.1 dex). MOND-SHARED: discriminates ED+MOND from LCDM; only the a0 normalization is ED-distinctive</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier)</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>current — slope-4 + tightness are MOND-SHARED; only the a0 normalization is ED-distinctive</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>a0(z) = cH(z)/(2pi) evolves factor-for-factor with H</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense)</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier); ONLY 031 §8.8 reflects the 2026 data</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>current — flagship; ~30sigma evolution confirmed, exact rate alpha=1 the open number (Staleness #1)</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>038.6</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Activity-dependent weak lensing ~ |grad mu|^2</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>activity-INDEPENDENT lensing refutes. PROVISIONAL — alpha_act, A(x), the |grad mu|^2-vs-feedback discriminator observable all OPEN</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier)</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>current — PROVISIONAL (alpha_act, A(x), the discriminator observable all OPEN)</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>GR-II</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Scalar (breathing) GW polarization at c</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>definitive absence of a scalar/breathing GW polarization excluding the khronon mode</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier)</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>GR-IV</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>alpha_1, alpha_2 preferred-frame (the keystone kill-switch)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>ANY nonzero alpha_2 kills it (alpha_2 = 0 EXACT, structural); alpha_1 &gt;~ 1e-5 kills it (alpha_1 &lt;~ 4e-93 safe). Passed favorably</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier)</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>current — passed favorably (alpha_2=0 exact, alpha_1 &gt;=70 orders safe)</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>OffsetVelocity/117</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Offset-velocity knee law: flat-knee-line-ceiling</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>LCDM velocity-independent scatter, or MOND-EFE smooth roll-off, refutes. Only the SHAPE is ingredient-robust; the knee location rests on a flagged nu~0.70 (3D O(3)) assumption</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier); only the SHAPE is ingredient-robust</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>current — knee location rests on a flagged nu~0.70 assumption</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>OneField</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>'One field, one scale, five roles' (arrow, Einstein sector, MOND, clustering dial, Lambda-scale)</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>capstone; carries a 2026-07-19 correction banner downgrading 'DM is not a particle' to a CANDIDATE + flagging the khronon-alone abundance gap (needs a real relic -&gt; dark-sector)</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>QuadraticStrain</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>MOND = interference cross-term: Newton=diagonal, MOND=off-diagonal of |sum P|^2</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>discharges P14 (geometric mean = forced interference modulus) + 030's regime assumption (horizon is a dipole not a monopole); STRUCTURAL, conditional on P-Quadratic-Strain; residual = constructive sign (measured tier)</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>038.5</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Whether Lambda frozen-floor value is FORCED or stipulated</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>OPEN (§3.5) — bootstrap knot; the driver is matter-dilution (Cos_05)</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>038.5/KM-II</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Ab-initio V1 boundary integral for Lambda (target W0=-24pi^2·Omega_L); Route-A closure</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — highest-leverage open derivation in the program</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>KM-I/KM-II</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Clusters + CMB not discharged; khronon-standalone ABUNDANCE GAP</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — now carried by a separate two-component warm relic (One-Field + 117 banners); see ../dark-sector/</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>MetricFromGraph</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Nonlinear / strong-field field equations; background-free construction</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — the nonlinear regime is the distinctive/falsifiable frontier (kinematic metric only so far)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I113"/>
+  <autoFilter ref="A1:I158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6566,8 +6566,1306 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Continuum gauge-covariant derivative D_mu=d_mu+iA_mu</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>DCGT coarse-graining + P-Polarity-Connection-Match</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>groups, couplings, local-gauge invariance all I</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>current — conditional on P-Polarity-Connection-Match (postulated)</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Lorentz covariance of the continuum free-scalar equation</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>from V1 Lorentz covariance (Paper_089) preserved by DCGT</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Continuum YM equations D_mu F=J (Euler-Lagrange)</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>standard variational step FROM the postulated action</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>action = P (P-YM-Action-Coarse-Graining); g_YM value I</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>current — EL step on a postulated action</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Spectral-gap FORM Delta ~ 1/l_* (Yang-Mills mass gap)</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>form FORCED given postulates; new content = substrate adaptation of Perron-Frobenius/Glimm-Jaffe to V1/V5</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>coeff INHERITED; continuum survival conditional on P-Profile-Rescaling (OPEN); numerical Delta OPEN</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>current — explicitly NOT a Clay proof</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Substrate quotient = physical-state space; BRST = coarse-grained quotient</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I: fiber-bundle quotient + DCGT</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>constructive Gribov resolution OPEN</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>current — under P-Gauge-Orbit-Non-Empty + P-Quotient-Hilbert</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Lindblad/GKSL master-equation form</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>FORM-FORCED as the Markovian limit of V5-modulated dynamics (D-via-I)</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>specific L_k, rates I; non-Markovian OPEN</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>current — no anomaly claim (consistent w/ Lindblad = line-gap, wrong type for anomaly)</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Gauge group U(N)=SU(N)xU(1) from channel multiplicity</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>non-abelian SU(N) forced by N indistinguishable channels + bandwidth conservation (P04) + invertibility unitarity</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>SM correspondence {1,2,3} and couplings inherited</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>current — THE one firm upgrade over T17's analogy</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>V1 QFT-arc propagator (Kallen-Lehmann retarded form)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I: KL machinery applied to P-V1-Spectral + P11 retardation</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>rho(m^2) values I; multi-point functions OPEN</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>current — Reference-adjacent</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>N1+GR1: V1 finite-width + 2-point function on a curved acoustic background</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I: QFCS + Hadamard machinery applied to V1</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>curvature corrections I; backreaction / Einstein eq OPEN</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>current — FORM-FORCED under P-Slow-Variation + P-Hadamard-Preservation</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Free scalar Klein-Gordon (box+m^2)phi=0 as the DCGT limit of V1</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>P-CONSTRUCTION matching the standard form (round-8 relabel: was D, now P) under P-Scalar-Match + P-Lorentz-Covariant-Continuum</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>mass values I; canonical quantization / interacting QFT NOT claimed</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>current — postulate-construction</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Non-abelian YM potential, field strength, YM equation</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>P-constructions matching standard forms under P-StructureConstants-Match</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>groups I; mass gap / OS NOT claimed here</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Substrate is a U(N) lattice gauge theory; escapes Nielsen-Ninomiya</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>P05-transport = U(N) link variable; relational graph (no Brillouin torus) + retarded arrow (non-hermitian) evade the two N-N premises</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>'P05 re-routes channels unitarily' is a structural reading, not a closed proof</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Spin-1/2 from relationality (tethered node carries SU(2)-&gt;SO(3) double cover)</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>orientation-entanglement / Dirac-belt reading</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Cl(3,1) + pi_1(SO(3))=Z_2 inherited (T2/T4)</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Parity violation is non-abelian: NO parity-violating abelian force</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>general gauge theory PERMITS chiral abelian U(1)s; ED forbids them. A measured parity-violating abelian (U(1)) force refutes it. Matches the low-energy world (EM abelian=vector, weak non-abelian=chiral)</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>V1 single-channel chirality-blind -&gt; abelian vector; V5 cross-channel chirality-sensitive -&gt; non-abelian can be chiral</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>WHICH force is chiral (weak assignment) OPEN/inherited</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>current — a falsifiable prediction</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Chirality gamma^5 = the arrow's 'screw'</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>handed-commitment twist as the chirality locus</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>evidence is a 1+1D TOY-lattice computation, NOT canonical V1; gamma^5 relocated to GLOBAL (=i g0 g1 g2 g3); 3 open bridges to a relativistic result</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>current — account; corrected inline (P-imprint retired: C native, P spontaneous+inherited)</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>{1,2,3} &lt;=&gt; internal amplitude dimension d=3 (Welch-bound); no stable SU(N&gt;=4)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>a stable/observed gauge sector requiring SU(N&gt;=4) — a 4th independently-stable channel family in the internal amplitude space — refutes the d=3 reduction</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>max mutually-orthogonal channels in C^d is N=d</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>WHY d=3 is itself OPEN</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>current — a falsifiable prediction</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Three spatial dimensions because the arrow must hold committed order</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>topological elimination (a link holds in 3D, frozen in 2D, unravels in 4D)</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>conditional on the OPEN premise that ED holds order by spatial linking</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>current — the topology half is Measured</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>V1 finite-width retarded vacuum kernel (QFT-arc presentation)</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>two-point/Wightman/propagator presentation of the canonical V1 (Paper_089); adds no new primitive</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>current — scaffolding for 014-023</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Linking held in 3D, erasable in 4D</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>linking_3d_vs_4d_probe: unlinking forces a collision (0.000) in 3D, slides free (0.600) in 4D</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>the ED-holds-order-by-linking premise still OPEN</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Retarded ('arrow') hopping produces net chirality signatures</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>1+1D toy: point-gap winding, skin effect, spectral flow — all zero in the Hermitian control</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>not yet Lorentz-covariantized to a gamma^5 coupling</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>current — toy; supports the §4.2 account only</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>015-019</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Empirical gauge groups SU(3)xSU(2)xU(1), couplings, masses, mixings</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED (value-layer matching) across the whole arc</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>015.5</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Integer-Chern quantization C_n in Z of photonic Hall drift</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>quantization INHERITED from standard Chern-class topology; ED supplies only the rule-type-bundle identification (form-IDENTIFIED, M3)</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>019/021/024</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>g_YM, mass-gap coefficient, Lindblad L_k &amp; rates</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED (empirical matching)</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>P-NonAbelian-Analogy (non-abelian gauge structure 'by analogy')</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;analogy; SUPERSEDED/upgraded to Derived by MS-II §2 (Staleness #2)</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>P-YM-Action-Coarse-Graining</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>the coarse-grained action = standard S_YM (the substantive declared content)</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>P-OS-Reflection-Positivity (OS3)</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>the one non-inheritable OS axiom (the rest of OS inherited)</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>P-Profile-Rescaling (YM continuum survival)</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>the Clay-hard wall; underived — the load-bearing OPEN gap for continuum survival</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Gribov ambiguity is a coarse-graining artifact (not constructively resolved)</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Yang-Mills arc closes at 'Clay-relevance / structural-positive level'</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>above structural analogy, below constructive proof; NOT a Clay-prize-eligible proof (preamble #1,#7)</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>019/020/021/023</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>YM continuum measure; OS3 derivation; mass-gap survival as a-&gt;0 (the 3 Clay-hard gaps)</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — 023 names all three and states the arc 'does not close' them</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>021/023</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Confinement, asymptotic freedom, glueball spectrum, numerical Delta</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>MS-I/MS-II</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Yang-Mills action (~F^2); electroweak/Higgs sector; EWSB; fermion masses</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>NOT derived — explicitly deferred to OPEN (archived-source check CLEAN: no four-band/dwell-mass reliance)</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>{1,2,3} uniqueness; weak-force specific chirality; anomaly cancellation; the linking premise</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — reduces to the T4 spinor gate #2b</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>MS-II</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Full channel-topology -&gt; representation spectrum; spinor construction</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — reduces to the T4 spinor gate #2b (highest-leverage open item in the program)</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I158"/>
+  <autoFilter ref="A1:I192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$220</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7864,8 +7864,1108 @@
       </c>
       <c r="I192" s="2" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Complex polar carrier P_K=sqrt(b_K)·e^{i pi_K}</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>carrier form from P01-P04 + P09 (audit = D); |P_K|^2=b_K algebraic</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>sqrt-convention + arg=pi_K = P; inner product = I (Paper #3)</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>current — convention-tagged</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Berry phase gamma_C = holonomy of the coarse-grained P05 connection</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (holonomy on Paper_016 connection)</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>numerical gamma_C inherited; non-abelian/off-diagonal OPEN</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Aharonov-Bohm phase from T17 bundle circulation</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (fiber-bundle holonomy)</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>e/hbar inherited; paper: 'ED does NOT newly predict AB'</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Bloch form psi_k=e^{ikx}u_k(x) from discrete translation symmetry</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (abelian rep theory)</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>band content inherited</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>012.7</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Galilean adjacency/propagation bandwidth-asymmetry</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>asymmetry FORCED by P03 (adjacency invariant) + P04 (propagation transforms)</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>full Galilean/Bargmann cohomology OPEN (P03 necessary, not sufficient); m inherited</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>current — M3, restricted scope</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Born rule f_K=|c_K|^2 as the participation-frequency limit</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>frequency limit f_K=b_K/sum b -&gt; Born (audit D)</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>rests on P-LinRate (P, load-bearing) + frequentist interp (A-&gt;assumption)</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded, NOT pure-M1 (README 'Derived' inflated)</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>003.5</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>P_K=sqrt(b_K)·e^{i pi_K} amplitude carrier, complex-valued forced</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>form FORCED by P04+P05+P09+interference (3 args)</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>b_K, pi_K values inherited</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>004.5</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Sesquilinear inner-product form &lt;P,Q&gt;=sum P_K* Q_K (discrete)</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>form M3-FORCED from P04+P09+composition</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Tsirelson bound 2sqrt2 INHERITED (Landau-Cirelson 1980); uses P_K=b_K e^{ipi} (|P|^2=b^2), inconsistent with 001/003.5 corrected sqrt(b) (Staleness #4)</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (form); Tsirelson Inherited</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>004.6</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Continuum inner-product int Psi* Phi dmu on L^2(M,dmu)</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>form-consistent under DCGT + P-ScaleSeparation</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>measure conventions inherited</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Projective measurement (projector Pi_K, collapse, Born prob)</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>post-state/completeness follow; Born prob D-conditional on P-LinRate</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>P-Commit-Projector-Match (P) load-bearing; rests on P-Channel-Orthogonality (from 004)</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded/Postulated</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>005.5</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Double-slit interference rho=|sum P_K|^2; which-path = V5 injection</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>M3 form-IDENTIFIED (zero pure-D rows)</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>fringe geom/lambda=h/p/visibility inherited; Theta_ED value + V5-injection-rate OPEN; Theta_ED 'P12 ED-threshold' mislabel corrected 2026-07-06</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (identification)</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Unitary evolution -&gt; Schrodinger i hbar d_t Psi = H Psi</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>norm-preserving =&gt; unitary; Stone =&gt; Hamiltonian form</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>P-Norm-Preservation (P) load-bearing; Stone+polarization = I; specific H inherited</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded (conditional)</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>006.5</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Schrodinger equation via Stone's theorem</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>load-bearing = the substrate identification (P11-&gt;norm-preservation, P13-&gt;time-translation)</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Schrodinger eqn itself = P (definitional, Paper_095 §2.3); Stone = I; hbar inherited</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>current — M2 (Intermediate Path C)</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>006.6</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Kinetic operator T=p^2/2m, the factor-2</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>factor-2 form-FORCED via the NR limit of Klein-Gordon</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>independent substrate-Galilean-Jacobian derivation of 1/2 = OPEN; V(x), m inherited</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>current — M3; 1/2-from-primitives Open</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>006.7</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Schrodinger emergence in the thin-participation limit</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>leading-order unitary form forced in-regime</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>V1-&gt;unitary coarse-graining OPEN (asserted via DCGT analogy)</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>current — M2, partly Open</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Hilbert space = Cauchy completion of the motif algebra</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>emergence D-conditional on P-Motif-Algebra (P) + Cauchy (I)</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>inner product = I; the I-&gt;D relabel needs both Gleason postulates (Staleness #1)</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>current — inner-product edge Open/SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Phase structure S^1/U(1) on rule-types</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>form-FORCED by P09+P10 + 3 postulates</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>2pi normalization inherited; O-Phase-1..4 open</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>008.5</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Phase-independence of bandwidth = U(1) gauge invariance</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>polar-decomp invariance lemma + identification with U(1) gauge</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>substrate derivation of U(1) gauge invariance from P09 alone OPEN; role of P11 OPEN</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (lemma + identification)</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>012.5</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Momentum operator p=-i hbar grad = translation generator</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>form-identified via Stone on the P03 translation group; CCR [x,p]=i hbar follows</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>P-MomentumIdentification declared (substrate derivation OPEN); hbar INHERITED</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>current — M3; hbar Inherited</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>012.6</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Heisenberg Dx·Dp &gt;= hbar/2</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>composition D-via-I</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>bound INHERITED (Robertson 1929 + Cauchy-Schwarz + CCR); hbar/2 inherited; P-FourBand declared, substrate-derivation OPEN</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>current — M3; four-band NOT the archived M-series (clean)</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>004.5</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Tsirelson bound 2sqrt2</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED (Landau-Cirelson 1980); a standing construction — NOT the separately-retracted 'Tsirelson reduction' V5 characterization</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>012.5/012.6/006.5/006.6</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>hbar throughout the operator sub-arc</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>value INHERITED (Paper_RQM_hbar)</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Gleason-Recon (sibling)</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Complex field C (from the Soler menu {R,C,H})</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>C SELECTED: P09 scalar phase rules out R; V5/063 composites rule out H</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>account-tier selection, not a from-scratch derivation</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Tensor-product composition Psi^AB=Psi^A x Psi^B</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>P-QMkin-Composition — 'not from P02+P03 alone... a paper-specific postulate' (preamble #2)</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>current — README 'Derived' inflated</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>P-RB-1 local rate of becoming; substrate-c constancy</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>'a commitment, not a set of derivations'; hbar (O-RB-1) and c-from-deeper (O-RB-2) OPEN</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>current — foundational commitment</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>011.5</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Four QM postulates unified under the participation measure</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>four postulates = 'four facets of one substrate structure' via distinct primitive routes</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis (M2); explicitly NOT a Hardy/CDP closed-proof; per-theorem closure OPEN</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Substrate Gleason: inner-product uniqueness</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>STALE framing: Paper_004 Update 2026-07-02 says 'P-Channel-Orthogonality fully open / three routes fail / blocking'. SUPERSEDED by the reconstruction (next row)</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>open (stale)</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>QM-kinematics</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Gleason-Recon (sibling)</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Orthogonality REDUCED; C selected; residual = Soler</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>channel-orthogonality REDUCED to channel-distinctness GIVEN the representation (operational distinguishability); C selected; covering law candidate-grounded; einselection primitive; Born non-contextuality resolved; equal-norm/angle discharged 2026-07-10</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>residual = Soler lattice technical rigor ONLY</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>current — 'reduced to the Soler residual': stronger than 004's blocking, weaker than a closed theorem</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I192"/>
+  <autoFilter ref="A1:I220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$238</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I220"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8964,8 +8964,730 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Cl(3,1) frame uniqueness up to similarity</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>unique irreducible 4-dim rep of Cl(3,1); all gamma-realizations similarity-equivalent (Pauli + Schur)</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>basis (Dirac/Weyl/Majorana) = choice of S, not value inheritance; conditional on Paper_017 signature</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>current — M1 (no numerical inheritance); conditional on 017, not primitives-alone</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Anyon prohibition in 3+1D</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>an anyon (continuous exchange phase eta=e^{i theta}) in a GENUINE 3+1D system — not an effective-2D FQH surface — refutes it. Matter-sector prohibition; general QFT permits anyons only in 2+1D</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>pi_1(config space)=S_n in d=3 =&gt; only 1-dim reps eta=±1 =&gt; anyons prohibited; anyons require d=2 (braid group B_n)</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>effective-2D FQH anyon phases empirical, not load-bearing</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>current — M1 pure dimension-comparison; the cleanest result; a distinctive matter-sector prohibition</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Spin-statistics eta=(-1)^{2s}</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>dichotomy FORM (only eta=±1, fermion/boson exhaustive) from P06+P09 exchange topology + pi_1(SO(3))=Z_2</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>specific spin assignments (e-=1/2, gamma=1) empirical; CPT/parity/T deferred</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (FORM-FORCED + VALUE-INHERITED)</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>106 (T4)</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Dirac equation (i gamma^mu d_mu - mc/hbar)Psi=0</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>structural mechanism identified: unique first-order Clifford factorization of KG on the Cl(3,1) bundle; §3.7 continuum limit COMPUTED + Wilson-term undoubling 16-&gt;1</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>explicit substrate-V1-&gt;Dirac closed proof OPEN; fully-covariant proof OPEN; graph-native SPINOR construction OPEN (canonical P07 supplies NO native channel topology); mass inherited</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>current — M2 (Intermediate Path C); THE #2b gate, genuinely OPEN; chirality NOT claimed derived (vector default, parity inherited). Row-15/§3.7 desync (Staleness #1)</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Klein-Gordon equation (box+m^2 c^2/hbar^2)Psi=0</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>substrate IDENTIFICATION of m as P04 rest-bandwidth; V1-kernel low-momentum-pole compatibility</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>KG form ITSELF is P-definitional/INHERITED from Paper_017 + std dispersion; V1-&gt;KG-propagator OPEN</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>current — M3, FORM-INHERITED (correctly reflects 017's round-8 D-&gt;P; no over-claim)</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Minimal-coupling KG + conserved 4-current</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>extension of KG to U(1) gauge; Noether current from U(1) phase-invariance</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>minimal-coupling form INHERITED (015/016); couplings empirical; V5 multi-channel substrate-graph derivation OPEN</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>current — M3, FORM-INHERITED</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Lorentz-representation taxonomy</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>finite SL(2,C) (j1,j2) taxonomy as substrate rule-type classification</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>which rule-type &lt;-&gt; which rep empirical; Wigner particle-state classification out of scope</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (form-IDENTIFIED + VALUE-INHERITED)</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Primitive-level UV finiteness</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>UV-finiteness from P04 finite bandwidth + P08 scale + V1/V5 finite-kernel form factors</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>cutoff omega_c=c/l_P value inherited; substrate-graph-&gt;power-counting derivation OPEN; renorm-reframe = A-&gt;position</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (form-IDENTIFIED + VALUE-INHERITED)</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>112 (T10)</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Lightlike worldlines for sigma=0 rule-types</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>null-geodesic propagation form-forced from massless dispersion (T5 at m=0) + std null-geodesic geometry</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>EXISTENCE of sigma=0 rule-types CONDITIONAL on Paper_114; substrate-c inherited; V1 at m=0 derivation OPEN</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 (structure forced, existence conditional)</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Mass structural form (Arc-M H1)</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>3 structural features form-forced: Lorentz-scalar, P04-bandwidth-anchored, statistics-class-mechanism</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>substrate-Higgs §3.3 + substrate-Yukawa §3.5 ASSERTED, NOT derived — OPEN; all mass values empirical; origin of 'statistics-class-mechanism' OPEN</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>current — M2 with OPEN flags; NOT built on archived four-band (dwell handle canonically licensed P02+P03+P07)</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>114 (GRH-D1)</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Existence of &gt;=1 massless Case-P gauge rule-type</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>existence form-forced CONDITIONAL on P-Gauge + T17 (015) + gauge-quotient (022)</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>specific gauge groups/couplings inherited; P-Gauge substrate derivation OPEN</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>current — M2 (conditional on the P-Gauge postulate); 112's sigma=0 existence depends on this</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Vacuum + particle dual Fock structure (sigma=0)</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>vacuum + 1-particle Fock decomposition from T10 + T8 + Wightman uniqueness</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>'no rest-frame =&gt; minimal dual' is heuristic, OPEN; mode-density normalization inherited</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>MR-R / MR-P conditional massless slot</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>two-branch mutually-exclusive massless slot (fermion-chiral MR-R / gauge MR-P); disjointness forced by T7</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>no-third-mechanism exhaustiveness OPEN; occupants empirical (neutrino MR-R); substrate-c inherited</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>110 (T8)</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Canonical (anti-)commutation [x,p]=i hbar</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>the commutator-vs-anticommutator DICHOTOMY forced by T1 (boson&lt;-&gt;commutator, fermion&lt;-&gt;anticommutator)</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>relation FORMS are P-definitional; hbar INHERITED; earlier 'structural origin of hbar' framing disowned as oversold</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>current — M3 FORM-INHERITED + VALUE-INHERITED</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>112 (hbar)</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>hbar origin = participation quantum per chain-step</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>dimensional structure (action=bandwidth x time) form-forced by P04+P05+P11; chain-step invariance (P03+P13) =&gt; hbar universal</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>value INHERITED; B_P04 has NO independent substrate definition — §3.3 CIRCULARITY disclaimer: hbar=int B_P04 ds is a relabeling, not a computation</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>current — M3, value-INHERITED with honest circularity</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>P-Gauge (paper-specific postulate)</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>gauge-class connection A_mu on rule-type bundles + gauge-quotient</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>substrate derivation from P05+P07+P09+P10 alone OPEN (F-Gauge would upgrade M2-&gt;M1)</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>current — Postulated (declared, non-primitive)</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>106/107/108/111/113</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Arc-R stage placements + M-verdict classification rows</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>position-statement classification (per Paper_095 §3.3)</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>current — A-&gt;position</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic-QM</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>'UV divergences = coarse-graining artifacts of omega_c-&gt;inf'; renorm = substrate-cutoff-absorption</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>framework-positioning reframing, explicitly NOT a derivation</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>current — A-&gt;position</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I220"/>
+  <autoFilter ref="A1:I238"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9686,8 +9686,617 @@
       </c>
       <c r="I238" s="2" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Positioning (Report §4)</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Arrow selects the pointer basis (einselection PRIMITIVE); repeatability + Born non-contextuality follow</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>reconstruction — the Gleason/Piron-Soler chain; orthogonality reduced to operational distinguishability, C selected, Soler lattice rigor the residual</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>current — consistent with the qm-kinematics/substrate-evaluation Gleason reconstruction</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29 (read in full)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Positioning (Report §6)</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Unitarity emergent, not fundamental (arrow forbids erasure; between-commitments = reversible QM)</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Positioning §7</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Geometry emergent g ~ 1/b (both matter and geometry emergent)</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>curvature-emergence, static half closed</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>ChannelGranularity</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>ED's channel/pointer basis is COARSE (&gt;&gt; l_ED), so bound charges are single-channel</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>3 standing pillars: (1) l_ED-fine dynamics = coherent Schrodinger evolution (emergent unitarity), not measurement; (2) einselection environment-set + coarse (energy eigenbasis for bound charges); (3) commitment individuates only distinguishable channels, distinguishability operational (A1)</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>explicit ED theorem + exact distinguishability floor OPEN (downgraded from load-bearing to write-up)</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>current — resolved grounded-in-kind (not yet a written ED theorem; imported standard einselection)</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>CollapseRate</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>tau ~ hbar/E_G SCALING from ED's primitives (two branch commitment-clocks N~sqrt(b) the single arrow cannot hold -&gt; einselection individuates)</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr"/>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>the scaling + its deeper origin (the arrow supplies Penrose's missing time)</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>E_G is IDENTIFIED with Penrose's self-energy, NOT computed (honest flag C4); coefficient OPEN; exact energy functional OPEN</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>current — grounded-in-kind scaling argument, NOT a structural derivation; the gap is narrowed, not closed</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>CollapseRate</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Two refinements over the rivals: a DEFINITE reduction (not Diosi's mere decoherence) + a NATIVE regulator for the point-mass divergence</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>from einselection (definiteness) + the finite substrate grain (regulator)</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>CollapseRate</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>NOT excluded by the 2020 spontaneous-radiation bound (Lindblad jump operators = channel projectors J=g·Pi, FORCED from P11; committed states = exact fixed points D[Pi]=0; no continuous diffusion)</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>FORCED jump-operator identification + exact projector algebra (a structural result); resolves the P11 line-gap 'C3 tension' (committed = dark states)</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>NOT a distinctive observable — standard QM predicts the same null (immunity, not a win)</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>current — structural result; the distinction is structural, not observational</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>OpenPiece-i</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>MOND enhancement of E_G (mesoscopic masses sub-a_0 in self-gravity -&gt; naive ~5-50x) is CLOSED by ED's own External Field Effect (Paper_029 horizon dipole sourced by total accel; Earth Newtonizes to ~3.5e-6 -&gt; ED ~ Penrose-Diosi in the lab)</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>the EFE derivation (structural) + the Newtonization arithmetic (solid); the naive 5-50x is an EFE artifact</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-Quadratic-Strain (Model C postulate) + the constructive interference sign (MEASURED tier only)</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>current — RESOLVED, near-term weapon closed (consistency result). BODY stale vs its own banner (Staleness #1)</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Positioning §3.2/§6</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Locality WITHOUT superdeterminism (local commitment + A1 capacity-zero + stochastic-at-commitment; no hidden variable)</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr"/>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>forward arrow = P11; controlled inter-region capacity = EXACTLY zero (A1, measured)</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>current — a genuine foundational advantage over hidden-variable collapse</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>OpenPiece-i</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Collapse rate depends on the ambient gravitational field (EFE) and is anisotropic along it</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>any measured environmental-field dependence of a collapse rate = an ED fingerprint (Penrose/Diosi carry none). But ~10^-6-small near Earth (needs deep-void g_ext &lt;~ a_0/100, inaccessible); its absence where ED predicts it would tension ED. NOTE: non-emission of collapse radiation is NOT an ED prediction (shared with standard QM)</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier)</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>current — distinctive-in-principle but ~10^-6-small and unmeasurable near Earth (needs deep-void g_ext &lt;~ a_0/100)</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>THE arrow = gravity's time = the pointer-basis selector — one primitive, two hats (collapse variable = TIME not energy)</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr"/>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>argued from the sole-process finding (commitment = the sole process primitive)</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>NOT forced by a deeper theorem; carries NO delivered prediction yet</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>current — structural synthesis, unconfirmed (Report §6 guardrail carried verbatim)</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Positioning §3.2</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>ED supplies the well-defined preferred time whose absence drives Penrose's argument (collapse upstream of E_Delta)</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>interpretive reframe: Penrose's 'no fact about which time flows' &lt;-&gt; ED's 'one arrow, two branch-clocks, forced to individuate'</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>quantitative content still Penrose's</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>current — the reframe, not a new number</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>ChannelGranularity</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Explicit channel-granularity theorem + exact distinguishability floor</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr"/>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>OPEN (a write-up task, no longer load-bearing)</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>CollapseRate</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Exact collapse coefficient</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr"/>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>State-reduction</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>CollapseRate/OpenPiece-i</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Exact energy functional (from ED's quadratic-strain gravity, not Einstein-Hilbert)</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — the quadratic-strain interference cross-term could shift it</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I238"/>
+  <autoFilter ref="A1:I253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I253"/>
+  <dimension ref="A1:I295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10295,8 +10295,1582 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>A1 (CommonCauseNotChannel)</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Controlled channel capacity between distinct regions is EXACTLY zero; boundary = common-cause not channel</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>L2=0.000000 (5/5, exact byte-identity) =&gt; MI=0 =&gt; capacity=0; ED locality confirmed as exact channel-zero</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>locality confirmed empirically, not derived from primitives</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>current — Derived (the L2=0 headline is an exact measured zero)</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>B4 (ChargeAsTopology)</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Winding w in Z conserved + irreversibility-protected; orientation-blindness realizes the skeleton, withholds the field</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>slipping requires uncommitting a polarity (P11 forbids); pi_1(U(1))=Z</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>local Coulomb withheld at the discrete layer (Grounded/Open)</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>current — quantization measured to machine precision</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>The parity-clean substrate is VECTOR for every channel-count (det H(k) even =&gt; winding=0 forall N); parity violation NECESSARILY spontaneous</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>parity-cleanness forces B=SAS^-1 =&gt; even det =&gt; zero winding (numerically N=1..6)</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>transport-level ONLY; the relativistic substrate-&gt;Dirac descent is OPEN (§8); the casting is inherited</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>current — Derived (theorem); supersedes The Parity Wall's verdict TIER (not direction)</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>QuantumDarwinism</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Committed records cost no V5 budget (accounting theorem) =&gt; classical objectivity unbounded</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr"/>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>committed record = recorded structure not kernel content; channel-free (A1) + no-erasure (P11)</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>absolute W_max inherited</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>current — Derived-structural</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>A2 (GrownNotInstalled)</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>A grown decoupling boundary reproduces exact channel-zero</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>bandwidth-collapse rule + 'weakest-link' (minimum) endpoint seals every boundary edge</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>the bandwidth-collapse rule's admissibility inherited from the gravity arc; one construction</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded/Measured</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>B4/Maxwell</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Integral Gauss law circulation=2·pi·w (loop-independent); the Maxwell action is LATENT in the coherence deficit (sin^2(dphi/2)~1/4(grad phi)^2)</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>discrete holonomy sum dphi = 2 pi w; standard int (grad phi)^2 electrostatic action</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>local Coulomb field withheld at the discrete layer (OPEN); DCGT-selection = the honest open edge</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded (Coulomb open)</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>gamma^5 = arrow x spontaneous spatial orientation; the vector clean substrate is automatically anomaly-free</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>standard gamma^5=i g0 g1 g2 g3 read in ED terms (both factors native); vector theory carries no gauge anomaly</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>chiral cancellation inherited with the content; contingent on the substrate-&gt;Dirac descent (open)</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded (structural)</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>GaugeStructure</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Gauge group U(N)=SU(N)xU(1)/Z_N form; F^2 action; mass-gap MECHANISM [A,A] lifts flat direction iff non-abelian; single U(1)_Y</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>given C-amplitude (from the keystone) + total bandwidth (P05 isometry); tree-level lift verified (0 for U(1), lifted U(2/3/4))</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>indistinguishability alone gives only S_N; continuum survival = the Clay core, OPEN, NOT a Clay proof; {1,2,3}/anomalies/charge-norm NOT derived</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded (derived-given-inputs; mechanism-tier for the gap)</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Gleason keystone</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Channel orthogonality REDUCES to channel-distinctness given the representation; einselection primitive; Born non-contextuality; C selected</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>operational distinguishability (max&lt;K|E|K&gt;=1-c^2); commits only in the channel basis; P09 rules out R, composites rule out H</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>the Soler lattice technical rigor is the residual (OPEN, #8b Gate 1)</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded; status = 'reduced to the Soler residual' (NOT blocking/three-routes-fail)</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>V5AttractiveSign/PhaseCoherence</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>V5's coupling IS the coherence content of the cross-chain superposition (sqrt(b_A b_B)cos(dpi-int A)); MOND cross-term constructive (P12-Coh rewards alignment)</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr"/>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Paper_090's difference-phase gauge law forces the conjugated-pair moment; Coh maximal at alignment</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>conditional on P-Bipartite-Mapping + like-chain reading; the earlier TSIRELSON characterization was RETRACTED (line 93), replaced by this gauge-law route; reach inherited</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded (gauge-law-forced); sign supplied at Measured tier</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>V5UnifiedBudget/QuantumDarwinism</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>rho_loc=1: monogamy budget = Class-C plateau budget (one W_max spent two ways); per-locus live cap N_live &lt;= W_max/w-bar</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>same int K_V5 at the P08 grain (structural identity); P-V5-Budget + P04 additivity</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>absolute W_max inherited; path-topology not capped per-locus</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>current — Grounded (D-structural identity)</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>AreaLaw/V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Straddling cross-chain (V5) edge count scales as AREA (r^2.02), reach-independent; holographic entropy = the edge count (~0.88/Planck cell)</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr"/>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>build of 40k loci; short-range-&gt;r^2.02, fully-long-range-&gt;r^2.7 (could-say-no fired)</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>assumes the emergent geometry (does not derive it); reproduces a known result = consilience, not a novel prediction</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>current — Measured (on a faithful V5 model)</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>KineticLatticeGas/CanonicalPDE</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Certified continuum = kinetic lattice-gas (BALLISTIC), NOT a diffusion PDE; and does NOT generate the UDM mobility law (beta~0 not 2)</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>diffusion R^2~0.001; ballistic |v|~1; pure ED never mixes (CV~1.2 vs 0.00); front mobility concentration-independent</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>certified Sigma-substrate only; UDM is a separate posit (refutes UDM-from-these-dynamics, not UDM)</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>current — Measured (tested, came-back-no)</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>KnotsNotCrystals/RelationalTick</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>No spontaneous long-range correlation-order in any sector; persistence is rhythmic (V5 binds local proper time, preserving time dilation)</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr"/>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>blind-&gt;common-cause only; no ordering coupling anywhere (5-arc); within-cluster spread 0.084-&gt;0.0005 at reach&lt;D</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>structural reading, NOT a theorem; silent on topological defects (knots); V5+memory honest structural additions</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>current — Measured (structural)</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>MassWithoutMass</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Binding confines massless fronts into a sub-luminal inertial composite (mass without mass); mass(binding) != time-dilation(commit-rate)</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>coupling-off disperses (28-&gt;55), on confines (1.4-2.3); forced-response 0.72 vs unbound 0.97</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>V5-CONDITIONAL (a structural addition, not primitive-forced); binding mass only, fundamental Higgs INHERITED</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>current — Measured (V5-conditional)</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Maxwell</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>The coherence-weighted continuum limit IS Coulomb, but the DETERMINATE substrate does NOT cast the smooth field (emergent shadow)</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr"/>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>lattice int(grad phi)^2: p=1, R^2=0.97 (vs 0.77 at p=2); substrate kinetic + phase-sector Sigma-blind</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>analytic/computed, NOT a substrate measurement — confirms the identification only</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>current — Measured (analytic); form native, smooth field a coarse-grained shadow</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>PhaseCoherence/V5AttractiveSign</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>P12 coherence rewards alignment but stays FINITE-REACH (no crystal) 2D+3D; V5's attractive local-lock from P12's positive sign (flip destroys it)</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>trivial connection crystallizes (R=1); disorder+irreversibility =&gt; xi few lattice units; within-cluster spread ~0.27x at finite reach</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>reach xi value-inherited; V5 existence stays a P10 posit</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>current — Measured (supplies the attractive/constructive sign)</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>The casting (which force is chiral) = SU(2) fundamental pseudoreal vs SU(N&gt;=3) complex</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED (account, surviving candidate) — the SM non-monotone pattern matches no transport winding</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>GaugeStructure/V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Couplings g, scale a, charge values, EWSB; absolute V5 budget scale W_max (=Gamma_plateau, t_Page, CKW coeff)</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr"/>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED / Higgs-gated; only the RELATIONS among budgets are pinned</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Gleason keystone</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Number field C selected from Soler's {R,C,H}</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>account-tier selection: P09 rules out R (central-scalar), V5/063 composites rule out H</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>ParityWall</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Matter/antimatter reference (C) natively selected (first-arrival P09-phase)</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>SELECTED (native) + account; asymmetry magnitude inherited</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>QuantumDarwinism</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>P-QD-LiveWeight (uncommitted branch-basis correlation consumes pairwise V5 weight)</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>argued CONSISTENT-WITH, not forced by, Paper_058's Class-C accounting; falls with F-QD-1</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>current — declared postulate</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>V5AttractiveSign/RelationalTick/MassWithoutMass</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>V5 existence as a cross-chain kernel</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>P10 licenses without forcing; forward derivation open</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>MinimalOntology</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Commitment (P11) is the SOLE process primitive (ED has a spatial arena but no separate temporal one)</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr"/>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>A P11-pivoted audit (pivot disclosed); 'keystone synthesis' is an account, not a theorem; 3D selected not derived</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>current — Asserted (structural, pivot-disclosed)</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>ProxyConversionDoctrine</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Proxy Conversion Doctrine D1-D4 (one rule set replacing five local patches)</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>methodological, falsifiable structure; the alpha-topological encoding-dependence was created then SETTLED same week (alpha_topological=0, Paper_058b)</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>Parity violation is a spontaneous, contingent orientation correlated with the matter/antimatter sign</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>a demonstrated LAW-LEVEL (non-spontaneous, non-contingent, fixed) origin of the weak handedness refutes it. Distinctive vs the SM's law-level fixed handedness</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr"/>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier); vs the SM's law-level fixed handedness</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>current — a sharpened distinctive prediction</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>QuantumDarwinism/V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Class-C plateau &lt;-&gt; GHZ-width commensurate ceiling (ratios 1:1:0.88:r_QD)</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>no commensurate ceiling, or standard fault-tolerance error-&gt;0 with no plateau, refutes it. Standard physics has neither ceiling. D-conditional on P-QD-LiveWeight</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier); standard physics has neither ceiling</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>current — D-conditional on P-QD-LiveWeight</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>ArrowSortsTheContinuum</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Solitons: the bare substrate does not build a reversible balance</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr"/>
+      <c r="F281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>measured negative: the bare rule disperses (defocusing + dissipative)</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (measured edge); not 'solitons impossible' (needs an added focusing medium)</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>GaugeStructure</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Multiplicities {1,2,3} and anomalies NOT selected</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr"/>
+      <c r="F282" s="2" t="inlineStr"/>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>ED's stability route to {1,2,3} tested and REFUTED (symmetric multiplet stable forall N); framework gives SU(N) for any N</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (#2b); unsolved in standard physics too; must NOT be tiered closed</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>ParityWall</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>The weak force's chirality (P) is NOT derived — found absent at every level checked</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr"/>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>no screw/pseudoscalar at wiring/transport/selection/spontaneous levels</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (#2b); superseded in TIER (not direction) by CleanSubstrateVector; P inherited</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Primes (FiniteMemoryCeiling)</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Finite memory saturates the prime template but PROVABLY NOT the escape (parity layer)</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>template reproduced exactly; escape blocked 3 ways; anchored to Sarnak Mobius-disjointness + the sieve parity barrier</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (proven); the program's ONLY theorem-anchored proven negative</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>ArrowSortsTheContinuum</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>The arrow sorts continuum laws into three classes (structure-making native / erasing at layer-2 / preserving = edge)</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>layer-1 native + layer-2 one forced operator + soliton edge (measured negative); full EFE not derived</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis (breaker-passed; per-entry tiers inside)</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>GravityAsEquationOfState</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>ED grounds Jacobson's 3 assumed inputs (severance/grain/eta) and lands G=c^3 l_P^2/hbar</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>the G-match is an algebraic identity; full nonlinear EFE not from ED's own rule; the 2pi/temperature still via the Euclidean route (open)</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis; STALE cross-ref to renamed Khronometric file (Staleness #4)</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>HowPDECoarseGrainReality</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Two hard shadows: YM F^2 derived-given-inputs + gap mechanism-tier (continuum OPEN); NS no-blow-up on 2 postulates; finite-grain singularity triple P04+V5+P11</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>the triple-identity is stated at SYNTHESIS tier, NOT a theorem (target #15); 4 other singularity PDEs same-shape/unexecuted</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>HowTheoryCoarseGrainReality</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Each best theory = a blur of one bandwidth field (kept-&gt;variables, discarded-&gt;symmetries); G/GR at the seam; Born un-blurred; thermo the receipt</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>an organizing lens over standing results, NOT a theorem; one rung certified (diffusion)</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>KnotsNotCrystals</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>ED has topological (knot/link) order, NOT crystalline</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>the correlation-order invariant is silent on topological defects</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis / Grounded</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>MinimalOntology</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Shortest naming of ED = 'commitment and participation' over a spatial stage (floor = 3 substrate + 4 arena + 1 commitment)</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>a mnemonic + one reduction (amplitude fusion) + one reclassification; NOT a reduction to two primitives; 3D selected-not-derived</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis / Grounded</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>Monogamy(065)+Page(050)+Class-C(058) = projections of one bounded envelope W_max; R2 ratios 1:1:0.88</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>form-forced parent; R1/R2 D-conditional; rho_loc=1 a structural identity, 0.88 the measured area-law tiling; absolute scale inherited</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis (form-forced parent)</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>B4/Maxwell</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Whether DCGT coarse-graining selects the Maxwell-action configuration</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>resolved NEGATIVELY for the determinate substrate (kinetic + Sigma-blind), so the smooth field is a shadow; the coarse-grained-selection question named</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic substrate-&gt;Dirac descent</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>behind a fully relativistic chirality statement + the one non-inherited anomaly candidate</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>open (#2b = the T4 gate)</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Gleason keystone</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Soler lattice technical rigor (exchange-property geometry, inf-dim)</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>the load-bearing residual riding under the whole reconstruction (#8b Gate 1)</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>open — 'reduced to the Soler residual'</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>V5AttractiveSign/RelationalTick</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Forward derivation of V5 from the primitives; the temporal envelope shape F_V5</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>V5 existence stays a P10 posit</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I253"/>
+  <autoFilter ref="A1:I295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$317</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$341</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I317"/>
+  <dimension ref="A1:I341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7407,17 +7407,17 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>054</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Continuum gauge-covariant derivative D_mu=d_mu+iA_mu</t>
+          <t>UR-1.1/1.2/1.3 three unresolvedness statements (M_eff&lt;M_cap; Gamma_cross&gt;Gamma_decoupling; Gamma_commit&lt;Gamma_indiv^-1)</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7428,17 +7428,17 @@
       <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>DCGT coarse-graining + P-Polarity-Connection-Match</t>
+          <t>algebraic from Gamma_commit + Gamma_indiv (given A-&gt;regime power-law); UR-1.2 from V5 (Paper_090)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>groups, couplings, local-gauge invariance all I</t>
+          <t>rests on the A-&gt;regime power-law form; coefficients inherited</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>current — conditional on P-Polarity-Connection-Match (postulated)</t>
+          <t>current — Derived (conditional)</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
@@ -7446,17 +7446,17 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>054/056</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Lorentz covariance of the continuum free-scalar equation</t>
+          <t>Existence of Gamma_commit, Gamma_indiv^-1~c/l_ED; M_cap=(Gamma_indiv/Gamma0)^{1/gamma} as the UR-1.1 threshold</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7467,13 +7467,17 @@
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>from V1 Lorentz covariance (Paper_089) preserved by DCGT</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr"/>
+          <t>existence from P11+P12+V1 finite width; M_cap from Gamma_commit(M_cap)=Gamma_indiv</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>numerical Gamma0, gamma inherited (empirical anchoring)</t>
+        </is>
+      </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — Derived (form)</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
@@ -7481,17 +7485,17 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>058b</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Continuum YM equations D_mu F=J (Euler-Lagrange)</t>
+          <t>alpha_topological = 0 (per-locus): the 058 §3.3 saturation never triggers for topological codes</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7502,35 +7506,39 @@
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>standard variational step FROM the postulated action</t>
+          <t>structural: 058's P-Corr-Budget is per-locus, V5 pairwise/finite-reach, a topological web is local (bounded degree, no long-range pairwise load); syndrome records P11-committed (budget-free)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>action = P (P-YM-Action-Coarse-Graining); g_YM value I</t>
+          <t>conditional on three inherited/QI rows</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>current — EL step on a postulated action</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
+          <t>current — Derived-structural settlement (2026-07-14)</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>058b</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Spectral-gap FORM Delta ~ 1/l_* (Yang-Mills mass gap)</t>
+          <t>Syndrome records are budget-free (P11 commitments)</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7541,60 +7549,52 @@
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>form FORCED given postulates; new content = substrate adaptation of Perron-Frobenius/Glimm-Jaffe to V1/V5</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>coeff INHERITED; continuum survival conditional on P-Profile-Rescaling (OPEN); numerical Delta OPEN</t>
-        </is>
-      </c>
+          <t>from the QuantumDarwinism record-bandwidth accounting theorem</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>current — explicitly NOT a Clay proof</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>053</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Substrate quotient = physical-state space; BRST = coarse-grained quotient</t>
+          <t>M_cap = min(N_bw, N_V5, N_commit) is one substrate object; min-structure forced by simultaneity</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>D-via-I: fiber-bundle quotient + DCGT</t>
+          <t>min-structure follows once the composite is postulated</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>constructive Gribov resolution OPEN</t>
+          <t>rests on P-Mcap-Unification + P-Mcap-Finiteness (postulates)</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>current — under P-Gauge-Orbit-Non-Empty + P-Quotient-Hilbert</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
@@ -7602,38 +7602,38 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>054</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Lindblad/GKSL master-equation form</t>
+          <t>The three UR-1 rate quantities have distinct PRIMARY DRIVERS (basis of A/B/C distinctness)</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>FORM-FORCED as the Markovian limit of V5-modulated dynamics (D-via-I)</t>
+          <t>categorization by primary driver</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>specific L_k, rates I; non-Markovian OPEN</t>
+          <t>formal mathematical INDEPENDENCE NOT proven (own audit: A-&gt;assertion)</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>current — no anomaly claim (consistent w/ Lindblad = line-gap, wrong type for anomaly)</t>
+          <t>current — weaker than independence</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
@@ -7641,38 +7641,38 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>055</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Gauge group U(N)=SU(N)xU(1) from channel multiplicity</t>
+          <t>A/B/C three-class EXHAUSTIVENESS — every architecture saturates one of the three constituents</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>non-abelian SU(N) forced by N indistinguishable channels + bandwidth conservation (P04) + invertibility unitarity</t>
+          <t>3 constituents -&gt; 3 classes; 'exhaustiveness is FORCED'</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>SM correspondence {1,2,3} and couplings inherited</t>
+          <t>rests ENTIRELY on P-Three-Constituent + P-Always-Binding (postulates), conditional on the 13-primitive ontology + V1 + V5</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>current — THE one firm upgrade over T17's analogy</t>
+          <t>current — postulate-driven, NOT a proof (README 'proven' overstates, Staleness #4)</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -7684,17 +7684,17 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>057</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>V1 QFT-arc propagator (Kallen-Lehmann retarded form)</t>
+          <t>Class-B exponential gap-suppression Gamma_fail ~ Gamma0 e^{-xi/xi0}</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -7705,17 +7705,17 @@
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>D-via-I: KL machinery applied to P-V1-Spectral + P11 retardation</t>
+          <t>exponential form conditional on P-Rigidity-Gap + P-Boltz-Analogy</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>rho(m^2) values I; multi-point functions OPEN</t>
+          <t>both postulates BY ANALOGY to standard topological-QM, NOT derived; leading-order form NOT unique to ED (topological-QC predicts the same)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>current — Reference-adjacent</t>
+          <t>current — prediction-facing</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
@@ -7723,17 +7723,17 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>058</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>N1+GR1: V1 finite-width + 2-point function on a curved acoustic background</t>
+          <t>Class-C plateau Gamma_fail -&gt; Gamma_plateau &gt; 0 at redundancy saturation</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -7744,17 +7744,17 @@
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>D-via-I: QFCS + Hadamard machinery applied to V1</t>
+          <t>plateau from the finite correlation budget</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>curvature corrections I; backreaction / Einstein eq OPEN</t>
+          <t>conditional on P-Corr-Budget + P-Redundancy-Mapping (linear = A-&gt;regime; domain settled by 058b)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>current — FORM-FORCED under P-Slow-Variation + P-Hadamard-Preservation</t>
+          <t>current — prediction-facing</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
@@ -7762,17 +7762,17 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>059</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Free scalar Klein-Gordon (box+m^2)phi=0 as the DCGT limit of V1</t>
+          <t>Meta-architectures (EC/DD/reservoir/hybrids) = compositions that shift which constituent binds -- NO fourth class</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -7783,39 +7783,35 @@
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>P-CONSTRUCTION matching the standard form (round-8 relabel: was D, now P) under P-Scalar-Match + P-Lorentz-Covariant-Continuum</t>
+          <t>composition structure</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>mass values I; canonical quantization / interacting QFT NOT claimed</t>
+          <t>rests on P-Composition-No-New-Class + P-Substrate-Shift-Locality; the four mappings individually postulated</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>current — postulate-construction</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>060</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Non-abelian YM potential, field strength, YM equation</t>
+          <t>M_crit unification: the matter-wave Q-C boundary and the qubit walls are one substrate threshold</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -7826,12 +7822,12 @@
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>P-constructions matching standard forms under P-StructureConstants-Match</t>
+          <t>same-threshold identification</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>groups I; mass gap / OS NOT claimed here</t>
+          <t>rests on P-Mcrit-Unified + P-Cross-Platform-Universality; values inherited; phase-transition comparison is A-&gt;analogy</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -7844,33 +7840,29 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>053-058</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Substrate is a U(N) lattice gauge theory; escapes Nielsen-Ninomiya</t>
+          <t>Substrate coefficients Gamma0, gamma, alpha, beta, xi0, Delta0, B_cross_max, R_C_sat, Gamma_plateau</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>P05-transport = U(N) link variable; relational graph (no Brillouin torus) + retarded arrow (non-hermitian) evade the two N-N premises</t>
-        </is>
-      </c>
+      <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>'P05 re-routes channels unitarily' is a structural reading, not a closed proof</t>
+          <t>all empirically anchored / platform-inherited</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -7883,33 +7875,29 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>056</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Spin-1/2 from relationality (tethered node carries SU(2)-&gt;SO(3) double cover)</t>
+          <t>140-250 kDa Class-A wall mass (central ~180 kDa)</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>orientation-entanglement / Dirac-belt reading</t>
-        </is>
-      </c>
+      <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Cl(3,1) + pi_1(SO(3))=Z_2 inherited (T2/T4)</t>
+          <t>2-POINT extrapolation (Eibenberger 2013 ~10 kDa + Fein 2019 ~25 kDa). UNDER PRESSURE: interference already shown at &gt;=170 kDa (Nature 2026), inside the window, still QM-consistent. Paper_056 does NOT record this (STALE, Staleness #1) -- do NOT bank as firm</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -7917,47 +7905,43 @@
           <t>current</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>057/058</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Parity violation is non-abelian: NO parity-violating abelian force</t>
+          <t>Specific codes (surface, Majorana, Shor, Steane, concatenated); rigidity/redundancy params xi, R_C</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>general gauge theory PERMITS chiral abelian U(1)s; ED forbids them. A measured parity-violating abelian (U(1)) force refutes it. Matches the low-energy world (EM abelian=vector, weak non-abelian=chiral)</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>V1 single-channel chirality-blind -&gt; abelian vector; V5 cross-channel chirality-sensitive -&gt; non-abelian can be chiral</t>
-        </is>
-      </c>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>WHICH force is chiral (weak assignment) OPEN/inherited</t>
+          <t>platform design / standard QI</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>current — a falsifiable prediction</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
@@ -7965,38 +7949,38 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>056</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Chirality gamma^5 = the arrow's 'screw'</t>
+          <t>Class-A wall EXISTS as sharp + architecture-independent (the shape is the claim, not the number)</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr"/>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>handed-commitment twist as the chirality locus</t>
-        </is>
-      </c>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>no sharp architecture-independent wall (smooth environment/architecture-DEPENDENT decoherence) refutes it. Standard decoherence-only + CSL predict no such wall. NUMBER 140-250 kDa is PRESSURED (&gt;=170 kDa interference already shown, Nature 2026, still QM-consistent) + the second-harmonic leg CONFOUNDED (KDTL optics); the SHAPE is the claim -- do NOT over-bank the number</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>evidence is a 1+1D TOY-lattice computation, NOT canonical V1; gamma^5 relocated to GLOBAL (=i g0 g1 g2 g3); 3 open bridges to a relativistic result</t>
+          <t>(see Falsifier); diverges from decoherence-only (no sharp architecture-independent wall) and from CSL (tuned)</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>current — account; corrected inline (P-imprint retired: C native, P spontaneous+inherited)</t>
+          <t>current — Prediction (live, shape-level); the folder's genuinely distinctive weapon</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -8008,42 +7992,34 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>057</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>{1,2,3} &lt;=&gt; internal amplitude dimension d=3 (Welch-bound); no stable SU(N&gt;=4)</t>
+          <t>Class-B error suppression exponential in xi across architectures</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>a stable/observed gauge sector requiring SU(N&gt;=4) — a 4th independently-stable channel family in the internal amplitude space — refutes the d=3 reduction</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>max mutually-orthogonal channels in C^d is N=d</t>
-        </is>
-      </c>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>WHY d=3 is itself OPEN</t>
+          <t>the leading exponential form is ALSO predicted by standard topological-QC; the wedge is only at higher-order cross-platform consistency</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>current — a falsifiable prediction</t>
+          <t>current — Prediction (weak wedge; NOT distinctive at leading order)</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
@@ -8051,73 +8027,77 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>058b</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Three spatial dimensions because the arrow must hold committed order</t>
+          <t>Class-C plateau, RE-SCOPED to broadcast-type redundancy (repetition / GHZ / cat), NOT surface-code distance</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr"/>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>topological elimination (a link holds in 3D, frozen in 2D, unravels in 4D)</t>
-        </is>
-      </c>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>surface-code clean suppression (Willow Lambda~2) is consistent-BY-CONSTRUCTION, NOT a passed test. Live pair = repetition-code floor persistence (Google ~1e-10 above d~15) + cat-state width ceiling; a floor surviving burst-mitigation at cross-platform-consistent content = the ED signature. Standard FT predicts error-&gt;0</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>conditional on the OPEN premise that ED holds order by spatial linking</t>
+          <t>(see Falsifier); topological branch predicts ABSENCE of plateau; surface-code suppression consistent-BY-CONSTRUCTION not a passed test; repetition-floor + cat-width pair = the live test</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>current — the topology half is Measured</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr"/>
+          <t>current — Prediction (domain-restricted-under-tension)</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>061</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>V1 finite-width retarded vacuum kernel (QFT-arc presentation)</t>
+          <t>Q-Compute arc consolidation (053-060); 'decoherence-centric -&gt; multiplicity-centric' reframing</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>two-point/Wightman/propagator presentation of the canonical V1 (Paper_089); adds no new primitive</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>the reframing row is A-&gt;position in its own audit; introduces no new primitives</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>current — scaffolding for 014-023</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
@@ -8125,38 +8105,34 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>062</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Linking held in 3D, erasable in 4D</t>
+          <t>Cross-domain echo: the BH horizon Gamma_cross-&gt;0 collapse and Q-Compute M_cap saturation share one V5 mechanism</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>linking_3d_vs_4d_probe: unlinking forces a collision (0.000) in 3D, slides free (0.600) in 4D</t>
-        </is>
-      </c>
+      <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>the ED-holds-order-by-linking premise still OPEN</t>
+          <t>A-&gt;position ('no platform realizes a horizon'); rests on P-V5-Shared-Mechanism</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — Synthesis / Asserted</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
@@ -8164,38 +8140,34 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>054</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Retarded ('arrow') hopping produces net chirality signatures</t>
+          <t>Formal mathematical independence of the three UR-1 rate quantities</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>1+1D toy: point-gap winding, skin effect, spectral flow — all zero in the Hermitian control</t>
-        </is>
-      </c>
+      <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>not yet Lorentz-covariantized to a gamma^5 coupling</t>
+          <t>OPEN — A/B/C distinctness + exhaustiveness inherit only 'distinct primary drivers'</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>current — toy; supports the §4.2 account only</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
@@ -8203,34 +8175,34 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>015-019</t>
+          <t>054</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Empirical gauge groups SU(3)xSU(2)xU(1), couplings, masses, mixings</t>
+          <t>The power-law form of Gamma_commit(M_eff)</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr"/>
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>INHERITED (value-layer matching) across the whole arc</t>
+          <t>OPEN (A-&gt;regime) — alternatives (exponential, log) are substrate-consistent and would change M_cap AND the wall; load-bearing under both the wall's shape and number</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
@@ -8238,34 +8210,34 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>015.5</t>
+          <t>056</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Integer-Chern quantization C_n in Z of photonic Hall drift</t>
+          <t>Strategy-1 substrate-derived platform-scaling commitments (cross-platform unification)</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>quantization INHERITED from standard Chern-class topology; ED supplies only the rule-type-bundle identification (form-IDENTIFIED, M3)</t>
+          <t>OPEN — acknowledged retroactive-fit risk until closed; only the sharp/architecture-independent FORM is retroactive-fit-immune today</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
@@ -8273,34 +8245,34 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>019/021/024</t>
+          <t>057</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>g_YM, mass-gap coefficient, Lindblad L_k &amp; rates</t>
+          <t>Substrate-level derivation of P-Rigidity-Gap + P-Boltz-Analogy from primitives</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>INHERITED (empirical matching)</t>
+          <t>OPEN ('in-queue'; currently by analogy to standard topological-QM)</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
@@ -8308,34 +8280,34 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>QFT</t>
+          <t>Q-compute</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>058b</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>P-NonAbelian-Analogy (non-abelian gauge structure 'by analogy')</t>
+          <t>The repetition-code-floor discriminator (does a residual floor survive burst mitigation at cross-platform-consistent content?)</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;analogy; SUPERSEDED/upgraded to Derived by MS-II §2 (Staleness #2)</t>
+          <t>OPEN — the live experiment; NO confirmation claimed</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
@@ -8348,29 +8320,33 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>016</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>P-YM-Action-Coarse-Graining</t>
+          <t>Continuum gauge-covariant derivative D_mu=d_mu+iA_mu</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>DCGT coarse-graining + P-Polarity-Connection-Match</t>
+        </is>
+      </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>the coarse-grained action = standard S_YM (the substantive declared content)</t>
+          <t>groups, couplings, local-gauge invariance all I</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — conditional on P-Polarity-Connection-Match (postulated)</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
@@ -8383,26 +8359,26 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>P-OS-Reflection-Positivity (OS3)</t>
+          <t>Lorentz covariance of the continuum free-scalar equation</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
-      <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>the one non-inheritable OS axiom (the rest of OS inherited)</t>
-        </is>
-      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>from V1 Lorentz covariance (Paper_089) preserved by DCGT</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>current</t>
@@ -8418,29 +8394,33 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>P-Profile-Rescaling (YM continuum survival)</t>
+          <t>Continuum YM equations D_mu F=J (Euler-Lagrange)</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>standard variational step FROM the postulated action</t>
+        </is>
+      </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>the Clay-hard wall; underived — the load-bearing OPEN gap for continuum survival</t>
+          <t>action = P (P-YM-Action-Coarse-Graining); g_YM value I</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — EL step on a postulated action</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr"/>
@@ -8453,32 +8433,40 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>021</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Gribov ambiguity is a coarse-graining artifact (not constructively resolved)</t>
+          <t>Spectral-gap FORM Delta ~ 1/l_* (Yang-Mills mass gap)</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>form FORCED given postulates; new content = substrate adaptation of Perron-Frobenius/Glimm-Jaffe to V1/V5</t>
+        </is>
+      </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>A-&gt;position</t>
+          <t>coeff INHERITED; continuum survival conditional on P-Profile-Rescaling (OPEN); numerical Delta OPEN</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
+          <t>current — explicitly NOT a Clay proof</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -8488,36 +8476,36 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>022</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Yang-Mills arc closes at 'Clay-relevance / structural-positive level'</t>
+          <t>Substrate quotient = physical-state space; BRST = coarse-grained quotient</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
-      <c r="F209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I: fiber-bundle quotient + DCGT</t>
+        </is>
+      </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>above structural analogy, below constructive proof; NOT a Clay-prize-eligible proof (preamble #1,#7)</t>
+          <t>constructive Gribov resolution OPEN</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — under P-Gauge-Orbit-Non-Empty + P-Quotient-Hilbert</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -8527,36 +8515,36 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>019/020/021/023</t>
+          <t>024</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>YM continuum measure; OS3 derivation; mass-gap survival as a-&gt;0 (the 3 Clay-hard gaps)</t>
+          <t>Lindblad/GKSL master-equation form</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
-      <c r="F210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>FORM-FORCED as the Markovian limit of V5-modulated dynamics (D-via-I)</t>
+        </is>
+      </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>OPEN — 023 names all three and states the arc 'does not close' them</t>
+          <t>specific L_k, rates I; non-Markovian OPEN</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — no anomaly claim (consistent w/ Lindblad = line-gap, wrong type for anomaly)</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -8566,32 +8554,40 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>021/023</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Confinement, asymptotic freedom, glueball spectrum, numerical Delta</t>
+          <t>Gauge group U(N)=SU(N)xU(1) from channel multiplicity</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>non-abelian SU(N) forced by N indistinguishable channels + bandwidth conservation (P04) + invertibility unitarity</t>
+        </is>
+      </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>SM correspondence {1,2,3} and couplings inherited</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr"/>
+          <t>current — THE one firm upgrade over T17's analogy</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -8601,36 +8597,36 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>MS-I/MS-II</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Yang-Mills action (~F^2); electroweak/Higgs sector; EWSB; fermion masses</t>
+          <t>V1 QFT-arc propagator (Kallen-Lehmann retarded form)</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I: KL machinery applied to P-V1-Spectral + P11 retardation</t>
+        </is>
+      </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>NOT derived — explicitly deferred to OPEN (archived-source check CLEAN: no four-band/dwell-mass reliance)</t>
+          <t>rho(m^2) values I; multi-point functions OPEN</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — Reference-adjacent</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8640,29 +8636,33 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>014</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>{1,2,3} uniqueness; weak-force specific chirality; anomaly cancellation; the linking premise</t>
+          <t>N1+GR1: V1 finite-width + 2-point function on a curved acoustic background</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr"/>
-      <c r="F213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I: QFCS + Hadamard machinery applied to V1</t>
+        </is>
+      </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>OPEN — reduces to the T4 spinor gate #2b</t>
+          <t>curvature corrections I; backreaction / Einstein eq OPEN</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current — FORM-FORCED under P-Slow-Variation + P-Hadamard-Preservation</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr"/>
@@ -8675,106 +8675,110 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>MS-II</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Full channel-topology -&gt; representation spectrum; spinor construction</t>
+          <t>Free scalar Klein-Gordon (box+m^2)phi=0 as the DCGT limit of V1</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
-      <c r="F214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>P-CONSTRUCTION matching the standard form (round-8 relabel: was D, now P) under P-Scalar-Match + P-Lorentz-Covariant-Continuum</t>
+        </is>
+      </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>OPEN — reduces to the T4 spinor gate #2b (highest-leverage open item in the program)</t>
+          <t>mass values I; canonical quantization / interacting QFT NOT claimed</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I214" s="2" t="inlineStr"/>
+          <t>current — postulate-construction</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>018</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Complex polar carrier P_K=sqrt(b_K)·e^{i pi_K}</t>
+          <t>Non-abelian YM potential, field strength, YM equation</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr"/>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>carrier form from P01-P04 + P09 (audit = D); |P_K|^2=b_K algebraic</t>
+          <t>P-constructions matching standard forms under P-StructureConstants-Match</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>sqrt-convention + arg=pi_K = P; inner product = I (Paper #3)</t>
+          <t>groups I; mass gap / OS NOT claimed here</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>current — convention-tagged</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Berry phase gamma_C = holonomy of the coarse-grained P05 connection</t>
+          <t>Substrate is a U(N) lattice gauge theory; escapes Nielsen-Ninomiya</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr"/>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>D-via-I (holonomy on Paper_016 connection)</t>
+          <t>P05-transport = U(N) link variable; relational graph (no Brillouin torus) + retarded arrow (non-hermitian) evade the two N-N premises</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>numerical gamma_C inherited; non-abelian/off-diagonal OPEN</t>
+          <t>'P05 re-routes channels unitarily' is a structural reading, not a closed proof</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -8787,33 +8791,33 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Aharonov-Bohm phase from T17 bundle circulation</t>
+          <t>Spin-1/2 from relationality (tethered node carries SU(2)-&gt;SO(3) double cover)</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr"/>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>D-via-I (fiber-bundle holonomy)</t>
+          <t>orientation-entanglement / Dirac-belt reading</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>e/hbar inherited; paper: 'ED does NOT newly predict AB'</t>
+          <t>Cl(3,1) + pi_1(SO(3))=Z_2 inherited (T2/T4)</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -8826,38 +8830,42 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Bloch form psi_k=e^{ikx}u_k(x) from discrete translation symmetry</t>
+          <t>Parity violation is non-abelian: NO parity-violating abelian force</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr"/>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>general gauge theory PERMITS chiral abelian U(1)s; ED forbids them. A measured parity-violating abelian (U(1)) force refutes it. Matches the low-energy world (EM abelian=vector, weak non-abelian=chiral)</t>
+        </is>
+      </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>D-via-I (abelian rep theory)</t>
+          <t>V1 single-channel chirality-blind -&gt; abelian vector; V5 cross-channel chirality-sensitive -&gt; non-abelian can be chiral</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>band content inherited</t>
+          <t>WHICH force is chiral (weak assignment) OPEN/inherited</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — a falsifiable prediction</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
@@ -8865,56 +8873,60 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>012.7</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Galilean adjacency/propagation bandwidth-asymmetry</t>
+          <t>Chirality gamma^5 = the arrow's 'screw'</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr"/>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>asymmetry FORCED by P03 (adjacency invariant) + P04 (propagation transforms)</t>
+          <t>handed-commitment twist as the chirality locus</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>full Galilean/Bargmann cohomology OPEN (P03 necessary, not sufficient); m inherited</t>
+          <t>evidence is a 1+1D TOY-lattice computation, NOT canonical V1; gamma^5 relocated to GLOBAL (=i g0 g1 g2 g3); 3 open bridges to a relativistic result</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>current — M3, restricted scope</t>
-        </is>
-      </c>
-      <c r="I219" s="2" t="inlineStr"/>
+          <t>current — account; corrected inline (P-imprint retired: C native, P spontaneous+inherited)</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Born rule f_K=|c_K|^2 as the participation-frequency limit</t>
+          <t>{1,2,3} &lt;=&gt; internal amplitude dimension d=3 (Welch-bound); no stable SU(N&gt;=4)</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -8922,42 +8934,42 @@
           <t>Grounded</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr"/>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>a stable/observed gauge sector requiring SU(N&gt;=4) — a 4th independently-stable channel family in the internal amplitude space — refutes the d=3 reduction</t>
+        </is>
+      </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>frequency limit f_K=b_K/sum b -&gt; Born (audit D)</t>
+          <t>max mutually-orthogonal channels in C^d is N=d</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>rests on P-LinRate (P, load-bearing) + frequentist interp (A-&gt;assumption)</t>
+          <t>WHY d=3 is itself OPEN</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded, NOT pure-M1 (README 'Derived' inflated)</t>
-        </is>
-      </c>
-      <c r="I220" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — a falsifiable prediction</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>003.5</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>P_K=sqrt(b_K)·e^{i pi_K} amplitude carrier, complex-valued forced</t>
+          <t>Three spatial dimensions because the arrow must hold committed order</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -8968,17 +8980,17 @@
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>form FORCED by P04+P05+P09+interference (3 args)</t>
+          <t>topological elimination (a link holds in 3D, frozen in 2D, unravels in 4D)</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>b_K, pi_K values inherited</t>
+          <t>conditional on the OPEN premise that ED holds order by spatial linking</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>current — M3</t>
+          <t>current — the topology half is Measured</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr"/>
@@ -8986,81 +8998,73 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>004.5</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Sesquilinear inner-product form &lt;P,Q&gt;=sum P_K* Q_K (discrete)</t>
+          <t>V1 finite-width retarded vacuum kernel (QFT-arc presentation)</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>form M3-FORCED from P04+P09+composition</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>Tsirelson bound 2sqrt2 INHERITED (Landau-Cirelson 1980); uses P_K=b_K e^{ipi} (|P|^2=b^2), inconsistent with 001/003.5 corrected sqrt(b) (Staleness #4)</t>
-        </is>
-      </c>
+          <t>two-point/Wightman/propagator presentation of the canonical V1 (Paper_089); adds no new primitive</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (form); Tsirelson Inherited</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — scaffolding for 014-023</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>004.6</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Continuum inner-product int Psi* Phi dmu on L^2(M,dmu)</t>
+          <t>Linking held in 3D, erasable in 4D</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>form-consistent under DCGT + P-ScaleSeparation</t>
+          <t>linking_3d_vs_4d_probe: unlinking forces a collision (0.000) in 3D, slides free (0.600) in 4D</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>measure conventions inherited</t>
+          <t>the ED-holds-order-by-linking premise still OPEN</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>current — M3</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
@@ -9068,38 +9072,38 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Projective measurement (projector Pi_K, collapse, Born prob)</t>
+          <t>Retarded ('arrow') hopping produces net chirality signatures</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>post-state/completeness follow; Born prob D-conditional on P-LinRate</t>
+          <t>1+1D toy: point-gap winding, skin effect, spectral flow — all zero in the Hermitian control</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>P-Commit-Projector-Match (P) load-bearing; rests on P-Channel-Orthogonality (from 004)</t>
+          <t>not yet Lorentz-covariantized to a gamma^5 coupling</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded/Postulated</t>
+          <t>current — toy; supports the §4.2 account only</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr"/>
@@ -9107,38 +9111,34 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>005.5</t>
+          <t>015-019</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Double-slit interference rho=|sum P_K|^2; which-path = V5 injection</t>
+          <t>Empirical gauge groups SU(3)xSU(2)xU(1), couplings, masses, mixings</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr"/>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>M3 form-IDENTIFIED (zero pure-D rows)</t>
-        </is>
-      </c>
+      <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>fringe geom/lambda=h/p/visibility inherited; Theta_ED value + V5-injection-rate OPEN; Theta_ED 'P12 ED-threshold' mislabel corrected 2026-07-06</t>
+          <t>INHERITED (value-layer matching) across the whole arc</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (identification)</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr"/>
@@ -9146,38 +9146,34 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>015.5</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Unitary evolution -&gt; Schrodinger i hbar d_t Psi = H Psi</t>
+          <t>Integer-Chern quantization C_n in Z of photonic Hall drift</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>norm-preserving =&gt; unitary; Stone =&gt; Hamiltonian form</t>
-        </is>
-      </c>
+      <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>P-Norm-Preservation (P) load-bearing; Stone+polarization = I; specific H inherited</t>
+          <t>quantization INHERITED from standard Chern-class topology; ED supplies only the rule-type-bundle identification (form-IDENTIFIED, M3)</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded (conditional)</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
@@ -9185,38 +9181,34 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>006.5</t>
+          <t>019/021/024</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Schrodinger equation via Stone's theorem</t>
+          <t>g_YM, mass-gap coefficient, Lindblad L_k &amp; rates</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>load-bearing = the substrate identification (P11-&gt;norm-preservation, P13-&gt;time-translation)</t>
-        </is>
-      </c>
+      <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Schrodinger eqn itself = P (definitional, Paper_095 §2.3); Stone = I; hbar inherited</t>
+          <t>INHERITED (empirical matching)</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>current — M2 (Intermediate Path C)</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
@@ -9224,38 +9216,34 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>006.6</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Kinetic operator T=p^2/2m, the factor-2</t>
+          <t>P-NonAbelian-Analogy (non-abelian gauge structure 'by analogy')</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>factor-2 form-FORCED via the NR limit of Klein-Gordon</t>
-        </is>
-      </c>
+      <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>independent substrate-Galilean-Jacobian derivation of 1/2 = OPEN; V(x), m inherited</t>
+          <t>A-&gt;analogy; SUPERSEDED/upgraded to Derived by MS-II §2 (Staleness #2)</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>current — M3; 1/2-from-primitives Open</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr"/>
@@ -9263,38 +9251,34 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>006.7</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Schrodinger emergence in the thin-participation limit</t>
+          <t>P-YM-Action-Coarse-Graining</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="2" t="inlineStr">
-        <is>
-          <t>leading-order unitary form forced in-regime</t>
-        </is>
-      </c>
+      <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>V1-&gt;unitary coarse-graining OPEN (asserted via DCGT analogy)</t>
+          <t>the coarse-grained action = standard S_YM (the substantive declared content)</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>current — M2, partly Open</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr"/>
@@ -9302,38 +9286,34 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>020</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Hilbert space = Cauchy completion of the motif algebra</t>
+          <t>P-OS-Reflection-Positivity (OS3)</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>emergence D-conditional on P-Motif-Algebra (P) + Cauchy (I)</t>
-        </is>
-      </c>
+      <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>inner product = I; the I-&gt;D relabel needs both Gleason postulates (Staleness #1)</t>
+          <t>the one non-inheritable OS axiom (the rest of OS inherited)</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>current — inner-product edge Open/SUPERSEDED</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
@@ -9341,38 +9321,34 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>021</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Phase structure S^1/U(1) on rule-types</t>
+          <t>P-Profile-Rescaling (YM continuum survival)</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>form-FORCED by P09+P10 + 3 postulates</t>
-        </is>
-      </c>
+      <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2pi normalization inherited; O-Phase-1..4 open</t>
+          <t>the Clay-hard wall; underived — the load-bearing OPEN gap for continuum survival</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>current — M3</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
@@ -9380,38 +9356,34 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>008.5</t>
+          <t>022</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Phase-independence of bandwidth = U(1) gauge invariance</t>
+          <t>Gribov ambiguity is a coarse-graining artifact (not constructively resolved)</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Asserted</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>polar-decomp invariance lemma + identification with U(1) gauge</t>
-        </is>
-      </c>
+      <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>substrate derivation of U(1) gauge invariance from P09 alone OPEN; role of P11 OPEN</t>
+          <t>A-&gt;position</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (lemma + identification)</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
@@ -9419,38 +9391,34 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>012.5</t>
+          <t>023</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Momentum operator p=-i hbar grad = translation generator</t>
+          <t>Yang-Mills arc closes at 'Clay-relevance / structural-positive level'</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
-      <c r="F233" s="2" t="inlineStr">
-        <is>
-          <t>form-identified via Stone on the P03 translation group; CCR [x,p]=i hbar follows</t>
-        </is>
-      </c>
+      <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>P-MomentumIdentification declared (substrate derivation OPEN); hbar INHERITED</t>
+          <t>above structural analogy, below constructive proof; NOT a Clay-prize-eligible proof (preamble #1,#7)</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>current — M3; hbar Inherited</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
@@ -9462,38 +9430,34 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>012.6</t>
+          <t>019/020/021/023</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Heisenberg Dx·Dp &gt;= hbar/2</t>
+          <t>YM continuum measure; OS3 derivation; mass-gap survival as a-&gt;0 (the 3 Clay-hard gaps)</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>composition D-via-I</t>
-        </is>
-      </c>
+      <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>bound INHERITED (Robertson 1929 + Cauchy-Schwarz + CCR); hbar/2 inherited; P-FourBand declared, substrate-derivation OPEN</t>
+          <t>OPEN — 023 names all three and states the arc 'does not close' them</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>current — M3; four-band NOT the archived M-series (clean)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
@@ -9505,34 +9469,34 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>004.5</t>
+          <t>021/023</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Tsirelson bound 2sqrt2</t>
+          <t>Confinement, asymptotic freedom, glueball spectrum, numerical Delta</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>INHERITED (Landau-Cirelson 1980); a standing construction — NOT the separately-retracted 'Tsirelson reduction' V5 characterization</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr"/>
@@ -9540,73 +9504,73 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>012.5/012.6/006.5/006.6</t>
+          <t>MS-I/MS-II</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>hbar throughout the operator sub-arc</t>
+          <t>Yang-Mills action (~F^2); electroweak/Higgs sector; EWSB; fermion masses</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>value INHERITED (Paper_RQM_hbar)</t>
+          <t>NOT derived — explicitly deferred to OPEN (archived-source check CLEAN: no four-band/dwell-mass reliance)</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I236" s="2" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Gleason-Recon (sibling)</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Complex field C (from the Soler menu {R,C,H})</t>
+          <t>{1,2,3} uniqueness; weak-force specific chirality; anomaly cancellation; the linking premise</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr"/>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>C SELECTED: P09 scalar phase rules out R; V5/063 composites rule out H</t>
-        </is>
-      </c>
+      <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>account-tier selection, not a from-scratch derivation</t>
+          <t>OPEN — reduces to the T4 spinor gate #2b</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
@@ -9614,41 +9578,37 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>QM-kinematics</t>
+          <t>QFT</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>MS-II</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Tensor-product composition Psi^AB=Psi^A x Psi^B</t>
+          <t>Full channel-topology -&gt; representation spectrum; spinor construction</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr"/>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>P-QMkin-Composition — 'not from P02+P03 alone... a paper-specific postulate' (preamble #2)</t>
+          <t>OPEN — reduces to the T4 spinor gate #2b (highest-leverage open item in the program)</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>current — README 'Derived' inflated</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -9658,32 +9618,40 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>001</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>P-RB-1 local rate of becoming; substrate-c constancy</t>
+          <t>Complex polar carrier P_K=sqrt(b_K)·e^{i pi_K}</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>carrier form from P01-P04 + P09 (audit = D); |P_K|^2=b_K algebraic</t>
+        </is>
+      </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>'a commitment, not a set of derivations'; hbar (O-RB-1) and c-from-deeper (O-RB-2) OPEN</t>
+          <t>sqrt-convention + arg=pi_K = P; inner product = I (Paper #3)</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>current — foundational commitment</t>
-        </is>
-      </c>
-      <c r="I239" s="2" t="inlineStr"/>
+          <t>current — convention-tagged</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -9693,29 +9661,33 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>011.5</t>
+          <t>009</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Four QM postulates unified under the participation measure</t>
+          <t>Berry phase gamma_C = holonomy of the coarse-grained P05 connection</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr"/>
-      <c r="F240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (holonomy on Paper_016 connection)</t>
+        </is>
+      </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>four postulates = 'four facets of one substrate structure' via distinct primitive routes</t>
+          <t>numerical gamma_C inherited; non-abelian/off-diagonal OPEN</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis (M2); explicitly NOT a Hardy/CDP closed-proof; per-theorem closure OPEN</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr"/>
@@ -9728,36 +9700,36 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>010</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Substrate Gleason: inner-product uniqueness</t>
+          <t>Aharonov-Bohm phase from T17 bundle circulation</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr"/>
-      <c r="F241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I (fiber-bundle holonomy)</t>
+        </is>
+      </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>STALE framing: Paper_004 Update 2026-07-02 says 'P-Channel-Orthogonality fully open / three routes fail / blocking'. SUPERSEDED by the reconstruction (next row)</t>
+          <t>e/hbar inherited; paper: 'ED does NOT newly predict AB'</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>open (stale)</t>
-        </is>
-      </c>
-      <c r="I241" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -9767,55 +9739,51 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Gleason-Recon (sibling)</t>
+          <t>011</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Orthogonality REDUCED; C selected; residual = Soler</t>
+          <t>Bloch form psi_k=e^{ikx}u_k(x) from discrete translation symmetry</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr"/>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>channel-orthogonality REDUCED to channel-distinctness GIVEN the representation (operational distinguishability); C selected; covering law candidate-grounded; einselection primitive; Born non-contextuality resolved; equal-norm/angle discharged 2026-07-10</t>
+          <t>D-via-I (abelian rep theory)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>residual = Soler lattice technical rigor ONLY</t>
+          <t>band content inherited</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>current — 'reduced to the Soler residual': stronger than 004's blocking, weaker than a closed theorem</t>
-        </is>
-      </c>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>012.7</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Cl(3,1) frame uniqueness up to similarity</t>
+          <t>Galilean adjacency/propagation bandwidth-asymmetry</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -9826,64 +9794,56 @@
       <c r="E243" s="2" t="inlineStr"/>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>unique irreducible 4-dim rep of Cl(3,1); all gamma-realizations similarity-equivalent (Pauli + Schur)</t>
+          <t>asymmetry FORCED by P03 (adjacency invariant) + P04 (propagation transforms)</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>basis (Dirac/Weyl/Majorana) = choice of S, not value inheritance; conditional on Paper_017 signature</t>
+          <t>full Galilean/Bargmann cohomology OPEN (P03 necessary, not sufficient); m inherited</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>current — M1 (no numerical inheritance); conditional on 017, not primitives-alone</t>
-        </is>
-      </c>
-      <c r="I243" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3, restricted scope</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>003</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Anyon prohibition in 3+1D</t>
+          <t>Born rule f_K=|c_K|^2 as the participation-frequency limit</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>an anyon (continuous exchange phase eta=e^{i theta}) in a GENUINE 3+1D system — not an effective-2D FQH surface — refutes it. Matter-sector prohibition; general QFT permits anyons only in 2+1D</t>
-        </is>
-      </c>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>pi_1(config space)=S_n in d=3 =&gt; only 1-dim reps eta=±1 =&gt; anyons prohibited; anyons require d=2 (braid group B_n)</t>
+          <t>frequency limit f_K=b_K/sum b -&gt; Born (audit D)</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>effective-2D FQH anyon phases empirical, not load-bearing</t>
+          <t>rests on P-LinRate (P, load-bearing) + frequentist interp (A-&gt;assumption)</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>current — M1 pure dimension-comparison; the cleanest result; a distinctive matter-sector prohibition</t>
+          <t>current — Grounded, NOT pure-M1 (README 'Derived' inflated)</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -9895,17 +9855,17 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>003.5</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Spin-statistics eta=(-1)^{2s}</t>
+          <t>P_K=sqrt(b_K)·e^{i pi_K} amplitude carrier, complex-valued forced</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -9916,39 +9876,35 @@
       <c r="E245" s="2" t="inlineStr"/>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>dichotomy FORM (only eta=±1, fermion/boson exhaustive) from P06+P09 exchange topology + pi_1(SO(3))=Z_2</t>
+          <t>form FORCED by P04+P05+P09+interference (3 args)</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>specific spin assignments (e-=1/2, gamma=1) empirical; CPT/parity/T deferred</t>
+          <t>b_K, pi_K values inherited</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (FORM-FORCED + VALUE-INHERITED)</t>
-        </is>
-      </c>
-      <c r="I245" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>106 (T4)</t>
+          <t>004.5</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Dirac equation (i gamma^mu d_mu - mc/hbar)Psi=0</t>
+          <t>Sesquilinear inner-product form &lt;P,Q&gt;=sum P_K* Q_K (discrete)</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -9959,17 +9915,17 @@
       <c r="E246" s="2" t="inlineStr"/>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>structural mechanism identified: unique first-order Clifford factorization of KG on the Cl(3,1) bundle; §3.7 continuum limit COMPUTED + Wilson-term undoubling 16-&gt;1</t>
+          <t>form M3-FORCED from P04+P09+composition</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>explicit substrate-V1-&gt;Dirac closed proof OPEN; fully-covariant proof OPEN; graph-native SPINOR construction OPEN (canonical P07 supplies NO native channel topology); mass inherited</t>
+          <t>Tsirelson bound 2sqrt2 INHERITED (Landau-Cirelson 1980); uses P_K=b_K e^{ipi} (|P|^2=b^2), inconsistent with 001/003.5 corrected sqrt(b) (Staleness #4)</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>current — M2 (Intermediate Path C); THE #2b gate, genuinely OPEN; chirality NOT claimed derived (vector default, parity inherited). Row-15/§3.7 desync (Staleness #1)</t>
+          <t>current — M3 (form); Tsirelson Inherited</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -9981,17 +9937,17 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>004.6</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Klein-Gordon equation (box+m^2 c^2/hbar^2)Psi=0</t>
+          <t>Continuum inner-product int Psi* Phi dmu on L^2(M,dmu)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10002,17 +9958,17 @@
       <c r="E247" s="2" t="inlineStr"/>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>substrate IDENTIFICATION of m as P04 rest-bandwidth; V1-kernel low-momentum-pole compatibility</t>
+          <t>form-consistent under DCGT + P-ScaleSeparation</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>KG form ITSELF is P-definitional/INHERITED from Paper_017 + std dispersion; V1-&gt;KG-propagator OPEN</t>
+          <t>measure conventions inherited</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>current — M3, FORM-INHERITED (correctly reflects 017's round-8 D-&gt;P; no over-claim)</t>
+          <t>current — M3</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
@@ -10020,17 +9976,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Minimal-coupling KG + conserved 4-current</t>
+          <t>Projective measurement (projector Pi_K, collapse, Born prob)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10041,17 +9997,17 @@
       <c r="E248" s="2" t="inlineStr"/>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>extension of KG to U(1) gauge; Noether current from U(1) phase-invariance</t>
+          <t>post-state/completeness follow; Born prob D-conditional on P-LinRate</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>minimal-coupling form INHERITED (015/016); couplings empirical; V5 multi-channel substrate-graph derivation OPEN</t>
+          <t>P-Commit-Projector-Match (P) load-bearing; rests on P-Channel-Orthogonality (from 004)</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>current — M3, FORM-INHERITED</t>
+          <t>current — Grounded/Postulated</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr"/>
@@ -10059,17 +10015,17 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>005.5</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Lorentz-representation taxonomy</t>
+          <t>Double-slit interference rho=|sum P_K|^2; which-path = V5 injection</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10080,17 +10036,17 @@
       <c r="E249" s="2" t="inlineStr"/>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>finite SL(2,C) (j1,j2) taxonomy as substrate rule-type classification</t>
+          <t>M3 form-IDENTIFIED (zero pure-D rows)</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>which rule-type &lt;-&gt; which rep empirical; Wigner particle-state classification out of scope</t>
+          <t>fringe geom/lambda=h/p/visibility inherited; Theta_ED value + V5-injection-rate OPEN; Theta_ED 'P12 ED-threshold' mislabel corrected 2026-07-06</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (form-IDENTIFIED + VALUE-INHERITED)</t>
+          <t>current — M3 (identification)</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr"/>
@@ -10098,17 +10054,17 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Primitive-level UV finiteness</t>
+          <t>Unitary evolution -&gt; Schrodinger i hbar d_t Psi = H Psi</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10119,17 +10075,17 @@
       <c r="E250" s="2" t="inlineStr"/>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>UV-finiteness from P04 finite bandwidth + P08 scale + V1/V5 finite-kernel form factors</t>
+          <t>norm-preserving =&gt; unitary; Stone =&gt; Hamiltonian form</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>cutoff omega_c=c/l_P value inherited; substrate-graph-&gt;power-counting derivation OPEN; renorm-reframe = A-&gt;position</t>
+          <t>P-Norm-Preservation (P) load-bearing; Stone+polarization = I; specific H inherited</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (form-IDENTIFIED + VALUE-INHERITED)</t>
+          <t>current — Grounded (conditional)</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr"/>
@@ -10137,17 +10093,17 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>112 (T10)</t>
+          <t>006.5</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Lightlike worldlines for sigma=0 rule-types</t>
+          <t>Schrodinger equation via Stone's theorem</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10158,17 +10114,17 @@
       <c r="E251" s="2" t="inlineStr"/>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>null-geodesic propagation form-forced from massless dispersion (T5 at m=0) + std null-geodesic geometry</t>
+          <t>load-bearing = the substrate identification (P11-&gt;norm-preservation, P13-&gt;time-translation)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>EXISTENCE of sigma=0 rule-types CONDITIONAL on Paper_114; substrate-c inherited; V1 at m=0 derivation OPEN</t>
+          <t>Schrodinger eqn itself = P (definitional, Paper_095 §2.3); Stone = I; hbar inherited</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>current — M3 (structure forced, existence conditional)</t>
+          <t>current — M2 (Intermediate Path C)</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr"/>
@@ -10176,17 +10132,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>006.6</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Mass structural form (Arc-M H1)</t>
+          <t>Kinetic operator T=p^2/2m, the factor-2</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10197,39 +10153,35 @@
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>3 structural features form-forced: Lorentz-scalar, P04-bandwidth-anchored, statistics-class-mechanism</t>
+          <t>factor-2 form-FORCED via the NR limit of Klein-Gordon</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>substrate-Higgs §3.3 + substrate-Yukawa §3.5 ASSERTED, NOT derived — OPEN; all mass values empirical; origin of 'statistics-class-mechanism' OPEN</t>
+          <t>independent substrate-Galilean-Jacobian derivation of 1/2 = OPEN; V(x), m inherited</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>current — M2 with OPEN flags; NOT built on archived four-band (dwell handle canonically licensed P02+P03+P07)</t>
-        </is>
-      </c>
-      <c r="I252" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3; 1/2-from-primitives Open</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>114 (GRH-D1)</t>
+          <t>006.7</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Existence of &gt;=1 massless Case-P gauge rule-type</t>
+          <t>Schrodinger emergence in the thin-participation limit</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10240,17 +10192,17 @@
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>existence form-forced CONDITIONAL on P-Gauge + T17 (015) + gauge-quotient (022)</t>
+          <t>leading-order unitary form forced in-regime</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>specific gauge groups/couplings inherited; P-Gauge substrate derivation OPEN</t>
+          <t>V1-&gt;unitary coarse-graining OPEN (asserted via DCGT analogy)</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>current — M2 (conditional on the P-Gauge postulate); 112's sigma=0 existence depends on this</t>
+          <t>current — M2, partly Open</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
@@ -10258,17 +10210,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Vacuum + particle dual Fock structure (sigma=0)</t>
+          <t>Hilbert space = Cauchy completion of the motif algebra</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10279,17 +10231,17 @@
       <c r="E254" s="2" t="inlineStr"/>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>vacuum + 1-particle Fock decomposition from T10 + T8 + Wightman uniqueness</t>
+          <t>emergence D-conditional on P-Motif-Algebra (P) + Cauchy (I)</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>'no rest-frame =&gt; minimal dual' is heuristic, OPEN; mode-density normalization inherited</t>
+          <t>inner product = I; the I-&gt;D relabel needs both Gleason postulates (Staleness #1)</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>current — M3</t>
+          <t>current — inner-product edge Open/SUPERSEDED</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr"/>
@@ -10297,17 +10249,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>MR-R / MR-P conditional massless slot</t>
+          <t>Phase structure S^1/U(1) on rule-types</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10318,12 +10270,12 @@
       <c r="E255" s="2" t="inlineStr"/>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>two-branch mutually-exclusive massless slot (fermion-chiral MR-R / gauge MR-P); disjointness forced by T7</t>
+          <t>form-FORCED by P09+P10 + 3 postulates</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>no-third-mechanism exhaustiveness OPEN; occupants empirical (neutrino MR-R); substrate-c inherited</t>
+          <t>2pi normalization inherited; O-Phase-1..4 open</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -10336,38 +10288,38 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>110 (T8)</t>
+          <t>008.5</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Canonical (anti-)commutation [x,p]=i hbar</t>
+          <t>Phase-independence of bandwidth = U(1) gauge invariance</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>the commutator-vs-anticommutator DICHOTOMY forced by T1 (boson&lt;-&gt;commutator, fermion&lt;-&gt;anticommutator)</t>
+          <t>polar-decomp invariance lemma + identification with U(1) gauge</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>relation FORMS are P-definitional; hbar INHERITED; earlier 'structural origin of hbar' framing disowned as oversold</t>
+          <t>substrate derivation of U(1) gauge invariance from P09 alone OPEN; role of P11 OPEN</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>current — M3 FORM-INHERITED + VALUE-INHERITED</t>
+          <t>current — M3 (lemma + identification)</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
@@ -10375,38 +10327,38 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>112 (hbar)</t>
+          <t>012.5</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>hbar origin = participation quantum per chain-step</t>
+          <t>Momentum operator p=-i hbar grad = translation generator</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>dimensional structure (action=bandwidth x time) form-forced by P04+P05+P11; chain-step invariance (P03+P13) =&gt; hbar universal</t>
+          <t>form-identified via Stone on the P03 translation group; CCR [x,p]=i hbar follows</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>value INHERITED; B_P04 has NO independent substrate definition — §3.3 CIRCULARITY disclaimer: hbar=int B_P04 ds is a relabeling, not a computation</t>
+          <t>P-MomentumIdentification declared (substrate derivation OPEN); hbar INHERITED</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>current — M3, value-INHERITED with honest circularity</t>
+          <t>current — M3; hbar Inherited</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
@@ -10418,73 +10370,77 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>012.6</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>P-Gauge (paper-specific postulate)</t>
+          <t>Heisenberg Dx·Dp &gt;= hbar/2</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>gauge-class connection A_mu on rule-type bundles + gauge-quotient</t>
+          <t>composition D-via-I</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>substrate derivation from P05+P07+P09+P10 alone OPEN (F-Gauge would upgrade M2-&gt;M1)</t>
+          <t>bound INHERITED (Robertson 1929 + Cauchy-Schwarz + CCR); hbar/2 inherited; P-FourBand declared, substrate-derivation OPEN</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>current — Postulated (declared, non-primitive)</t>
-        </is>
-      </c>
-      <c r="I258" s="2" t="inlineStr"/>
+          <t>current — M3; four-band NOT the archived M-series (clean)</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>106/107/108/111/113</t>
+          <t>004.5</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Arc-R stage placements + M-verdict classification rows</t>
+          <t>Tsirelson bound 2sqrt2</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr"/>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>position-statement classification (per Paper_095 §3.3)</t>
-        </is>
-      </c>
-      <c r="G259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr"/>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED (Landau-Cirelson 1980); a standing construction — NOT the separately-retracted 'Tsirelson reduction' V5 characterization</t>
+        </is>
+      </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>current — A-&gt;position</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr"/>
@@ -10492,34 +10448,34 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Relativistic-QM</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>012.5/012.6/006.5/006.6</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>'UV divergences = coarse-graining artifacts of omega_c-&gt;inf'; renorm = substrate-cutoff-absorption</t>
+          <t>hbar throughout the operator sub-arc</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr"/>
-      <c r="F260" s="2" t="inlineStr">
-        <is>
-          <t>framework-positioning reframing, explicitly NOT a derivation</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr"/>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>value INHERITED (Paper_RQM_hbar)</t>
+        </is>
+      </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>current — A-&gt;position</t>
+          <t>current</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
@@ -10527,69 +10483,73 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Positioning (Report §4)</t>
+          <t>Gleason-Recon (sibling)</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Arrow selects the pointer basis (einselection PRIMITIVE); repeatability + Born non-contextuality follow</t>
+          <t>Complex field C (from the Soler menu {R,C,H})</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Standing</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr"/>
-      <c r="F261" s="2" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>C SELECTED: P09 scalar phase rules out R; V5/063 composites rule out H</t>
+        </is>
+      </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>reconstruction — the Gleason/Piron-Soler chain; orthogonality reduced to operational distinguishability, C selected, Soler lattice rigor the residual</t>
+          <t>account-tier selection, not a from-scratch derivation</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>current — consistent with the qm-kinematics/substrate-evaluation Gleason reconstruction</t>
-        </is>
-      </c>
-      <c r="I261" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29 (read in full)</t>
-        </is>
-      </c>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Positioning (Report §6)</t>
+          <t>002</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Unitarity emergent, not fundamental (arrow forbids erasure; between-commitments = reversible QM)</t>
+          <t>Tensor-product composition Psi^AB=Psi^A x Psi^B</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Standing</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr"/>
       <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr"/>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>P-QMkin-Composition — 'not from P02+P03 alone... a paper-specific postulate' (preamble #2)</t>
+        </is>
+      </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — README 'Derived' inflated</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
@@ -10601,120 +10561,104 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Positioning §7</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Geometry emergent g ~ 1/b (both matter and geometry emergent)</t>
+          <t>P-RB-1 local rate of becoming; substrate-c constancy</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Standing</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr"/>
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>curvature-emergence, static half closed</t>
+          <t>'a commitment, not a set of derivations'; hbar (O-RB-1) and c-from-deeper (O-RB-2) OPEN</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I263" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — foundational commitment</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>ChannelGranularity</t>
+          <t>011.5</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>ED's channel/pointer basis is COARSE (&gt;&gt; l_ED), so bound charges are single-channel</t>
+          <t>Four QM postulates unified under the participation measure</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr"/>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>3 standing pillars: (1) l_ED-fine dynamics = coherent Schrodinger evolution (emergent unitarity), not measurement; (2) einselection environment-set + coarse (energy eigenbasis for bound charges); (3) commitment individuates only distinguishable channels, distinguishability operational (A1)</t>
-        </is>
-      </c>
+      <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>explicit ED theorem + exact distinguishability floor OPEN (downgraded from load-bearing to write-up)</t>
+          <t>four postulates = 'four facets of one substrate structure' via distinct primitive routes</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>current — resolved grounded-in-kind (not yet a written ED theorem; imported standard einselection)</t>
-        </is>
-      </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — Synthesis (M2); explicitly NOT a Hardy/CDP closed-proof; per-theorem closure OPEN</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>CollapseRate</t>
+          <t>004</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>tau ~ hbar/E_G SCALING from ED's primitives (two branch commitment-clocks N~sqrt(b) the single arrow cannot hold -&gt; einselection individuates)</t>
+          <t>Substrate Gleason: inner-product uniqueness</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr"/>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>the scaling + its deeper origin (the arrow supplies Penrose's missing time)</t>
-        </is>
-      </c>
+      <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>E_G is IDENTIFIED with Penrose's self-energy, NOT computed (honest flag C4); coefficient OPEN; exact energy functional OPEN</t>
+          <t>STALE framing: Paper_004 Update 2026-07-02 says 'P-Channel-Orthogonality fully open / three routes fail / blocking'. SUPERSEDED by the reconstruction (next row)</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>current — grounded-in-kind scaling argument, NOT a structural derivation; the gap is narrowed, not closed</t>
+          <t>open (stale)</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
@@ -10726,34 +10670,38 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>QM-kinematics</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CollapseRate</t>
+          <t>Gleason-Recon (sibling)</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Two refinements over the rivals: a DEFINITE reduction (not Diosi's mere decoherence) + a NATIVE regulator for the point-mass divergence</t>
+          <t>Orthogonality REDUCED; C selected; residual = Soler</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr"/>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>from einselection (definiteness) + the finite substrate grain (regulator)</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr"/>
+          <t>channel-orthogonality REDUCED to channel-distinctness GIVEN the representation (operational distinguishability); C selected; covering law candidate-grounded; einselection primitive; Born non-contextuality resolved; equal-norm/angle discharged 2026-07-10</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>residual = Soler lattice technical rigor ONLY</t>
+        </is>
+      </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — 'reduced to the Soler residual': stronger than 004's blocking, weaker than a closed theorem</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
@@ -10765,38 +10713,38 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>CollapseRate</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>NOT excluded by the 2020 spontaneous-radiation bound (Lindblad jump operators = channel projectors J=g·Pi, FORCED from P11; committed states = exact fixed points D[Pi]=0; no continuous diffusion)</t>
+          <t>Cl(3,1) frame uniqueness up to similarity</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr"/>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>FORCED jump-operator identification + exact projector algebra (a structural result); resolves the P11 line-gap 'C3 tension' (committed = dark states)</t>
+          <t>unique irreducible 4-dim rep of Cl(3,1); all gamma-realizations similarity-equivalent (Pauli + Schur)</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>NOT a distinctive observable — standard QM predicts the same null (immunity, not a win)</t>
+          <t>basis (Dirac/Weyl/Majorana) = choice of S, not value inheritance; conditional on Paper_017 signature</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>current — structural result; the distinction is structural, not observational</t>
+          <t>current — M1 (no numerical inheritance); conditional on 017, not primitives-alone</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
@@ -10808,38 +10756,42 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>OpenPiece-i</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>MOND enhancement of E_G (mesoscopic masses sub-a_0 in self-gravity -&gt; naive ~5-50x) is CLOSED by ED's own External Field Effect (Paper_029 horizon dipole sourced by total accel; Earth Newtonizes to ~3.5e-6 -&gt; ED ~ Penrose-Diosi in the lab)</t>
+          <t>Anyon prohibition in 3+1D</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr"/>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>an anyon (continuous exchange phase eta=e^{i theta}) in a GENUINE 3+1D system — not an effective-2D FQH surface — refutes it. Matter-sector prohibition; general QFT permits anyons only in 2+1D</t>
+        </is>
+      </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>the EFE derivation (structural) + the Newtonization arithmetic (solid); the naive 5-50x is an EFE artifact</t>
+          <t>pi_1(config space)=S_n in d=3 =&gt; only 1-dim reps eta=±1 =&gt; anyons prohibited; anyons require d=2 (braid group B_n)</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-Quadratic-Strain (Model C postulate) + the constructive interference sign (MEASURED tier only)</t>
+          <t>effective-2D FQH anyon phases empirical, not load-bearing</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>current — RESOLVED, near-term weapon closed (consistency result). BODY stale vs its own banner (Staleness #1)</t>
+          <t>current — M1 pure dimension-comparison; the cleanest result; a distinctive matter-sector prohibition</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
@@ -10851,17 +10803,17 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Positioning §3.2/§6</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Locality WITHOUT superdeterminism (local commitment + A1 capacity-zero + stochastic-at-commitment; no hidden variable)</t>
+          <t>Spin-statistics eta=(-1)^{2s}</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -10872,13 +10824,17 @@
       <c r="E269" s="2" t="inlineStr"/>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>forward arrow = P11; controlled inter-region capacity = EXACTLY zero (A1, measured)</t>
-        </is>
-      </c>
-      <c r="G269" s="2" t="inlineStr"/>
+          <t>dichotomy FORM (only eta=±1, fermion/boson exhaustive) from P06+P09 exchange topology + pi_1(SO(3))=Z_2</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>specific spin assignments (e-=1/2, gamma=1) empirical; CPT/parity/T deferred</t>
+        </is>
+      </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>current — a genuine foundational advantage over hidden-variable collapse</t>
+          <t>current — M3 (FORM-FORCED + VALUE-INHERITED)</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr">
@@ -10890,38 +10846,38 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>OpenPiece-i</t>
+          <t>106 (T4)</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Collapse rate depends on the ambient gravitational field (EFE) and is anisotropic along it</t>
+          <t>Dirac equation (i gamma^mu d_mu - mc/hbar)Psi=0</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr">
-        <is>
-          <t>any measured environmental-field dependence of a collapse rate = an ED fingerprint (Penrose/Diosi carry none). But ~10^-6-small near Earth (needs deep-void g_ext &lt;~ a_0/100, inaccessible); its absence where ED predicts it would tension ED. NOTE: non-emission of collapse radiation is NOT an ED prediction (shared with standard QM)</t>
-        </is>
-      </c>
-      <c r="F270" s="2" t="inlineStr"/>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>structural mechanism identified: unique first-order Clifford factorization of KG on the Cl(3,1) bundle; §3.7 continuum limit COMPUTED + Wilson-term undoubling 16-&gt;1</t>
+        </is>
+      </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier)</t>
+          <t>explicit substrate-V1-&gt;Dirac closed proof OPEN; fully-covariant proof OPEN; graph-native SPINOR construction OPEN (canonical P07 supplies NO native channel topology); mass inherited</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>current — distinctive-in-principle but ~10^-6-small and unmeasurable near Earth (needs deep-void g_ext &lt;~ a_0/100)</t>
+          <t>current — M2 (Intermediate Path C); THE #2b gate, genuinely OPEN; chirality NOT claimed derived (vector default, parity inherited). Row-15/§3.7 desync (Staleness #1)</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
@@ -10933,241 +10889,233 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>THE arrow = gravity's time = the pointer-basis selector — one primitive, two hats (collapse variable = TIME not energy)</t>
+          <t>Klein-Gordon equation (box+m^2 c^2/hbar^2)Psi=0</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>argued from the sole-process finding (commitment = the sole process primitive)</t>
+          <t>substrate IDENTIFICATION of m as P04 rest-bandwidth; V1-kernel low-momentum-pole compatibility</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>NOT forced by a deeper theorem; carries NO delivered prediction yet</t>
+          <t>KG form ITSELF is P-definitional/INHERITED from Paper_017 + std dispersion; V1-&gt;KG-propagator OPEN</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>current — structural synthesis, unconfirmed (Report §6 guardrail carried verbatim)</t>
-        </is>
-      </c>
-      <c r="I271" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3, FORM-INHERITED (correctly reflects 017's round-8 D-&gt;P; no over-claim)</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Positioning §3.2</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ED supplies the well-defined preferred time whose absence drives Penrose's argument (collapse upstream of E_Delta)</t>
+          <t>Minimal-coupling KG + conserved 4-current</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr"/>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>interpretive reframe: Penrose's 'no fact about which time flows' &lt;-&gt; ED's 'one arrow, two branch-clocks, forced to individuate'</t>
+          <t>extension of KG to U(1) gauge; Noether current from U(1) phase-invariance</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>quantitative content still Penrose's</t>
+          <t>minimal-coupling form INHERITED (015/016); couplings empirical; V5 multi-channel substrate-graph derivation OPEN</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>current — the reframe, not a new number</t>
-        </is>
-      </c>
-      <c r="I272" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3, FORM-INHERITED</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>ChannelGranularity</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Explicit channel-granularity theorem + exact distinguishability floor</t>
+          <t>Lorentz-representation taxonomy</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr"/>
-      <c r="F273" s="2" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>finite SL(2,C) (j1,j2) taxonomy as substrate rule-type classification</t>
+        </is>
+      </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>OPEN (a write-up task, no longer load-bearing)</t>
+          <t>which rule-type &lt;-&gt; which rep empirical; Wigner particle-state classification out of scope</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I273" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3 (form-IDENTIFIED + VALUE-INHERITED)</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>CollapseRate</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Exact collapse coefficient</t>
+          <t>Primitive-level UV finiteness</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr"/>
-      <c r="F274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>UV-finiteness from P04 finite bandwidth + P08 scale + V1/V5 finite-kernel form factors</t>
+        </is>
+      </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>cutoff omega_c=c/l_P value inherited; substrate-graph-&gt;power-counting derivation OPEN; renorm-reframe = A-&gt;position</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3 (form-IDENTIFIED + VALUE-INHERITED)</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>State-reduction</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>CollapseRate/OpenPiece-i</t>
+          <t>112 (T10)</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Exact energy functional (from ED's quadratic-strain gravity, not Einstein-Hilbert)</t>
+          <t>Lightlike worldlines for sigma=0 rule-types</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr"/>
-      <c r="F275" s="2" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>null-geodesic propagation form-forced from massless dispersion (T5 at m=0) + std null-geodesic geometry</t>
+        </is>
+      </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>OPEN — the quadratic-strain interference cross-term could shift it</t>
+          <t>EXISTENCE of sigma=0 rule-types CONDITIONAL on Paper_114; substrate-c inherited; V1 at m=0 derivation OPEN</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="I275" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3 (structure forced, existence conditional)</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>A1 (CommonCauseNotChannel)</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Controlled channel capacity between distinct regions is EXACTLY zero; boundary = common-cause not channel</t>
+          <t>Mass structural form (Arc-M H1)</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr"/>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>L2=0.000000 (5/5, exact byte-identity) =&gt; MI=0 =&gt; capacity=0; ED locality confirmed as exact channel-zero</t>
+          <t>3 structural features form-forced: Lorentz-scalar, P04-bandwidth-anchored, statistics-class-mechanism</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>locality confirmed empirically, not derived from primitives</t>
+          <t>substrate-Higgs §3.3 + substrate-Yukawa §3.5 ASSERTED, NOT derived — OPEN; all mass values empirical; origin of 'statistics-class-mechanism' OPEN</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>current — Derived (the L2=0 headline is an exact measured zero)</t>
+          <t>current — M2 with OPEN flags; NOT built on archived four-band (dwell handle canonically licensed P02+P03+P07)</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
@@ -11179,38 +11127,38 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>B4 (ChargeAsTopology)</t>
+          <t>114 (GRH-D1)</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Winding w in Z conserved + irreversibility-protected; orientation-blindness realizes the skeleton, withholds the field</t>
+          <t>Existence of &gt;=1 massless Case-P gauge rule-type</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>slipping requires uncommitting a polarity (P11 forbids); pi_1(U(1))=Z</t>
+          <t>existence form-forced CONDITIONAL on P-Gauge + T17 (015) + gauge-quotient (022)</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>local Coulomb withheld at the discrete layer (Grounded/Open)</t>
+          <t>specific gauge groups/couplings inherited; P-Gauge substrate derivation OPEN</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>current — quantization measured to machine precision</t>
+          <t>current — M2 (conditional on the P-Gauge postulate); 112's sigma=0 existence depends on this</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr"/>
@@ -11218,81 +11166,77 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>CleanSubstrateVector</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>The parity-clean substrate is VECTOR for every channel-count (det H(k) even =&gt; winding=0 forall N); parity violation NECESSARILY spontaneous</t>
+          <t>Vacuum + particle dual Fock structure (sigma=0)</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr"/>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>parity-cleanness forces B=SAS^-1 =&gt; even det =&gt; zero winding (numerically N=1..6)</t>
+          <t>vacuum + 1-particle Fock decomposition from T10 + T8 + Wightman uniqueness</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>transport-level ONLY; the relativistic substrate-&gt;Dirac descent is OPEN (§8); the casting is inherited</t>
+          <t>'no rest-frame =&gt; minimal dual' is heuristic, OPEN; mode-density normalization inherited</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>current — Derived (theorem); supersedes The Parity Wall's verdict TIER (not direction)</t>
-        </is>
-      </c>
-      <c r="I278" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — M3</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>QuantumDarwinism</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Committed records cost no V5 budget (accounting theorem) =&gt; classical objectivity unbounded</t>
+          <t>MR-R / MR-P conditional massless slot</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>committed record = recorded structure not kernel content; channel-free (A1) + no-erasure (P11)</t>
+          <t>two-branch mutually-exclusive massless slot (fermion-chiral MR-R / gauge MR-P); disjointness forced by T7</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>absolute W_max inherited</t>
+          <t>no-third-mechanism exhaustiveness OPEN; occupants empirical (neutrino MR-R); substrate-c inherited</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>current — Derived-structural</t>
+          <t>current — M3</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr"/>
@@ -11300,38 +11244,38 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>A2 (GrownNotInstalled)</t>
+          <t>110 (T8)</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>A grown decoupling boundary reproduces exact channel-zero</t>
+          <t>Canonical (anti-)commutation [x,p]=i hbar</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr"/>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>bandwidth-collapse rule + 'weakest-link' (minimum) endpoint seals every boundary edge</t>
+          <t>the commutator-vs-anticommutator DICHOTOMY forced by T1 (boson&lt;-&gt;commutator, fermion&lt;-&gt;anticommutator)</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>the bandwidth-collapse rule's admissibility inherited from the gravity arc; one construction</t>
+          <t>relation FORMS are P-definitional; hbar INHERITED; earlier 'structural origin of hbar' framing disowned as oversold</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded/Measured</t>
+          <t>current — M3 FORM-INHERITED + VALUE-INHERITED</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr"/>
@@ -11339,77 +11283,81 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>B4/Maxwell</t>
+          <t>112 (hbar)</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Integral Gauss law circulation=2·pi·w (loop-independent); the Maxwell action is LATENT in the coherence deficit (sin^2(dphi/2)~1/4(grad phi)^2)</t>
+          <t>hbar origin = participation quantum per chain-step</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr"/>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>discrete holonomy sum dphi = 2 pi w; standard int (grad phi)^2 electrostatic action</t>
+          <t>dimensional structure (action=bandwidth x time) form-forced by P04+P05+P11; chain-step invariance (P03+P13) =&gt; hbar universal</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>local Coulomb field withheld at the discrete layer (OPEN); DCGT-selection = the honest open edge</t>
+          <t>value INHERITED; B_P04 has NO independent substrate definition — §3.3 CIRCULARITY disclaimer: hbar=int B_P04 ds is a relabeling, not a computation</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded (Coulomb open)</t>
-        </is>
-      </c>
-      <c r="I281" s="2" t="inlineStr"/>
+          <t>current — M3, value-INHERITED with honest circularity</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>CleanSubstrateVector</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>gamma^5 = arrow x spontaneous spatial orientation; the vector clean substrate is automatically anomaly-free</t>
+          <t>P-Gauge (paper-specific postulate)</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr"/>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>standard gamma^5=i g0 g1 g2 g3 read in ED terms (both factors native); vector theory carries no gauge anomaly</t>
+          <t>gauge-class connection A_mu on rule-type bundles + gauge-quotient</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>chiral cancellation inherited with the content; contingent on the substrate-&gt;Dirac descent (open)</t>
+          <t>substrate derivation from P05+P07+P09+P10 alone OPEN (F-Gauge would upgrade M2-&gt;M1)</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded (structural)</t>
+          <t>current — Postulated (declared, non-primitive)</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr"/>
@@ -11417,649 +11365,681 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>GaugeStructure</t>
+          <t>106/107/108/111/113</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Gauge group U(N)=SU(N)xU(1)/Z_N form; F^2 action; mass-gap MECHANISM [A,A] lifts flat direction iff non-abelian; single U(1)_Y</t>
+          <t>Arc-R stage placements + M-verdict classification rows</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Asserted</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr"/>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>given C-amplitude (from the keystone) + total bandwidth (P05 isometry); tree-level lift verified (0 for U(1), lifted U(2/3/4))</t>
-        </is>
-      </c>
-      <c r="G283" s="2" t="inlineStr">
-        <is>
-          <t>indistinguishability alone gives only S_N; continuum survival = the Clay core, OPEN, NOT a Clay proof; {1,2,3}/anomalies/charge-norm NOT derived</t>
-        </is>
-      </c>
+          <t>position-statement classification (per Paper_095 §3.3)</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded (derived-given-inputs; mechanism-tier for the gap)</t>
-        </is>
-      </c>
-      <c r="I283" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — A-&gt;position</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>Relativistic-QM</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Gleason keystone</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Channel orthogonality REDUCES to channel-distinctness given the representation; einselection primitive; Born non-contextuality; C selected</t>
+          <t>'UV divergences = coarse-graining artifacts of omega_c-&gt;inf'; renorm = substrate-cutoff-absorption</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Asserted</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr"/>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>operational distinguishability (max&lt;K|E|K&gt;=1-c^2); commits only in the channel basis; P09 rules out R, composites rule out H</t>
-        </is>
-      </c>
-      <c r="G284" s="2" t="inlineStr">
-        <is>
-          <t>the Soler lattice technical rigor is the residual (OPEN, #8b Gate 1)</t>
-        </is>
-      </c>
+          <t>framework-positioning reframing, explicitly NOT a derivation</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded; status = 'reduced to the Soler residual' (NOT blocking/three-routes-fail)</t>
-        </is>
-      </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — A-&gt;position</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>V5AttractiveSign/PhaseCoherence</t>
+          <t>Positioning (Report §4)</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>V5's coupling IS the coherence content of the cross-chain superposition (sqrt(b_A b_B)cos(dpi-int A)); MOND cross-term constructive (P12-Coh rewards alignment)</t>
+          <t>Arrow selects the pointer basis (einselection PRIMITIVE); repeatability + Born non-contextuality follow</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr"/>
-      <c r="F285" s="2" t="inlineStr">
-        <is>
-          <t>Paper_090's difference-phase gauge law forces the conjugated-pair moment; Coh maximal at alignment</t>
-        </is>
-      </c>
+      <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>conditional on P-Bipartite-Mapping + like-chain reading; the earlier TSIRELSON characterization was RETRACTED (line 93), replaced by this gauge-law route; reach inherited</t>
+          <t>reconstruction — the Gleason/Piron-Soler chain; orthogonality reduced to operational distinguishability, C selected, Soler lattice rigor the residual</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded (gauge-law-forced); sign supplied at Measured tier</t>
+          <t>current — consistent with the qm-kinematics/substrate-evaluation Gleason reconstruction</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>yes 2026-07-29</t>
+          <t>yes 2026-07-29 (read in full)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>V5UnifiedBudget/QuantumDarwinism</t>
+          <t>Positioning (Report §6)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>rho_loc=1: monogamy budget = Class-C plateau budget (one W_max spent two ways); per-locus live cap N_live &lt;= W_max/w-bar</t>
+          <t>Unitarity emergent, not fundamental (arrow forbids erasure; between-commitments = reversible QM)</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Grounded</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr"/>
-      <c r="F286" s="2" t="inlineStr">
-        <is>
-          <t>same int K_V5 at the P08 grain (structural identity); P-V5-Budget + P04 additivity</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>absolute W_max inherited; path-topology not capped per-locus</t>
-        </is>
-      </c>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr"/>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>current — Grounded (D-structural identity)</t>
-        </is>
-      </c>
-      <c r="I286" s="2" t="inlineStr"/>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>AreaLaw/V5UnifiedBudget</t>
+          <t>Positioning §7</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Straddling cross-chain (V5) edge count scales as AREA (r^2.02), reach-independent; holographic entropy = the edge count (~0.88/Planck cell)</t>
+          <t>Geometry emergent g ~ 1/b (both matter and geometry emergent)</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Standing</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr"/>
-      <c r="F287" s="2" t="inlineStr">
-        <is>
-          <t>build of 40k loci; short-range-&gt;r^2.02, fully-long-range-&gt;r^2.7 (could-say-no fired)</t>
-        </is>
-      </c>
+      <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>assumes the emergent geometry (does not derive it); reproduces a known result = consilience, not a novel prediction</t>
+          <t>curvature-emergence, static half closed</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>current — Measured (on a faithful V5 model)</t>
-        </is>
-      </c>
-      <c r="I287" s="2" t="inlineStr"/>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>KineticLatticeGas/CanonicalPDE</t>
+          <t>ChannelGranularity</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Certified continuum = kinetic lattice-gas (BALLISTIC), NOT a diffusion PDE; and does NOT generate the UDM mobility law (beta~0 not 2)</t>
+          <t>ED's channel/pointer basis is COARSE (&gt;&gt; l_ED), so bound charges are single-channel</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr"/>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>diffusion R^2~0.001; ballistic |v|~1; pure ED never mixes (CV~1.2 vs 0.00); front mobility concentration-independent</t>
+          <t>3 standing pillars: (1) l_ED-fine dynamics = coherent Schrodinger evolution (emergent unitarity), not measurement; (2) einselection environment-set + coarse (energy eigenbasis for bound charges); (3) commitment individuates only distinguishable channels, distinguishability operational (A1)</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>certified Sigma-substrate only; UDM is a separate posit (refutes UDM-from-these-dynamics, not UDM)</t>
+          <t>explicit ED theorem + exact distinguishability floor OPEN (downgraded from load-bearing to write-up)</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>current — Measured (tested, came-back-no)</t>
-        </is>
-      </c>
-      <c r="I288" s="2" t="inlineStr"/>
+          <t>current — resolved grounded-in-kind (not yet a written ED theorem; imported standard einselection)</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>KnotsNotCrystals/RelationalTick</t>
+          <t>CollapseRate</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>No spontaneous long-range correlation-order in any sector; persistence is rhythmic (V5 binds local proper time, preserving time dilation)</t>
+          <t>tau ~ hbar/E_G SCALING from ED's primitives (two branch commitment-clocks N~sqrt(b) the single arrow cannot hold -&gt; einselection individuates)</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr"/>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>blind-&gt;common-cause only; no ordering coupling anywhere (5-arc); within-cluster spread 0.084-&gt;0.0005 at reach&lt;D</t>
+          <t>the scaling + its deeper origin (the arrow supplies Penrose's missing time)</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>structural reading, NOT a theorem; silent on topological defects (knots); V5+memory honest structural additions</t>
+          <t>E_G is IDENTIFIED with Penrose's self-energy, NOT computed (honest flag C4); coefficient OPEN; exact energy functional OPEN</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>current — Measured (structural)</t>
-        </is>
-      </c>
-      <c r="I289" s="2" t="inlineStr"/>
+          <t>current — grounded-in-kind scaling argument, NOT a structural derivation; the gap is narrowed, not closed</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>MassWithoutMass</t>
+          <t>CollapseRate</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Binding confines massless fronts into a sub-luminal inertial composite (mass without mass); mass(binding) != time-dilation(commit-rate)</t>
+          <t>Two refinements over the rivals: a DEFINITE reduction (not Diosi's mere decoherence) + a NATIVE regulator for the point-mass divergence</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr"/>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>coupling-off disperses (28-&gt;55), on confines (1.4-2.3); forced-response 0.72 vs unbound 0.97</t>
-        </is>
-      </c>
-      <c r="G290" s="2" t="inlineStr">
-        <is>
-          <t>V5-CONDITIONAL (a structural addition, not primitive-forced); binding mass only, fundamental Higgs INHERITED</t>
-        </is>
-      </c>
+          <t>from einselection (definiteness) + the finite substrate grain (regulator)</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr"/>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>current — Measured (V5-conditional)</t>
-        </is>
-      </c>
-      <c r="I290" s="2" t="inlineStr"/>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>CollapseRate</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>The coherence-weighted continuum limit IS Coulomb, but the DETERMINATE substrate does NOT cast the smooth field (emergent shadow)</t>
+          <t>NOT excluded by the 2020 spontaneous-radiation bound (Lindblad jump operators = channel projectors J=g·Pi, FORCED from P11; committed states = exact fixed points D[Pi]=0; no continuous diffusion)</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr"/>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>lattice int(grad phi)^2: p=1, R^2=0.97 (vs 0.77 at p=2); substrate kinetic + phase-sector Sigma-blind</t>
+          <t>FORCED jump-operator identification + exact projector algebra (a structural result); resolves the P11 line-gap 'C3 tension' (committed = dark states)</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>analytic/computed, NOT a substrate measurement — confirms the identification only</t>
+          <t>NOT a distinctive observable — standard QM predicts the same null (immunity, not a win)</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>current — Measured (analytic); form native, smooth field a coarse-grained shadow</t>
-        </is>
-      </c>
-      <c r="I291" s="2" t="inlineStr"/>
+          <t>current — structural result; the distinction is structural, not observational</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>PhaseCoherence/V5AttractiveSign</t>
+          <t>OpenPiece-i</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>P12 coherence rewards alignment but stays FINITE-REACH (no crystal) 2D+3D; V5's attractive local-lock from P12's positive sign (flip destroys it)</t>
+          <t>MOND enhancement of E_G (mesoscopic masses sub-a_0 in self-gravity -&gt; naive ~5-50x) is CLOSED by ED's own External Field Effect (Paper_029 horizon dipole sourced by total accel; Earth Newtonizes to ~3.5e-6 -&gt; ED ~ Penrose-Diosi in the lab)</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Measured</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr"/>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>trivial connection crystallizes (R=1); disorder+irreversibility =&gt; xi few lattice units; within-cluster spread ~0.27x at finite reach</t>
+          <t>the EFE derivation (structural) + the Newtonization arithmetic (solid); the naive 5-50x is an EFE artifact</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>reach xi value-inherited; V5 existence stays a P10 posit</t>
+          <t>conditional on P-Quadratic-Strain (Model C postulate) + the constructive interference sign (MEASURED tier only)</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>current — Measured (supplies the attractive/constructive sign)</t>
-        </is>
-      </c>
-      <c r="I292" s="2" t="inlineStr"/>
+          <t>current — RESOLVED, near-term weapon closed (consistency result). BODY stale vs its own banner (Staleness #1)</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>CleanSubstrateVector</t>
+          <t>Positioning §3.2/§6</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>The casting (which force is chiral) = SU(2) fundamental pseudoreal vs SU(N&gt;=3) complex</t>
+          <t>Locality WITHOUT superdeterminism (local commitment + A1 capacity-zero + stochastic-at-commitment; no hidden variable)</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr"/>
-      <c r="F293" s="2" t="inlineStr"/>
-      <c r="G293" s="2" t="inlineStr">
-        <is>
-          <t>INHERITED (account, surviving candidate) — the SM non-monotone pattern matches no transport winding</t>
-        </is>
-      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>forward arrow = P11; controlled inter-region capacity = EXACTLY zero (A1, measured)</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr"/>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I293" s="2" t="inlineStr"/>
+          <t>current — a genuine foundational advantage over hidden-variable collapse</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>GaugeStructure/V5UnifiedBudget</t>
+          <t>OpenPiece-i</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Couplings g, scale a, charge values, EWSB; absolute V5 budget scale W_max (=Gamma_plateau, t_Page, CKW coeff)</t>
+          <t>Collapse rate depends on the ambient gravitational field (EFE) and is anisotropic along it</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr"/>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>any measured environmental-field dependence of a collapse rate = an ED fingerprint (Penrose/Diosi carry none). But ~10^-6-small near Earth (needs deep-void g_ext &lt;~ a_0/100, inaccessible); its absence where ED predicts it would tension ED. NOTE: non-emission of collapse radiation is NOT an ED prediction (shared with standard QM)</t>
+        </is>
+      </c>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>INHERITED / Higgs-gated; only the RELATIONS among budgets are pinned</t>
+          <t>(see Falsifier)</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I294" s="2" t="inlineStr"/>
+          <t>current — distinctive-in-principle but ~10^-6-small and unmeasurable near Earth (needs deep-void g_ext &lt;~ a_0/100)</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Gleason keystone</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Number field C selected from Soler's {R,C,H}</t>
+          <t>THE arrow = gravity's time = the pointer-basis selector — one primitive, two hats (collapse variable = TIME not energy)</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr"/>
-      <c r="F295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>argued from the sole-process finding (commitment = the sole process primitive)</t>
+        </is>
+      </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>account-tier selection: P09 rules out R (central-scalar), V5/063 composites rule out H</t>
+          <t>NOT forced by a deeper theorem; carries NO delivered prediction yet</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I295" s="2" t="inlineStr"/>
+          <t>current — structural synthesis, unconfirmed (Report §6 guardrail carried verbatim)</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>ParityWall</t>
+          <t>Positioning §3.2</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Matter/antimatter reference (C) natively selected (first-arrival P09-phase)</t>
+          <t>ED supplies the well-defined preferred time whose absence drives Penrose's argument (collapse upstream of E_Delta)</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Synthesis</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr"/>
-      <c r="F296" s="2" t="inlineStr"/>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>interpretive reframe: Penrose's 'no fact about which time flows' &lt;-&gt; ED's 'one arrow, two branch-clocks, forced to individuate'</t>
+        </is>
+      </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>SELECTED (native) + account; asymmetry magnitude inherited</t>
+          <t>quantitative content still Penrose's</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I296" s="2" t="inlineStr"/>
+          <t>current — the reframe, not a new number</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>QuantumDarwinism</t>
+          <t>ChannelGranularity</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>P-QD-LiveWeight (uncommitted branch-basis correlation consumes pairwise V5 weight)</t>
+          <t>Explicit channel-granularity theorem + exact distinguishability floor</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr"/>
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>argued CONSISTENT-WITH, not forced by, Paper_058's Class-C accounting; falls with F-QD-1</t>
+          <t>OPEN (a write-up task, no longer load-bearing)</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>current — declared postulate</t>
-        </is>
-      </c>
-      <c r="I297" s="2" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>V5AttractiveSign/RelationalTick/MassWithoutMass</t>
+          <t>CollapseRate</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>V5 existence as a cross-chain kernel</t>
+          <t>Exact collapse coefficient</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Postulated</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr"/>
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>P10 licenses without forcing; forward derivation open</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I298" s="2" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>Substrate-evaluation</t>
+          <t>State-reduction</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>MinimalOntology</t>
+          <t>CollapseRate/OpenPiece-i</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Commitment (P11) is the SOLE process primitive (ED has a spatial arena but no separate temporal one)</t>
+          <t>Exact energy functional (from ED's quadratic-strain gravity, not Einstein-Hilbert)</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr"/>
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>A P11-pivoted audit (pivot disclosed); 'keystone synthesis' is an account, not a theorem; 3D selected not derived</t>
+          <t>OPEN — the quadratic-strain interference cross-term could shift it</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>current — Asserted (structural, pivot-disclosed)</t>
-        </is>
-      </c>
-      <c r="I299" s="2" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -12069,32 +12049,40 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>ProxyConversionDoctrine</t>
+          <t>A1 (CommonCauseNotChannel)</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Proxy Conversion Doctrine D1-D4 (one rule set replacing five local patches)</t>
+          <t>Controlled channel capacity between distinct regions is EXACTLY zero; boundary = common-cause not channel</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Asserted</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr"/>
-      <c r="F300" s="2" t="inlineStr"/>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>L2=0.000000 (5/5, exact byte-identity) =&gt; MI=0 =&gt; capacity=0; ED locality confirmed as exact channel-zero</t>
+        </is>
+      </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>methodological, falsifiable structure; the alpha-topological encoding-dependence was created then SETTLED same week (alpha_topological=0, Paper_058b)</t>
+          <t>locality confirmed empirically, not derived from primitives</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr"/>
+          <t>current — Derived (the L2=0 headline is an exact measured zero)</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -12104,33 +12092,33 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>CleanSubstrateVector</t>
+          <t>B4 (ChargeAsTopology)</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Parity violation is a spontaneous, contingent orientation correlated with the matter/antimatter sign</t>
+          <t>Winding w in Z conserved + irreversibility-protected; orientation-blindness realizes the skeleton, withholds the field</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>a demonstrated LAW-LEVEL (non-spontaneous, non-contingent, fixed) origin of the weak handedness refutes it. Distinctive vs the SM's law-level fixed handedness</t>
-        </is>
-      </c>
-      <c r="F301" s="2" t="inlineStr"/>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr"/>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>slipping requires uncommitting a polarity (P11 forbids); pi_1(U(1))=Z</t>
+        </is>
+      </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier); vs the SM's law-level fixed handedness</t>
+          <t>local Coulomb withheld at the discrete layer (Grounded/Open)</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>current — a sharpened distinctive prediction</t>
+          <t>current — quantization measured to machine precision</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr"/>
@@ -12143,36 +12131,40 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>QuantumDarwinism/V5UnifiedBudget</t>
+          <t>CleanSubstrateVector</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Class-C plateau &lt;-&gt; GHZ-width commensurate ceiling (ratios 1:1:0.88:r_QD)</t>
+          <t>The parity-clean substrate is VECTOR for every channel-count (det H(k) even =&gt; winding=0 forall N); parity violation NECESSARILY spontaneous</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Prediction</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>no commensurate ceiling, or standard fault-tolerance error-&gt;0 with no plateau, refutes it. Standard physics has neither ceiling. D-conditional on P-QD-LiveWeight</t>
-        </is>
-      </c>
-      <c r="F302" s="2" t="inlineStr"/>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr"/>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>parity-cleanness forces B=SAS^-1 =&gt; even det =&gt; zero winding (numerically N=1..6)</t>
+        </is>
+      </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>(see Falsifier); standard physics has neither ceiling</t>
+          <t>transport-level ONLY; the relativistic substrate-&gt;Dirac descent is OPEN (§8); the casting is inherited</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>current — D-conditional on P-QD-LiveWeight</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr"/>
+          <t>current — Derived (theorem); supersedes The Parity Wall's verdict TIER (not direction)</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -12182,29 +12174,33 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>ArrowSortsTheContinuum</t>
+          <t>QuantumDarwinism</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Solitons: the bare substrate does not build a reversible balance</t>
+          <t>Committed records cost no V5 budget (accounting theorem) =&gt; classical objectivity unbounded</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr"/>
-      <c r="F303" s="2" t="inlineStr"/>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>committed record = recorded structure not kernel content; channel-free (A1) + no-erasure (P11)</t>
+        </is>
+      </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>measured negative: the bare rule disperses (defocusing + dissipative)</t>
+          <t>absolute W_max inherited</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>current — Wall (measured edge); not 'solitons impossible' (needs an added focusing medium)</t>
+          <t>current — Derived-structural</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr"/>
@@ -12217,36 +12213,36 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>GaugeStructure</t>
+          <t>A2 (GrownNotInstalled)</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Multiplicities {1,2,3} and anomalies NOT selected</t>
+          <t>A grown decoupling boundary reproduces exact channel-zero</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr"/>
-      <c r="F304" s="2" t="inlineStr"/>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>bandwidth-collapse rule + 'weakest-link' (minimum) endpoint seals every boundary edge</t>
+        </is>
+      </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>ED's stability route to {1,2,3} tested and REFUTED (symmetric multiplet stable forall N); framework gives SU(N) for any N</t>
+          <t>the bandwidth-collapse rule's admissibility inherited from the gravity arc; one construction</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>current — Wall (#2b); unsolved in standard physics too; must NOT be tiered closed</t>
-        </is>
-      </c>
-      <c r="I304" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — Grounded/Measured</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -12256,29 +12252,33 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>ParityWall</t>
+          <t>B4/Maxwell</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>The weak force's chirality (P) is NOT derived — found absent at every level checked</t>
+          <t>Integral Gauss law circulation=2·pi·w (loop-independent); the Maxwell action is LATENT in the coherence deficit (sin^2(dphi/2)~1/4(grad phi)^2)</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr"/>
-      <c r="F305" s="2" t="inlineStr"/>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>discrete holonomy sum dphi = 2 pi w; standard int (grad phi)^2 electrostatic action</t>
+        </is>
+      </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>no screw/pseudoscalar at wiring/transport/selection/spontaneous levels</t>
+          <t>local Coulomb field withheld at the discrete layer (OPEN); DCGT-selection = the honest open edge</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>current — Wall (#2b); superseded in TIER (not direction) by CleanSubstrateVector; P inherited</t>
+          <t>current — Grounded (Coulomb open)</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr"/>
@@ -12291,36 +12291,36 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Primes (FiniteMemoryCeiling)</t>
+          <t>CleanSubstrateVector</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Finite memory saturates the prime template but PROVABLY NOT the escape (parity layer)</t>
+          <t>gamma^5 = arrow x spontaneous spatial orientation; the vector clean substrate is automatically anomaly-free</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
-      <c r="F306" s="2" t="inlineStr"/>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>standard gamma^5=i g0 g1 g2 g3 read in ED terms (both factors native); vector theory carries no gauge anomaly</t>
+        </is>
+      </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>template reproduced exactly; escape blocked 3 ways; anchored to Sarnak Mobius-disjointness + the sieve parity barrier</t>
+          <t>chiral cancellation inherited with the content; contingent on the substrate-&gt;Dirac descent (open)</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>current — Wall (proven); the program's ONLY theorem-anchored proven negative</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr">
-        <is>
-          <t>yes 2026-07-29</t>
-        </is>
-      </c>
+          <t>current — Grounded (structural)</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -12330,32 +12330,40 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>ArrowSortsTheContinuum</t>
+          <t>GaugeStructure</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>The arrow sorts continuum laws into three classes (structure-making native / erasing at layer-2 / preserving = edge)</t>
+          <t>Gauge group U(N)=SU(N)xU(1)/Z_N form; F^2 action; mass-gap MECHANISM [A,A] lifts flat direction iff non-abelian; single U(1)_Y</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr"/>
-      <c r="F307" s="2" t="inlineStr"/>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>given C-amplitude (from the keystone) + total bandwidth (P05 isometry); tree-level lift verified (0 for U(1), lifted U(2/3/4))</t>
+        </is>
+      </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>layer-1 native + layer-2 one forced operator + soliton edge (measured negative); full EFE not derived</t>
+          <t>indistinguishability alone gives only S_N; continuum survival = the Clay core, OPEN, NOT a Clay proof; {1,2,3}/anomalies/charge-norm NOT derived</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis (breaker-passed; per-entry tiers inside)</t>
-        </is>
-      </c>
-      <c r="I307" s="2" t="inlineStr"/>
+          <t>current — Grounded (derived-given-inputs; mechanism-tier for the gap)</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -12365,32 +12373,40 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>GravityAsEquationOfState</t>
+          <t>Gleason keystone</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>ED grounds Jacobson's 3 assumed inputs (severance/grain/eta) and lands G=c^3 l_P^2/hbar</t>
+          <t>Channel orthogonality REDUCES to channel-distinctness given the representation; einselection primitive; Born non-contextuality; C selected</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr"/>
-      <c r="F308" s="2" t="inlineStr"/>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>operational distinguishability (max&lt;K|E|K&gt;=1-c^2); commits only in the channel basis; P09 rules out R, composites rule out H</t>
+        </is>
+      </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>the G-match is an algebraic identity; full nonlinear EFE not from ED's own rule; the 2pi/temperature still via the Euclidean route (open)</t>
+          <t>the Soler lattice technical rigor is the residual (OPEN, #8b Gate 1)</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis; STALE cross-ref to renamed Khronometric file (Staleness #4)</t>
-        </is>
-      </c>
-      <c r="I308" s="2" t="inlineStr"/>
+          <t>current — Grounded; status = 'reduced to the Soler residual' (NOT blocking/three-routes-fail)</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -12400,32 +12416,40 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>HowPDECoarseGrainReality</t>
+          <t>V5AttractiveSign/PhaseCoherence</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Two hard shadows: YM F^2 derived-given-inputs + gap mechanism-tier (continuum OPEN); NS no-blow-up on 2 postulates; finite-grain singularity triple P04+V5+P11</t>
+          <t>V5's coupling IS the coherence content of the cross-chain superposition (sqrt(b_A b_B)cos(dpi-int A)); MOND cross-term constructive (P12-Coh rewards alignment)</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr"/>
-      <c r="F309" s="2" t="inlineStr"/>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Paper_090's difference-phase gauge law forces the conjugated-pair moment; Coh maximal at alignment</t>
+        </is>
+      </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>the triple-identity is stated at SYNTHESIS tier, NOT a theorem (target #15); 4 other singularity PDEs same-shape/unexecuted</t>
+          <t>conditional on P-Bipartite-Mapping + like-chain reading; the earlier TSIRELSON characterization was RETRACTED (line 93), replaced by this gauge-law route; reach inherited</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis</t>
-        </is>
-      </c>
-      <c r="I309" s="2" t="inlineStr"/>
+          <t>current — Grounded (gauge-law-forced); sign supplied at Measured tier</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -12435,29 +12459,33 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>HowTheoryCoarseGrainReality</t>
+          <t>V5UnifiedBudget/QuantumDarwinism</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Each best theory = a blur of one bandwidth field (kept-&gt;variables, discarded-&gt;symmetries); G/GR at the seam; Born un-blurred; thermo the receipt</t>
+          <t>rho_loc=1: monogamy budget = Class-C plateau budget (one W_max spent two ways); per-locus live cap N_live &lt;= W_max/w-bar</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr"/>
-      <c r="F310" s="2" t="inlineStr"/>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>same int K_V5 at the P08 grain (structural identity); P-V5-Budget + P04 additivity</t>
+        </is>
+      </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>an organizing lens over standing results, NOT a theorem; one rung certified (diffusion)</t>
+          <t>absolute W_max inherited; path-topology not capped per-locus</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis</t>
+          <t>current — Grounded (D-structural identity)</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr"/>
@@ -12470,29 +12498,33 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>KnotsNotCrystals</t>
+          <t>AreaLaw/V5UnifiedBudget</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>ED has topological (knot/link) order, NOT crystalline</t>
+          <t>Straddling cross-chain (V5) edge count scales as AREA (r^2.02), reach-independent; holographic entropy = the edge count (~0.88/Planck cell)</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr"/>
-      <c r="F311" s="2" t="inlineStr"/>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>build of 40k loci; short-range-&gt;r^2.02, fully-long-range-&gt;r^2.7 (could-say-no fired)</t>
+        </is>
+      </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>the correlation-order invariant is silent on topological defects</t>
+          <t>assumes the emergent geometry (does not derive it); reproduces a known result = consilience, not a novel prediction</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis / Grounded</t>
+          <t>current — Measured (on a faithful V5 model)</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
@@ -12505,29 +12537,33 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>MinimalOntology</t>
+          <t>KineticLatticeGas/CanonicalPDE</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Shortest naming of ED = 'commitment and participation' over a spatial stage (floor = 3 substrate + 4 arena + 1 commitment)</t>
+          <t>Certified continuum = kinetic lattice-gas (BALLISTIC), NOT a diffusion PDE; and does NOT generate the UDM mobility law (beta~0 not 2)</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr"/>
-      <c r="F312" s="2" t="inlineStr"/>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>diffusion R^2~0.001; ballistic |v|~1; pure ED never mixes (CV~1.2 vs 0.00); front mobility concentration-independent</t>
+        </is>
+      </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>a mnemonic + one reduction (amplitude fusion) + one reclassification; NOT a reduction to two primitives; 3D selected-not-derived</t>
+          <t>certified Sigma-substrate only; UDM is a separate posit (refutes UDM-from-these-dynamics, not UDM)</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis / Grounded</t>
+          <t>current — Measured (tested, came-back-no)</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr"/>
@@ -12540,29 +12576,33 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>V5UnifiedBudget</t>
+          <t>KnotsNotCrystals/RelationalTick</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Monogamy(065)+Page(050)+Class-C(058) = projections of one bounded envelope W_max; R2 ratios 1:1:0.88</t>
+          <t>No spontaneous long-range correlation-order in any sector; persistence is rhythmic (V5 binds local proper time, preserving time dilation)</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Synthesis</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr"/>
-      <c r="F313" s="2" t="inlineStr"/>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>blind-&gt;common-cause only; no ordering coupling anywhere (5-arc); within-cluster spread 0.084-&gt;0.0005 at reach&lt;D</t>
+        </is>
+      </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>form-forced parent; R1/R2 D-conditional; rho_loc=1 a structural identity, 0.88 the measured area-law tiling; absolute scale inherited</t>
+          <t>structural reading, NOT a theorem; silent on topological defects (knots); V5+memory honest structural additions</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>current — Synthesis (form-forced parent)</t>
+          <t>current — Measured (structural)</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr"/>
@@ -12575,29 +12615,33 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>B4/Maxwell</t>
+          <t>MassWithoutMass</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Whether DCGT coarse-graining selects the Maxwell-action configuration</t>
+          <t>Binding confines massless fronts into a sub-luminal inertial composite (mass without mass); mass(binding) != time-dilation(commit-rate)</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
-      <c r="F314" s="2" t="inlineStr"/>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>coupling-off disperses (28-&gt;55), on confines (1.4-2.3); forced-response 0.72 vs unbound 0.97</t>
+        </is>
+      </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>resolved NEGATIVELY for the determinate substrate (kinetic + Sigma-blind), so the smooth field is a shadow; the coarse-grained-selection question named</t>
+          <t>V5-CONDITIONAL (a structural addition, not primitive-forced); binding mass only, fundamental Higgs INHERITED</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>current — Measured (V5-conditional)</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr"/>
@@ -12610,29 +12654,33 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>CleanSubstrateVector</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Relativistic substrate-&gt;Dirac descent</t>
+          <t>The coherence-weighted continuum limit IS Coulomb, but the DETERMINATE substrate does NOT cast the smooth field (emergent shadow)</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr"/>
-      <c r="F315" s="2" t="inlineStr"/>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>lattice int(grad phi)^2: p=1, R^2=0.97 (vs 0.77 at p=2); substrate kinetic + phase-sector Sigma-blind</t>
+        </is>
+      </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>behind a fully relativistic chirality statement + the one non-inherited anomaly candidate</t>
+          <t>analytic/computed, NOT a substrate measurement — confirms the identification only</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>open (#2b = the T4 gate)</t>
+          <t>current — Measured (analytic); form native, smooth field a coarse-grained shadow</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr"/>
@@ -12645,29 +12693,33 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Gleason keystone</t>
+          <t>PhaseCoherence/V5AttractiveSign</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Soler lattice technical rigor (exchange-property geometry, inf-dim)</t>
+          <t>P12 coherence rewards alignment but stays FINITE-REACH (no crystal) 2D+3D; V5's attractive local-lock from P12's positive sign (flip destroys it)</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr"/>
-      <c r="F316" s="2" t="inlineStr"/>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>trivial connection crystallizes (R=1); disorder+irreversibility =&gt; xi few lattice units; within-cluster spread ~0.27x at finite reach</t>
+        </is>
+      </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>the load-bearing residual riding under the whole reconstruction (#8b Gate 1)</t>
+          <t>reach xi value-inherited; V5 existence stays a P10 posit</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>open — 'reduced to the Soler residual'</t>
+          <t>current — Measured (supplies the attractive/constructive sign)</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr"/>
@@ -12680,35 +12732,891 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>V5AttractiveSign/RelationalTick</t>
+          <t>CleanSubstrateVector</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Forward derivation of V5 from the primitives; the temporal envelope shape F_V5</t>
+          <t>The casting (which force is chiral) = SU(2) fundamental pseudoreal vs SU(N&gt;=3) complex</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Selected/Inherited</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr"/>
       <c r="F317" s="2" t="inlineStr"/>
       <c r="G317" s="2" t="inlineStr">
         <is>
+          <t>INHERITED (account, surviving candidate) — the SM non-monotone pattern matches no transport winding</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>GaugeStructure/V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>Couplings g, scale a, charge values, EWSB; absolute V5 budget scale W_max (=Gamma_plateau, t_Page, CKW coeff)</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr"/>
+      <c r="F318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>INHERITED / Higgs-gated; only the RELATIONS among budgets are pinned</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Gleason keystone</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>Number field C selected from Soler's {R,C,H}</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr"/>
+      <c r="F319" s="2" t="inlineStr"/>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>account-tier selection: P09 rules out R (central-scalar), V5/063 composites rule out H</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>ParityWall</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>Matter/antimatter reference (C) natively selected (first-arrival P09-phase)</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr"/>
+      <c r="F320" s="2" t="inlineStr"/>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>SELECTED (native) + account; asymmetry magnitude inherited</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>QuantumDarwinism</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>P-QD-LiveWeight (uncommitted branch-basis correlation consumes pairwise V5 weight)</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr"/>
+      <c r="F321" s="2" t="inlineStr"/>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>argued CONSISTENT-WITH, not forced by, Paper_058's Class-C accounting; falls with F-QD-1</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>current — declared postulate</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>V5AttractiveSign/RelationalTick/MassWithoutMass</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>V5 existence as a cross-chain kernel</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr"/>
+      <c r="F322" s="2" t="inlineStr"/>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>P10 licenses without forcing; forward derivation open</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>MinimalOntology</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>Commitment (P11) is the SOLE process primitive (ED has a spatial arena but no separate temporal one)</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr"/>
+      <c r="F323" s="2" t="inlineStr"/>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>A P11-pivoted audit (pivot disclosed); 'keystone synthesis' is an account, not a theorem; 3D selected not derived</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>current — Asserted (structural, pivot-disclosed)</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>ProxyConversionDoctrine</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Proxy Conversion Doctrine D1-D4 (one rule set replacing five local patches)</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr"/>
+      <c r="F324" s="2" t="inlineStr"/>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>methodological, falsifiable structure; the alpha-topological encoding-dependence was created then SETTLED same week (alpha_topological=0, Paper_058b)</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>Parity violation is a spontaneous, contingent orientation correlated with the matter/antimatter sign</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>a demonstrated LAW-LEVEL (non-spontaneous, non-contingent, fixed) origin of the weak handedness refutes it. Distinctive vs the SM's law-level fixed handedness</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr"/>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier); vs the SM's law-level fixed handedness</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>current — a sharpened distinctive prediction</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>QuantumDarwinism/V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>Class-C plateau &lt;-&gt; GHZ-width commensurate ceiling (ratios 1:1:0.88:r_QD)</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>no commensurate ceiling, or standard fault-tolerance error-&gt;0 with no plateau, refutes it. Standard physics has neither ceiling. D-conditional on P-QD-LiveWeight</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr"/>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>(see Falsifier); standard physics has neither ceiling</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>current — D-conditional on P-QD-LiveWeight</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>ArrowSortsTheContinuum</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>Solitons: the bare substrate does not build a reversible balance</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr"/>
+      <c r="F327" s="2" t="inlineStr"/>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>measured negative: the bare rule disperses (defocusing + dissipative)</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (measured edge); not 'solitons impossible' (needs an added focusing medium)</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>GaugeStructure</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>Multiplicities {1,2,3} and anomalies NOT selected</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr"/>
+      <c r="F328" s="2" t="inlineStr"/>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>ED's stability route to {1,2,3} tested and REFUTED (symmetric multiplet stable forall N); framework gives SU(N) for any N</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (#2b); unsolved in standard physics too; must NOT be tiered closed</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>ParityWall</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>The weak force's chirality (P) is NOT derived — found absent at every level checked</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr"/>
+      <c r="F329" s="2" t="inlineStr"/>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>no screw/pseudoscalar at wiring/transport/selection/spontaneous levels</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (#2b); superseded in TIER (not direction) by CleanSubstrateVector; P inherited</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Primes (FiniteMemoryCeiling)</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>Finite memory saturates the prime template but PROVABLY NOT the escape (parity layer)</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr"/>
+      <c r="F330" s="2" t="inlineStr"/>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>template reproduced exactly; escape blocked 3 ways; anchored to Sarnak Mobius-disjointness + the sieve parity barrier</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>current — Wall (proven); the program's ONLY theorem-anchored proven negative</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>yes 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>ArrowSortsTheContinuum</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>The arrow sorts continuum laws into three classes (structure-making native / erasing at layer-2 / preserving = edge)</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr"/>
+      <c r="F331" s="2" t="inlineStr"/>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>layer-1 native + layer-2 one forced operator + soliton edge (measured negative); full EFE not derived</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis (breaker-passed; per-entry tiers inside)</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>GravityAsEquationOfState</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>ED grounds Jacobson's 3 assumed inputs (severance/grain/eta) and lands G=c^3 l_P^2/hbar</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr"/>
+      <c r="F332" s="2" t="inlineStr"/>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>the G-match is an algebraic identity; full nonlinear EFE not from ED's own rule; the 2pi/temperature still via the Euclidean route (open)</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis; STALE cross-ref to renamed Khronometric file (Staleness #4)</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>HowPDECoarseGrainReality</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>Two hard shadows: YM F^2 derived-given-inputs + gap mechanism-tier (continuum OPEN); NS no-blow-up on 2 postulates; finite-grain singularity triple P04+V5+P11</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr"/>
+      <c r="F333" s="2" t="inlineStr"/>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>the triple-identity is stated at SYNTHESIS tier, NOT a theorem (target #15); 4 other singularity PDEs same-shape/unexecuted</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>HowTheoryCoarseGrainReality</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>Each best theory = a blur of one bandwidth field (kept-&gt;variables, discarded-&gt;symmetries); G/GR at the seam; Born un-blurred; thermo the receipt</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr"/>
+      <c r="F334" s="2" t="inlineStr"/>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>an organizing lens over standing results, NOT a theorem; one rung certified (diffusion)</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>KnotsNotCrystals</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>ED has topological (knot/link) order, NOT crystalline</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr"/>
+      <c r="F335" s="2" t="inlineStr"/>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>the correlation-order invariant is silent on topological defects</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis / Grounded</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>MinimalOntology</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>Shortest naming of ED = 'commitment and participation' over a spatial stage (floor = 3 substrate + 4 arena + 1 commitment)</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr"/>
+      <c r="F336" s="2" t="inlineStr"/>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>a mnemonic + one reduction (amplitude fusion) + one reclassification; NOT a reduction to two primitives; 3D selected-not-derived</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis / Grounded</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>V5UnifiedBudget</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>Monogamy(065)+Page(050)+Class-C(058) = projections of one bounded envelope W_max; R2 ratios 1:1:0.88</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr"/>
+      <c r="F337" s="2" t="inlineStr"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>form-forced parent; R1/R2 D-conditional; rho_loc=1 a structural identity, 0.88 the measured area-law tiling; absolute scale inherited</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>current — Synthesis (form-forced parent)</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>B4/Maxwell</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>Whether DCGT coarse-graining selects the Maxwell-action configuration</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr"/>
+      <c r="F338" s="2" t="inlineStr"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>resolved NEGATIVELY for the determinate substrate (kinetic + Sigma-blind), so the smooth field is a shadow; the coarse-grained-selection question named</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>CleanSubstrateVector</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>Relativistic substrate-&gt;Dirac descent</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr"/>
+      <c r="F339" s="2" t="inlineStr"/>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>behind a fully relativistic chirality statement + the one non-inherited anomaly candidate</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>open (#2b = the T4 gate)</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Gleason keystone</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>Soler lattice technical rigor (exchange-property geometry, inf-dim)</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr"/>
+      <c r="F340" s="2" t="inlineStr"/>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>the load-bearing residual riding under the whole reconstruction (#8b Gate 1)</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>open — 'reduced to the Soler residual'</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Substrate-evaluation</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>V5AttractiveSign/RelationalTick</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>Forward derivation of V5 from the primitives; the temporal envelope shape F_V5</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr"/>
+      <c r="F341" s="2" t="inlineStr"/>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
           <t>V5 existence stays a P10 posit</t>
         </is>
       </c>
-      <c r="H317" s="2" t="inlineStr">
+      <c r="H341" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="I317" s="2" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I317"/>
+  <autoFilter ref="A1:I341"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tier Key" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier Key'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15882,4 +15884,490 @@
   <autoFilter ref="A1:I402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="108" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>A settled result from another ED arc, cited here and built on — not re-derived in this folder.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Forced/proven from the 13 primitives (+ standard math) with NO paper-specific postulate — the strongest claim tier (theorems; M1).</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>D-via-I / Form-forced</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>The FORM is derived by composing inherited/standard pieces (derived-via-inherited); the form is forced, the numbers inherited.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Structural / conditional / account-tier: form-forced GIVEN a stated input or a declared paper-specific postulate (M2/M3).</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A canonical DEFINITION or catalogue (a kernel, the verdict grammar, an audit) — scaffolding, not a claim to be proven.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>A simulation / build-and-run / probe result on the certified substrate (or a faithful model of it).</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Inherited / Consilience</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Reproduces a known result/sequence framed THROUGH the substrate — supporting consilience, NOT a novel prediction.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Native / V5-conditional</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Mechanism is native but rests on V5, a faithful structural addition not shown primitive-forced.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A value taken from measurement, or a principled selection among a theorem's allowed options — not substrate-derived.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>A fundamental constant, by when it enters: event-scale (units, present at the first events) / derived-combination / inherited-late.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Primitive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>One of the 13 postulated axioms (P01-P13) — the corpus's single 'conditional on'; postulated, not derived, not claimed minimal.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Rests on a named paper-specific postulate (a declared commitment BEYOND the 13 primitives).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>An A-&gt;position / A-&gt;assertion: stated in the paper's own audit as a position, NOT proven (the weakest claim tier).</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Prediction</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>A falsifiable, experiment-facing bet — carries a kill-condition (see the Falsifier / Kill-Cond column).</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>A structural mapping onto an existing EXTERNAL framework (e.g. Penrose CCC, Jacobson's equation of state).</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>A proven or honestly-checked LIMIT — the order or result ED does NOT reach (a load-bearing 'no').</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>An arc consolidation / overview / organizing lens; composes standing results, adds no new derivation.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Retracted / withdrawn / superseded by a later corpus result (kept for provenance).</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>A declared OPEN / unclosed item — a named gap or frontier.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Claims" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Tier Key" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Untunability" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$402</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +39,28 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -79,12 +102,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -16370,4 +16414,221 @@
   <autoFilter ref="A1:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Untunability — the figure of merit: domains reproduced ÷ free inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>A proxy for “could you have tuned it?” — the answer is NO when the denominator is small AND shared. This counts DOMAINS (folders) and SHARED inputs, not claim-rows (see the caveat at the bottom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ingredients (computed from the Claims sheet)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Domains reproduced (independent physics folders)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>each with its standard structure form-reproduced; grows as you add sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Reproduced-structure claims across them</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Standing 7 / Derived 50 / D-via-I 13 / Grounded 82 / Measured 12 / Inherited 4 / Native 1 / Identification 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Forward predictions (separate; NOT reproductions)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>the falsifiable bets — not part of the reproduction count</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>— Shared axioms: the 13 primitives (P01–P13)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ONE set, shared across ALL domains — not 13-per-domain. The load-bearing fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>— Shared inherited scales</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>c, ħ, ℓ_P (= units, all 1) + H₀ (sets BOTH a₀ and Λ). G is derived; a₀/Λ are H₀-derived — not free knobs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>— Matter-sector values (inherited, as the SM's ~20)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>masses, couplings, α — openly inherited, not ED-fixed (same status as the Standard Model)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>— Live paper-specific postulates</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>~15</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>of 24 Postulated rows: −6 Foundations meta-rows (about the axiom system), −3 discharged/definitional (P14→QuadraticStrain, P-GW-Saddle=naming, P-NonAbelian-Analogy→MS-II). The only per-domain knobs; some still shared (V5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>FRAMING 1 — domains per shared primitive</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>FRAMING 2 — fixed denominator, growing numerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>12 domains ÷ 13 shared axioms  ≈  0.92 domains / primitive</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>denominator = 13 (fixed)   ·   numerator = 12 (and growing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>But this UNDERSELLS it: each of the 13 primitives feeds MANY domains, so they are reused, not spent per domain. The honest read is not “0.9” — it is that ~12 unrelated domains (gravity, the Born rule, viscoelastic relaxation, the dark sector…) come out of ONE 13-axiom structure. You cannot tune 13 shared primitives to independently hit that many unrelated fields by accident, because they all run through the SAME primitives.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Add a domain and the numerator rises; the denominator (13 primitives) does NOT. Contrast “a theory per domain” — GR + QM + a dark-matter particle + brute constants — where each new domain brings its OWN axioms AND its own inputs. ED adds domains at ~0 new-axiom cost. So the figure of merit is not a number to maximize; it is that the denominator refuses to grow while the numerator does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Why NOT results ÷ rows (172 / 88 ≈ 2 is meaningless): (1) numerator granularity is arbitrary — a folder is one domain but many rows (gravity 45, state-reduction 15); (2) the 41 Selected/Inherited rows are only ~5 DISTINCT values re-cited across folders (ħ, ℓ_P, c… counted once per folder is not a new knob); (3) the 24 Postulated rows include discharged and definitional-only ones. This sheet deliberately counts DOMAINS and SHARED inputs. Assumptions are stated in-cell so this reads as an argument, not a headline number.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="E15:G15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Untunability" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$I$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Claims'!$A$1:$J$402</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier Key'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I402"/>
+  <dimension ref="A1:J402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,7 @@
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,6 +557,11 @@
           <t>SpotChecked</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Postulate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -599,6 +605,7 @@
           <t>yes 2026-07-29 (read in full before import)</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -642,6 +649,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -681,6 +689,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -720,6 +729,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -763,6 +773,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -802,6 +813,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -841,6 +853,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -880,6 +893,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -919,6 +933,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -958,6 +973,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -997,6 +1013,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1036,6 +1053,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1075,6 +1093,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1114,6 +1133,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1157,6 +1177,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1196,6 +1217,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1231,6 +1253,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1266,6 +1289,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1301,6 +1325,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1336,6 +1361,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1371,6 +1397,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1406,6 +1433,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1441,6 +1469,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1480,6 +1509,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1523,6 +1553,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1558,6 +1589,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1593,6 +1625,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1628,6 +1661,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1663,6 +1697,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1698,6 +1733,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1733,6 +1769,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1772,6 +1809,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1807,6 +1845,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1842,6 +1881,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1881,6 +1921,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1916,6 +1957,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1951,6 +1993,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1986,6 +2029,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2025,6 +2069,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2068,6 +2113,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2103,6 +2149,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2138,6 +2185,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2177,6 +2225,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2216,6 +2265,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2251,6 +2301,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2286,6 +2337,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2321,6 +2373,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2356,6 +2409,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2391,6 +2445,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2434,6 +2489,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2473,6 +2529,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2512,6 +2569,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2555,6 +2613,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2598,6 +2657,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2637,6 +2697,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2680,6 +2741,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2719,6 +2781,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2758,6 +2821,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2797,6 +2861,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2836,6 +2901,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2871,6 +2937,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2906,6 +2973,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2941,6 +3009,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2976,6 +3045,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3015,6 +3085,11 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3054,6 +3129,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3093,6 +3169,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3132,6 +3209,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3171,6 +3249,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3206,6 +3285,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3241,6 +3321,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3280,6 +3361,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3319,6 +3401,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3354,6 +3437,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3389,6 +3473,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3424,6 +3509,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3459,6 +3545,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3494,6 +3581,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3529,6 +3617,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3564,6 +3653,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3603,6 +3693,7 @@
           <t>yes 2026-07-29 (read in full)</t>
         </is>
       </c>
+      <c r="J82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3646,6 +3737,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3689,6 +3781,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3732,6 +3825,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3775,6 +3869,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3822,6 +3917,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3869,6 +3965,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3912,6 +4009,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3951,6 +4049,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3990,6 +4089,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4029,6 +4129,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4068,6 +4169,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4111,6 +4213,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4150,6 +4253,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4189,6 +4293,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4228,6 +4333,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4271,6 +4377,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4314,6 +4421,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4357,6 +4465,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4396,6 +4505,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4435,6 +4545,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4478,6 +4589,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4517,6 +4629,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4556,6 +4669,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4595,6 +4709,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4634,6 +4749,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4677,6 +4793,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4716,6 +4833,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4759,6 +4877,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4798,6 +4917,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4837,6 +4957,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4880,6 +5001,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4919,6 +5041,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4958,6 +5081,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5001,6 +5125,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5036,6 +5161,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -5075,6 +5201,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5114,6 +5241,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5149,6 +5277,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5184,6 +5313,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5219,6 +5349,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>definitional</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5254,6 +5389,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5293,6 +5429,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5328,6 +5465,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5363,6 +5501,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5398,6 +5537,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5433,6 +5573,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5472,6 +5613,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5511,6 +5653,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5550,6 +5693,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5593,6 +5737,7 @@
           <t>yes 2026-07-28</t>
         </is>
       </c>
+      <c r="J132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5632,6 +5777,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5671,6 +5817,7 @@
           <t>yes 2026-07-28</t>
         </is>
       </c>
+      <c r="J134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5706,6 +5853,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5741,6 +5889,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5776,6 +5925,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5819,6 +5969,7 @@
           <t>yes 2026-07-28</t>
         </is>
       </c>
+      <c r="J138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5858,6 +6009,11 @@
           <t>yes 2026-07-28</t>
         </is>
       </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5893,6 +6049,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -5928,6 +6089,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5963,6 +6129,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -6002,6 +6173,7 @@
           <t>yes 2026-07-28</t>
         </is>
       </c>
+      <c r="J143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -6037,6 +6209,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -6072,6 +6245,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -6107,6 +6281,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6138,6 +6313,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -6173,6 +6349,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -6208,6 +6385,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6243,6 +6421,7 @@
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6282,6 +6461,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6325,6 +6505,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6364,6 +6545,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6403,6 +6585,7 @@
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -6438,6 +6621,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6477,6 +6661,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6520,6 +6705,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6563,6 +6749,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6598,6 +6785,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -6633,6 +6821,7 @@
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6668,6 +6857,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6703,6 +6893,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -6742,6 +6933,11 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6777,6 +6973,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -6812,6 +7013,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6847,6 +7053,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6882,6 +7093,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6921,6 +7137,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -6960,6 +7181,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6999,6 +7221,7 @@
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -7038,6 +7261,7 @@
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -7077,6 +7301,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -7112,6 +7337,7 @@
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -7147,6 +7373,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -7182,6 +7409,7 @@
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -7217,6 +7445,7 @@
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -7256,6 +7485,7 @@
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7295,6 +7525,7 @@
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -7334,6 +7565,7 @@
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -7373,6 +7605,7 @@
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -7412,6 +7645,7 @@
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -7455,6 +7689,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -7494,6 +7729,7 @@
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -7533,6 +7769,7 @@
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -7572,6 +7809,7 @@
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -7611,6 +7849,7 @@
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -7650,6 +7889,7 @@
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -7689,6 +7929,7 @@
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -7728,6 +7969,7 @@
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -7771,6 +8013,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -7810,6 +8053,7 @@
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -7853,6 +8097,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -7892,6 +8137,7 @@
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -7931,6 +8177,7 @@
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -7974,6 +8221,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -8017,6 +8265,7 @@
           <t>yes 2026-07-29 (corroborated via 030/QuadraticStrain checks)</t>
         </is>
       </c>
+      <c r="J196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -8056,6 +8305,7 @@
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -8095,6 +8345,7 @@
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -8134,6 +8385,7 @@
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -8173,6 +8425,7 @@
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -8212,6 +8465,7 @@
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -8251,6 +8505,7 @@
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -8290,6 +8545,7 @@
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -8329,6 +8585,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -8368,6 +8625,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -8403,6 +8661,7 @@
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -8438,6 +8697,11 @@
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>discharged</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -8473,6 +8737,11 @@
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -8508,6 +8777,11 @@
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -8551,6 +8825,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -8594,6 +8869,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -8633,6 +8909,7 @@
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8672,6 +8949,7 @@
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -8715,6 +8993,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -8754,6 +9033,7 @@
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -8789,6 +9069,7 @@
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -8828,6 +9109,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -8863,6 +9145,7 @@
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -8898,6 +9181,7 @@
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -8933,6 +9217,7 @@
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -8972,6 +9257,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -9011,6 +9297,7 @@
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -9050,6 +9337,7 @@
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -9089,6 +9377,7 @@
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -9128,6 +9417,7 @@
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -9167,6 +9457,7 @@
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -9206,6 +9497,7 @@
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
+      <c r="J227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -9241,6 +9533,7 @@
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -9280,6 +9573,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -9315,6 +9609,7 @@
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -9350,6 +9645,7 @@
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -9385,6 +9681,7 @@
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -9420,6 +9717,7 @@
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -9459,6 +9757,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -9494,6 +9793,7 @@
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -9529,6 +9829,7 @@
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -9564,6 +9865,7 @@
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -9599,6 +9901,7 @@
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -9638,6 +9941,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -9673,6 +9977,7 @@
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -9712,6 +10017,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -9751,6 +10057,7 @@
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr"/>
+      <c r="J242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -9790,6 +10097,7 @@
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr"/>
+      <c r="J243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -9833,6 +10141,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -9868,6 +10177,7 @@
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
+      <c r="J245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -9907,6 +10217,7 @@
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr"/>
+      <c r="J246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -9946,6 +10257,7 @@
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
+      <c r="J247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -9989,6 +10301,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -10028,6 +10341,7 @@
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr"/>
+      <c r="J249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -10067,6 +10381,7 @@
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -10106,6 +10421,7 @@
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr"/>
+      <c r="J251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -10145,6 +10461,7 @@
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr"/>
+      <c r="J252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -10180,6 +10497,7 @@
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -10219,6 +10537,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -10254,6 +10573,7 @@
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr"/>
+      <c r="J255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -10297,6 +10617,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -10332,6 +10653,7 @@
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr"/>
+      <c r="J257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -10375,6 +10697,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -10410,6 +10733,7 @@
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr"/>
+      <c r="J259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -10445,6 +10769,7 @@
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -10480,6 +10805,7 @@
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr"/>
+      <c r="J261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -10515,6 +10841,7 @@
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
+      <c r="J262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -10550,6 +10877,7 @@
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
+      <c r="J263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -10585,6 +10913,7 @@
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr"/>
+      <c r="J264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -10620,6 +10949,7 @@
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr"/>
+      <c r="J265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -10659,6 +10989,7 @@
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
+      <c r="J266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -10694,6 +11025,7 @@
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
+      <c r="J267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -10733,6 +11065,7 @@
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -10776,6 +11109,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -10815,6 +11149,7 @@
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr"/>
+      <c r="J270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -10854,6 +11189,7 @@
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -10897,6 +11233,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -10936,6 +11273,7 @@
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -10975,6 +11313,7 @@
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
+      <c r="J274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -11018,6 +11357,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -11057,6 +11397,7 @@
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr"/>
+      <c r="J276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -11096,6 +11437,7 @@
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr"/>
+      <c r="J277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -11135,6 +11477,7 @@
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -11178,6 +11521,7 @@
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr"/>
+      <c r="J279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -11221,6 +11565,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -11264,6 +11609,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr"/>
+      <c r="J281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -11303,6 +11649,7 @@
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr"/>
+      <c r="J282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -11338,6 +11685,7 @@
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -11377,6 +11725,7 @@
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -11416,6 +11765,7 @@
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -11451,6 +11801,7 @@
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr"/>
+      <c r="J286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -11486,6 +11837,7 @@
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr"/>
+      <c r="J287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -11521,6 +11873,7 @@
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -11556,6 +11909,11 @@
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr"/>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>discharged</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -11591,6 +11949,11 @@
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr"/>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -11626,6 +11989,11 @@
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr"/>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -11661,6 +12029,11 @@
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr"/>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -11696,6 +12069,7 @@
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr"/>
+      <c r="J293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -11735,6 +12109,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -11774,6 +12149,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -11809,6 +12185,7 @@
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr"/>
+      <c r="J296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -11848,6 +12225,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -11883,6 +12261,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr"/>
+      <c r="J298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -11918,6 +12297,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
+      <c r="J299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -11961,6 +12341,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -12000,6 +12381,7 @@
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr"/>
+      <c r="J301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -12039,6 +12421,7 @@
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr"/>
+      <c r="J302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -12078,6 +12461,7 @@
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr"/>
+      <c r="J303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -12117,6 +12501,7 @@
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr"/>
+      <c r="J304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -12160,6 +12545,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -12199,6 +12585,7 @@
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr"/>
+      <c r="J306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -12242,6 +12629,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -12281,6 +12669,7 @@
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr"/>
+      <c r="J308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -12320,6 +12709,7 @@
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr"/>
+      <c r="J309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -12359,6 +12749,7 @@
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr"/>
+      <c r="J310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -12398,6 +12789,7 @@
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
+      <c r="J311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -12437,6 +12829,7 @@
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr"/>
+      <c r="J312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -12476,6 +12869,7 @@
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr"/>
+      <c r="J313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -12515,6 +12909,7 @@
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr"/>
+      <c r="J314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -12554,6 +12949,7 @@
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr"/>
+      <c r="J315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -12593,6 +12989,7 @@
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr"/>
+      <c r="J316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -12632,6 +13029,7 @@
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr"/>
+      <c r="J317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -12675,6 +13073,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -12718,6 +13117,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -12753,6 +13153,7 @@
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr"/>
+      <c r="J320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -12788,6 +13189,7 @@
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>
+      <c r="J321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -12827,6 +13229,7 @@
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr"/>
+      <c r="J322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -12866,6 +13269,11 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -12901,6 +13309,11 @@
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr"/>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -12936,6 +13349,7 @@
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr"/>
+      <c r="J325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -12975,6 +13389,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -13018,6 +13433,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -13061,6 +13477,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -13108,6 +13525,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -13151,6 +13569,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -13194,6 +13613,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -13233,6 +13653,7 @@
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr"/>
+      <c r="J332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -13272,6 +13693,7 @@
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr"/>
+      <c r="J333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -13311,6 +13733,7 @@
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr"/>
+      <c r="J334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -13350,6 +13773,7 @@
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr"/>
+      <c r="J335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -13389,6 +13813,7 @@
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr"/>
+      <c r="J336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -13432,6 +13857,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J337" s="2" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -13471,6 +13897,7 @@
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr"/>
+      <c r="J338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -13510,6 +13937,7 @@
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr"/>
+      <c r="J339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -13549,6 +13977,7 @@
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr"/>
+      <c r="J340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -13588,6 +14017,7 @@
         </is>
       </c>
       <c r="I341" s="2" t="inlineStr"/>
+      <c r="J341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -13631,6 +14061,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -13670,6 +14101,11 @@
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr"/>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -13705,6 +14141,7 @@
         </is>
       </c>
       <c r="I344" s="2" t="inlineStr"/>
+      <c r="J344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -13740,6 +14177,7 @@
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr"/>
+      <c r="J345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -13779,6 +14217,7 @@
           <t>yes 2026-07-29 (read in full)</t>
         </is>
       </c>
+      <c r="J346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -13814,6 +14253,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -13853,6 +14293,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -13896,6 +14337,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -13939,6 +14381,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -13978,6 +14421,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -14021,6 +14465,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -14064,6 +14509,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -14103,6 +14549,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -14146,6 +14593,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -14189,6 +14637,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -14232,6 +14681,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -14271,6 +14721,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -14310,6 +14761,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -14349,6 +14801,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -14392,6 +14845,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -14431,6 +14885,7 @@
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr"/>
+      <c r="J362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -14474,6 +14929,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -14513,6 +14969,7 @@
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr"/>
+      <c r="J364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -14552,6 +15009,7 @@
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr"/>
+      <c r="J365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -14591,6 +15049,7 @@
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr"/>
+      <c r="J366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -14630,6 +15089,7 @@
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr"/>
+      <c r="J367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -14673,6 +15133,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -14716,6 +15177,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -14759,6 +15221,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -14798,6 +15261,7 @@
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr"/>
+      <c r="J371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -14837,6 +15301,7 @@
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr"/>
+      <c r="J372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -14876,6 +15341,7 @@
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr"/>
+      <c r="J373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -14915,6 +15381,7 @@
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr"/>
+      <c r="J374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -14954,6 +15421,7 @@
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr"/>
+      <c r="J375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -14993,6 +15461,7 @@
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr"/>
+      <c r="J376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -15032,6 +15501,7 @@
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr"/>
+      <c r="J377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -15067,6 +15537,7 @@
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr"/>
+      <c r="J378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -15102,6 +15573,7 @@
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr"/>
+      <c r="J379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -15137,6 +15609,7 @@
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr"/>
+      <c r="J380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -15172,6 +15645,7 @@
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr"/>
+      <c r="J381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -15207,6 +15681,11 @@
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr"/>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -15242,6 +15721,11 @@
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr"/>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -15277,6 +15761,7 @@
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr"/>
+      <c r="J384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -15312,6 +15797,7 @@
         </is>
       </c>
       <c r="I385" s="2" t="inlineStr"/>
+      <c r="J385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -15351,6 +15837,7 @@
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr"/>
+      <c r="J386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -15390,6 +15877,7 @@
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr"/>
+      <c r="J387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -15425,6 +15913,7 @@
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr"/>
+      <c r="J388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -15464,6 +15953,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -15499,6 +15989,7 @@
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr"/>
+      <c r="J390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -15538,6 +16029,7 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
+      <c r="J391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -15573,6 +16065,7 @@
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr"/>
+      <c r="J392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -15608,6 +16101,7 @@
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr"/>
+      <c r="J393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -15643,6 +16137,7 @@
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr"/>
+      <c r="J394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -15678,6 +16173,7 @@
         </is>
       </c>
       <c r="I395" s="2" t="inlineStr"/>
+      <c r="J395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -15713,6 +16209,7 @@
         </is>
       </c>
       <c r="I396" s="2" t="inlineStr"/>
+      <c r="J396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -15748,6 +16245,7 @@
         </is>
       </c>
       <c r="I397" s="2" t="inlineStr"/>
+      <c r="J397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -15783,6 +16281,7 @@
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr"/>
+      <c r="J398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -15818,6 +16317,7 @@
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
+      <c r="J399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -15853,6 +16353,7 @@
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
+      <c r="J400" s="2" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -15888,6 +16389,7 @@
         </is>
       </c>
       <c r="I401" s="2" t="inlineStr"/>
+      <c r="J401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -15923,9 +16425,10 @@
         </is>
       </c>
       <c r="I402" s="2" t="inlineStr"/>
+      <c r="J402" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I402"/>
+  <autoFilter ref="A1:J402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16563,14 +17066,12 @@
           <t>— Live paper-specific postulates</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>~15</t>
-        </is>
+      <c r="B11" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>of 24 Postulated rows: −6 Foundations meta-rows (about the axiom system), −3 discharged/definitional (P14→QuadraticStrain, P-GW-Saddle=naming, P-NonAbelian-Analogy→MS-II). The only per-domain knobs; some still shared (V5).</t>
+          <t>of 24 Postulated rows (see the 'Postulate' flag column on the Claims sheet): 15 live, 2 discharged (P14→QuadraticStrain, P-NonAbelian-Analogy→MS-II §2), 1 definitional-only (P-GW-Saddle, naming), 6 Foundations meta-rows. The live ones are the only per-domain knobs; some still shared (V5).</t>
         </is>
       </c>
     </row>

--- a/ED_TieredClaims_Master.xlsx
+++ b/ED_TieredClaims_Master.xlsx
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E2" s="40" t="inlineStr">
         <is>
-          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense)</t>
+          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense) || DISCRIMINATOR (2026-08-02): a0=cH(z) [ED, RISES with z] vs a0=c2*sqrt(Lambda) [CONSTANT] coincide today but diverge with z; a0 following the sqrt(Lambda)-constant form rather than cH(z) refutes the ED relation. Recent high-z RAR literature (arXiv 2405.01841, 2504.20857) shows a MILD PREFERENCE for a0 rising with z -&gt; favors ED's cH(z) over the Lambda-tied form.</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="E46" s="41" t="inlineStr">
         <is>
-          <t>F3: MOND scale shown CONSTANT with z refutes it. First data (MUSE-DARK III, A&amp;A 2026) instead EXCLUDE constant a0 at ~30sigma (evolution confirmed); a robustly-confirmed rate incompatible with ~H(z) refutes the EXACT bet (data run faster), not the evolution</t>
+          <t>F3: MOND scale shown CONSTANT with z refutes it. First data (MUSE-DARK III, A&amp;A 2026) instead EXCLUDE constant a0 at ~30sigma (evolution confirmed); a robustly-confirmed rate incompatible with ~H(z) refutes the EXACT bet (data run faster), not the evolution || DISCRIMINATOR (2026-08-02): a0=cH(z) [ED, RISES with z] vs a0=c2*sqrt(Lambda) [CONSTANT] coincide today but diverge with z; a0 following the sqrt(Lambda)-constant form rather than cH(z) refutes the ED relation. Recent high-z RAR literature (arXiv 2405.01841, 2504.20857) shows a MILD PREFERENCE for a0 rising with z -&gt; favors ED's cH(z) over the Lambda-tied form.</t>
         </is>
       </c>
       <c r="F46" s="41" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="E288" s="41" t="inlineStr">
         <is>
-          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense)</t>
+          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense) || DISCRIMINATOR (2026-08-02): a0=cH(z) [ED, RISES with z] vs a0=c2*sqrt(Lambda) [CONSTANT] coincide today but diverge with z; a0 following the sqrt(Lambda)-constant form rather than cH(z) refutes the ED relation. Recent high-z RAR literature (arXiv 2405.01841, 2504.20857) shows a MILD PREFERENCE for a0 rising with z -&gt; favors ED's cH(z) over the Lambda-tied form.</t>
         </is>
       </c>
       <c r="F288" s="41" t="n"/>
